--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="191">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,339 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>CONCACAF Nations League A</t>
+  </si>
+  <si>
+    <t>CONCACAF Nations League B</t>
+  </si>
+  <si>
+    <t>Canadian Premier League</t>
+  </si>
+  <si>
+    <t>Mexican Liga MX</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Spanish Segunda Division</t>
+  </si>
+  <si>
+    <t>UEFA Nations League</t>
+  </si>
+  <si>
+    <t>Slovakian 2 Liga</t>
+  </si>
+  <si>
+    <t>Swedish Division 1</t>
+  </si>
+  <si>
+    <t>Dutch Eerste Divisie</t>
+  </si>
+  <si>
+    <t>Argentinian Primera B Metropolitana</t>
+  </si>
+  <si>
+    <t>Irish Division 1</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>01:15:00</t>
+  </si>
+  <si>
+    <t>03:00:00</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>14:15:00</t>
+  </si>
+  <si>
+    <t>14:30:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
+    <t>19:30:00</t>
+  </si>
+  <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
+    <t>Jamaica</t>
+  </si>
+  <si>
+    <t>Barbados</t>
+  </si>
+  <si>
+    <t>Honduras</t>
+  </si>
+  <si>
+    <t>Cavalry</t>
+  </si>
+  <si>
+    <t>Atlante</t>
+  </si>
+  <si>
+    <t>Once Caldas</t>
+  </si>
+  <si>
+    <t>El Salvador</t>
+  </si>
+  <si>
+    <t>Tijuana</t>
+  </si>
+  <si>
+    <t>AD Ceuta FC</t>
+  </si>
+  <si>
+    <t>Slovenia</t>
+  </si>
+  <si>
+    <t>OFK Banik Lehota</t>
+  </si>
+  <si>
+    <t>Samorin</t>
+  </si>
+  <si>
+    <t>MSK Povazska Bystrica</t>
+  </si>
+  <si>
+    <t>Sollentuna FF</t>
+  </si>
+  <si>
+    <t>Granada</t>
+  </si>
+  <si>
+    <t>Heracles</t>
+  </si>
+  <si>
+    <t>Utsiktens</t>
+  </si>
+  <si>
+    <t>Faroe Islands</t>
+  </si>
+  <si>
+    <t>Bulgaria</t>
+  </si>
+  <si>
+    <t>Iceland</t>
+  </si>
+  <si>
+    <t>San Marino</t>
+  </si>
+  <si>
+    <t>Zlate Moravce</t>
+  </si>
+  <si>
+    <t>Celta Vigo B</t>
+  </si>
+  <si>
+    <t>Tenerife</t>
+  </si>
+  <si>
+    <t>MVV Maastricht</t>
+  </si>
+  <si>
+    <t>FC Volendam</t>
+  </si>
+  <si>
+    <t>NAC Breda</t>
+  </si>
+  <si>
+    <t>Emmen</t>
+  </si>
+  <si>
+    <t>Argentino de Merlo</t>
+  </si>
+  <si>
+    <t>Roda JC</t>
+  </si>
+  <si>
+    <t>Longford</t>
+  </si>
+  <si>
+    <t>Slovakia</t>
+  </si>
+  <si>
+    <t>Albania</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>Czechia</t>
+  </si>
+  <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
+    <t>Nautico PE</t>
+  </si>
+  <si>
+    <t>Operario PR</t>
+  </si>
+  <si>
+    <t>HFX Wanderers</t>
+  </si>
+  <si>
+    <t>Guatemala</t>
+  </si>
+  <si>
+    <t>St Lucia</t>
+  </si>
+  <si>
+    <t>Suriname</t>
+  </si>
+  <si>
+    <t>FC Supra du Quebec</t>
+  </si>
+  <si>
+    <t>Monterrey</t>
+  </si>
+  <si>
+    <t>Atletico Bucaramanga</t>
+  </si>
+  <si>
+    <t>Martinique</t>
+  </si>
+  <si>
+    <t>Atlas</t>
+  </si>
+  <si>
+    <t>Sociedad B</t>
+  </si>
+  <si>
+    <t>Scotland</t>
+  </si>
+  <si>
+    <t>FC Slovan Galanta</t>
+  </si>
+  <si>
+    <t>Lokomotiva Zvolen</t>
+  </si>
+  <si>
+    <t>FO Kinex Bytca</t>
+  </si>
+  <si>
+    <t>FC Stockholm Internazionale</t>
+  </si>
+  <si>
+    <t>FC Andorra</t>
+  </si>
+  <si>
+    <t>Vitesse Arnhem</t>
+  </si>
+  <si>
+    <t>Jonkopings Sodra</t>
+  </si>
+  <si>
+    <t>Kazakhstan</t>
+  </si>
+  <si>
+    <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>Estonia</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t>FC Petrzalka</t>
+  </si>
+  <si>
+    <t>Sabadell</t>
+  </si>
+  <si>
+    <t>Cadiz</t>
+  </si>
+  <si>
+    <t>Helmond Sport</t>
+  </si>
+  <si>
+    <t>VVV Venlo</t>
+  </si>
+  <si>
+    <t>FC Eindhoven</t>
+  </si>
+  <si>
+    <t>FC Oss</t>
+  </si>
+  <si>
+    <t>Villa San Carlos</t>
+  </si>
+  <si>
+    <t>RKC Waalwijk</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Moldova</t>
+  </si>
+  <si>
+    <t>Belarus</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Croatia</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
+    <t>Ceara SC Fortaleza</t>
+  </si>
+  <si>
+    <t>Atletico Ottawa</t>
+  </si>
+  <si>
+    <t>2026-09-24 01:37:00</t>
   </si>
 </sst>
 </file>
@@ -585,7 +918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +1161,9444 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2">
+        <v>1.75</v>
+      </c>
+      <c r="G2">
+        <v>2.22</v>
+      </c>
+      <c r="H2">
+        <v>3.85</v>
+      </c>
+      <c r="I2">
+        <v>6.2</v>
+      </c>
+      <c r="J2">
+        <v>3.2</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>1.45</v>
+      </c>
+      <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
+        <v>2.4</v>
+      </c>
+      <c r="O2">
+        <v>1.41</v>
+      </c>
+      <c r="P2">
+        <v>1.55</v>
+      </c>
+      <c r="Q2">
+        <v>2</v>
+      </c>
+      <c r="R2">
+        <v>1.19</v>
+      </c>
+      <c r="S2">
+        <v>3.7</v>
+      </c>
+      <c r="T2">
+        <v>1.01</v>
+      </c>
+      <c r="U2">
+        <v>1.01</v>
+      </c>
+      <c r="V2">
+        <v>1.2</v>
+      </c>
+      <c r="W2">
+        <v>1.81</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.03</v>
+      </c>
+      <c r="AQ2">
+        <v>1.03</v>
+      </c>
+      <c r="AR2">
+        <v>1.03</v>
+      </c>
+      <c r="AS2">
+        <v>1.03</v>
+      </c>
+      <c r="AT2">
+        <v>1.03</v>
+      </c>
+      <c r="AU2">
+        <v>1.03</v>
+      </c>
+      <c r="AV2">
+        <v>1.03</v>
+      </c>
+      <c r="AW2">
+        <v>1.03</v>
+      </c>
+      <c r="AX2">
+        <v>1.03</v>
+      </c>
+      <c r="AY2">
+        <v>1.03</v>
+      </c>
+      <c r="AZ2">
+        <v>1.03</v>
+      </c>
+      <c r="BA2">
+        <v>1.03</v>
+      </c>
+      <c r="BB2">
+        <v>1.03</v>
+      </c>
+      <c r="BC2">
+        <v>1.03</v>
+      </c>
+      <c r="BD2">
+        <v>1.03</v>
+      </c>
+      <c r="BE2">
+        <v>1.03</v>
+      </c>
+      <c r="BF2">
+        <v>1.01</v>
+      </c>
+      <c r="BG2">
+        <v>1.01</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>2.54</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F3">
+        <v>3.15</v>
+      </c>
+      <c r="G3">
+        <v>3.45</v>
+      </c>
+      <c r="H3">
+        <v>2.32</v>
+      </c>
+      <c r="I3">
+        <v>2.42</v>
+      </c>
+      <c r="J3">
+        <v>3.55</v>
+      </c>
+      <c r="K3">
+        <v>3.9</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.05</v>
+      </c>
+      <c r="N3">
+        <v>3.55</v>
+      </c>
+      <c r="O3">
+        <v>1.27</v>
+      </c>
+      <c r="P3">
+        <v>1.98</v>
+      </c>
+      <c r="Q3">
+        <v>1.81</v>
+      </c>
+      <c r="R3">
+        <v>1.41</v>
+      </c>
+      <c r="S3">
+        <v>2.8</v>
+      </c>
+      <c r="T3">
+        <v>1.67</v>
+      </c>
+      <c r="U3">
+        <v>2.22</v>
+      </c>
+      <c r="V3">
+        <v>1.7</v>
+      </c>
+      <c r="W3">
+        <v>1.4</v>
+      </c>
+      <c r="X3">
+        <v>17</v>
+      </c>
+      <c r="Y3">
+        <v>11.5</v>
+      </c>
+      <c r="Z3">
+        <v>16</v>
+      </c>
+      <c r="AA3">
+        <v>30</v>
+      </c>
+      <c r="AB3">
+        <v>15</v>
+      </c>
+      <c r="AC3">
+        <v>8.6</v>
+      </c>
+      <c r="AD3">
+        <v>11.5</v>
+      </c>
+      <c r="AE3">
+        <v>24</v>
+      </c>
+      <c r="AF3">
+        <v>25</v>
+      </c>
+      <c r="AG3">
+        <v>14.5</v>
+      </c>
+      <c r="AH3">
+        <v>17</v>
+      </c>
+      <c r="AI3">
+        <v>36</v>
+      </c>
+      <c r="AJ3">
+        <v>60</v>
+      </c>
+      <c r="AK3">
+        <v>38</v>
+      </c>
+      <c r="AL3">
+        <v>46</v>
+      </c>
+      <c r="AM3">
+        <v>90</v>
+      </c>
+      <c r="AN3">
+        <v>34</v>
+      </c>
+      <c r="AO3">
+        <v>16.5</v>
+      </c>
+      <c r="AP3">
+        <v>11</v>
+      </c>
+      <c r="AQ3">
+        <v>10</v>
+      </c>
+      <c r="AR3">
+        <v>13.5</v>
+      </c>
+      <c r="AS3">
+        <v>26</v>
+      </c>
+      <c r="AT3">
+        <v>12.5</v>
+      </c>
+      <c r="AU3">
+        <v>1.03</v>
+      </c>
+      <c r="AV3">
+        <v>10</v>
+      </c>
+      <c r="AW3">
+        <v>20</v>
+      </c>
+      <c r="AX3">
+        <v>17</v>
+      </c>
+      <c r="AY3">
+        <v>1.03</v>
+      </c>
+      <c r="AZ3">
+        <v>14.5</v>
+      </c>
+      <c r="BA3">
+        <v>1.03</v>
+      </c>
+      <c r="BB3">
+        <v>42</v>
+      </c>
+      <c r="BC3">
+        <v>25</v>
+      </c>
+      <c r="BD3">
+        <v>36</v>
+      </c>
+      <c r="BE3">
+        <v>1.03</v>
+      </c>
+      <c r="BF3">
+        <v>19.5</v>
+      </c>
+      <c r="BG3">
+        <v>13.5</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>2.76</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.01</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F4">
+        <v>1.83</v>
+      </c>
+      <c r="G4">
+        <v>2.04</v>
+      </c>
+      <c r="H4">
+        <v>4.1</v>
+      </c>
+      <c r="I4">
+        <v>5.6</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>3.75</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.08</v>
+      </c>
+      <c r="N4">
+        <v>2.88</v>
+      </c>
+      <c r="O4">
+        <v>1.4</v>
+      </c>
+      <c r="P4">
+        <v>1.63</v>
+      </c>
+      <c r="Q4">
+        <v>2.1</v>
+      </c>
+      <c r="R4">
+        <v>1.25</v>
+      </c>
+      <c r="S4">
+        <v>3.35</v>
+      </c>
+      <c r="T4">
+        <v>1.98</v>
+      </c>
+      <c r="U4">
+        <v>1.83</v>
+      </c>
+      <c r="V4">
+        <v>1.21</v>
+      </c>
+      <c r="W4">
+        <v>1.96</v>
+      </c>
+      <c r="X4">
+        <v>12</v>
+      </c>
+      <c r="Y4">
+        <v>15.5</v>
+      </c>
+      <c r="Z4">
+        <v>46</v>
+      </c>
+      <c r="AA4">
+        <v>170</v>
+      </c>
+      <c r="AB4">
+        <v>7.6</v>
+      </c>
+      <c r="AC4">
+        <v>8.4</v>
+      </c>
+      <c r="AD4">
+        <v>22</v>
+      </c>
+      <c r="AE4">
+        <v>100</v>
+      </c>
+      <c r="AF4">
+        <v>11.5</v>
+      </c>
+      <c r="AG4">
+        <v>11</v>
+      </c>
+      <c r="AH4">
+        <v>24</v>
+      </c>
+      <c r="AI4">
+        <v>110</v>
+      </c>
+      <c r="AJ4">
+        <v>24</v>
+      </c>
+      <c r="AK4">
+        <v>25</v>
+      </c>
+      <c r="AL4">
+        <v>60</v>
+      </c>
+      <c r="AM4">
+        <v>190</v>
+      </c>
+      <c r="AN4">
+        <v>22</v>
+      </c>
+      <c r="AO4">
+        <v>140</v>
+      </c>
+      <c r="AP4">
+        <v>4.6</v>
+      </c>
+      <c r="AQ4">
+        <v>5</v>
+      </c>
+      <c r="AR4">
+        <v>6.4</v>
+      </c>
+      <c r="AS4">
+        <v>7</v>
+      </c>
+      <c r="AT4">
+        <v>3.75</v>
+      </c>
+      <c r="AU4">
+        <v>3.95</v>
+      </c>
+      <c r="AV4">
+        <v>5.5</v>
+      </c>
+      <c r="AW4">
+        <v>6.8</v>
+      </c>
+      <c r="AX4">
+        <v>4.5</v>
+      </c>
+      <c r="AY4">
+        <v>4.4</v>
+      </c>
+      <c r="AZ4">
+        <v>5.7</v>
+      </c>
+      <c r="BA4">
+        <v>7</v>
+      </c>
+      <c r="BB4">
+        <v>5.7</v>
+      </c>
+      <c r="BC4">
+        <v>5.7</v>
+      </c>
+      <c r="BD4">
+        <v>6.6</v>
+      </c>
+      <c r="BE4">
+        <v>7</v>
+      </c>
+      <c r="BF4">
+        <v>5.5</v>
+      </c>
+      <c r="BG4">
+        <v>7</v>
+      </c>
+      <c r="BH4">
+        <v>3.8</v>
+      </c>
+      <c r="BI4">
+        <v>2.52</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.01</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.01</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.01</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F5">
+        <v>1.64</v>
+      </c>
+      <c r="G5">
+        <v>1.9</v>
+      </c>
+      <c r="H5">
+        <v>3.9</v>
+      </c>
+      <c r="I5">
+        <v>6.4</v>
+      </c>
+      <c r="J5">
+        <v>3.85</v>
+      </c>
+      <c r="K5">
+        <v>7.4</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.01</v>
+      </c>
+      <c r="N5">
+        <v>3.5</v>
+      </c>
+      <c r="O5">
+        <v>1.19</v>
+      </c>
+      <c r="P5">
+        <v>2.16</v>
+      </c>
+      <c r="Q5">
+        <v>1.53</v>
+      </c>
+      <c r="R5">
+        <v>1.43</v>
+      </c>
+      <c r="S5">
+        <v>2.4</v>
+      </c>
+      <c r="T5">
+        <v>1.01</v>
+      </c>
+      <c r="U5">
+        <v>1.01</v>
+      </c>
+      <c r="V5">
+        <v>1.19</v>
+      </c>
+      <c r="W5">
+        <v>2.1</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>1000</v>
+      </c>
+      <c r="AD5">
+        <v>1000</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>1000</v>
+      </c>
+      <c r="AH5">
+        <v>1000</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>1.03</v>
+      </c>
+      <c r="AQ5">
+        <v>1.03</v>
+      </c>
+      <c r="AR5">
+        <v>1.03</v>
+      </c>
+      <c r="AS5">
+        <v>1.03</v>
+      </c>
+      <c r="AT5">
+        <v>1.03</v>
+      </c>
+      <c r="AU5">
+        <v>1.03</v>
+      </c>
+      <c r="AV5">
+        <v>1.03</v>
+      </c>
+      <c r="AW5">
+        <v>1.03</v>
+      </c>
+      <c r="AX5">
+        <v>1.03</v>
+      </c>
+      <c r="AY5">
+        <v>1.03</v>
+      </c>
+      <c r="AZ5">
+        <v>1.03</v>
+      </c>
+      <c r="BA5">
+        <v>1.03</v>
+      </c>
+      <c r="BB5">
+        <v>1.03</v>
+      </c>
+      <c r="BC5">
+        <v>1.03</v>
+      </c>
+      <c r="BD5">
+        <v>1.03</v>
+      </c>
+      <c r="BE5">
+        <v>1.03</v>
+      </c>
+      <c r="BF5">
+        <v>1.01</v>
+      </c>
+      <c r="BG5">
+        <v>1.01</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.01</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.01</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.01</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F6">
+        <v>3.7</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>2.02</v>
+      </c>
+      <c r="I6">
+        <v>2.12</v>
+      </c>
+      <c r="J6">
+        <v>3.8</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>1.31</v>
+      </c>
+      <c r="M6">
+        <v>1.05</v>
+      </c>
+      <c r="N6">
+        <v>4.4</v>
+      </c>
+      <c r="O6">
+        <v>1.26</v>
+      </c>
+      <c r="P6">
+        <v>2.16</v>
+      </c>
+      <c r="Q6">
+        <v>1.78</v>
+      </c>
+      <c r="R6">
+        <v>1.46</v>
+      </c>
+      <c r="S6">
+        <v>2.96</v>
+      </c>
+      <c r="T6">
+        <v>1.68</v>
+      </c>
+      <c r="U6">
+        <v>2.3</v>
+      </c>
+      <c r="V6">
+        <v>1.86</v>
+      </c>
+      <c r="W6">
+        <v>1.34</v>
+      </c>
+      <c r="X6">
+        <v>24</v>
+      </c>
+      <c r="Y6">
+        <v>11.5</v>
+      </c>
+      <c r="Z6">
+        <v>14.5</v>
+      </c>
+      <c r="AA6">
+        <v>25</v>
+      </c>
+      <c r="AB6">
+        <v>20</v>
+      </c>
+      <c r="AC6">
+        <v>9</v>
+      </c>
+      <c r="AD6">
+        <v>11</v>
+      </c>
+      <c r="AE6">
+        <v>21</v>
+      </c>
+      <c r="AF6">
+        <v>32</v>
+      </c>
+      <c r="AG6">
+        <v>16</v>
+      </c>
+      <c r="AH6">
+        <v>16.5</v>
+      </c>
+      <c r="AI6">
+        <v>38</v>
+      </c>
+      <c r="AJ6">
+        <v>70</v>
+      </c>
+      <c r="AK6">
+        <v>42</v>
+      </c>
+      <c r="AL6">
+        <v>46</v>
+      </c>
+      <c r="AM6">
+        <v>75</v>
+      </c>
+      <c r="AN6">
+        <v>44</v>
+      </c>
+      <c r="AO6">
+        <v>12.5</v>
+      </c>
+      <c r="AP6">
+        <v>16</v>
+      </c>
+      <c r="AQ6">
+        <v>10</v>
+      </c>
+      <c r="AR6">
+        <v>12.5</v>
+      </c>
+      <c r="AS6">
+        <v>7.2</v>
+      </c>
+      <c r="AT6">
+        <v>14.5</v>
+      </c>
+      <c r="AU6">
+        <v>8</v>
+      </c>
+      <c r="AV6">
+        <v>9.4</v>
+      </c>
+      <c r="AW6">
+        <v>18</v>
+      </c>
+      <c r="AX6">
+        <v>7.4</v>
+      </c>
+      <c r="AY6">
+        <v>14</v>
+      </c>
+      <c r="AZ6">
+        <v>15</v>
+      </c>
+      <c r="BA6">
+        <v>7.8</v>
+      </c>
+      <c r="BB6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC6">
+        <v>36</v>
+      </c>
+      <c r="BD6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF6">
+        <v>8</v>
+      </c>
+      <c r="BG6">
+        <v>11</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>3.2</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>7</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>5.6</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.01</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>4.2</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>2.16</v>
+      </c>
+      <c r="H7">
+        <v>4.1</v>
+      </c>
+      <c r="I7">
+        <v>4.8</v>
+      </c>
+      <c r="J7">
+        <v>3.35</v>
+      </c>
+      <c r="K7">
+        <v>3.6</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.09</v>
+      </c>
+      <c r="N7">
+        <v>3.15</v>
+      </c>
+      <c r="O7">
+        <v>1.4</v>
+      </c>
+      <c r="P7">
+        <v>1.77</v>
+      </c>
+      <c r="Q7">
+        <v>2.14</v>
+      </c>
+      <c r="R7">
+        <v>1.25</v>
+      </c>
+      <c r="S7">
+        <v>3.95</v>
+      </c>
+      <c r="T7">
+        <v>1.95</v>
+      </c>
+      <c r="U7">
+        <v>1.97</v>
+      </c>
+      <c r="V7">
+        <v>1.27</v>
+      </c>
+      <c r="W7">
+        <v>1.87</v>
+      </c>
+      <c r="X7">
+        <v>14</v>
+      </c>
+      <c r="Y7">
+        <v>16.5</v>
+      </c>
+      <c r="Z7">
+        <v>34</v>
+      </c>
+      <c r="AA7">
+        <v>120</v>
+      </c>
+      <c r="AB7">
+        <v>9.6</v>
+      </c>
+      <c r="AC7">
+        <v>9.4</v>
+      </c>
+      <c r="AD7">
+        <v>22</v>
+      </c>
+      <c r="AE7">
+        <v>75</v>
+      </c>
+      <c r="AF7">
+        <v>15</v>
+      </c>
+      <c r="AG7">
+        <v>11.5</v>
+      </c>
+      <c r="AH7">
+        <v>25</v>
+      </c>
+      <c r="AI7">
+        <v>85</v>
+      </c>
+      <c r="AJ7">
+        <v>27</v>
+      </c>
+      <c r="AK7">
+        <v>25</v>
+      </c>
+      <c r="AL7">
+        <v>55</v>
+      </c>
+      <c r="AM7">
+        <v>160</v>
+      </c>
+      <c r="AN7">
+        <v>23</v>
+      </c>
+      <c r="AO7">
+        <v>95</v>
+      </c>
+      <c r="AP7">
+        <v>10</v>
+      </c>
+      <c r="AQ7">
+        <v>11.5</v>
+      </c>
+      <c r="AR7">
+        <v>4.6</v>
+      </c>
+      <c r="AS7">
+        <v>5.1</v>
+      </c>
+      <c r="AT7">
+        <v>7.2</v>
+      </c>
+      <c r="AU7">
+        <v>7</v>
+      </c>
+      <c r="AV7">
+        <v>15</v>
+      </c>
+      <c r="AW7">
+        <v>5</v>
+      </c>
+      <c r="AX7">
+        <v>10.5</v>
+      </c>
+      <c r="AY7">
+        <v>9.6</v>
+      </c>
+      <c r="AZ7">
+        <v>18</v>
+      </c>
+      <c r="BA7">
+        <v>5</v>
+      </c>
+      <c r="BB7">
+        <v>18.5</v>
+      </c>
+      <c r="BC7">
+        <v>20</v>
+      </c>
+      <c r="BD7">
+        <v>4.9</v>
+      </c>
+      <c r="BE7">
+        <v>5.2</v>
+      </c>
+      <c r="BF7">
+        <v>16</v>
+      </c>
+      <c r="BG7">
+        <v>5.1</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>1.01</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
+        <v>1.01</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>1.01</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.01</v>
+      </c>
+      <c r="BT7">
+        <v>1000</v>
+      </c>
+      <c r="BU7">
+        <v>1.01</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>1.01</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" t="s">
+        <v>157</v>
+      </c>
+      <c r="F8">
+        <v>1.82</v>
+      </c>
+      <c r="G8">
+        <v>2.02</v>
+      </c>
+      <c r="H8">
+        <v>4.1</v>
+      </c>
+      <c r="I8">
+        <v>5.4</v>
+      </c>
+      <c r="J8">
+        <v>3.4</v>
+      </c>
+      <c r="K8">
+        <v>3.8</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>3.1</v>
+      </c>
+      <c r="O8">
+        <v>1.39</v>
+      </c>
+      <c r="P8">
+        <v>1.77</v>
+      </c>
+      <c r="Q8">
+        <v>2.16</v>
+      </c>
+      <c r="R8">
+        <v>1.21</v>
+      </c>
+      <c r="S8">
+        <v>3.5</v>
+      </c>
+      <c r="T8">
+        <v>1.66</v>
+      </c>
+      <c r="U8">
+        <v>1.58</v>
+      </c>
+      <c r="V8">
+        <v>1.22</v>
+      </c>
+      <c r="W8">
+        <v>1.98</v>
+      </c>
+      <c r="X8">
+        <v>1000</v>
+      </c>
+      <c r="Y8">
+        <v>21</v>
+      </c>
+      <c r="Z8">
+        <v>50</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>10.5</v>
+      </c>
+      <c r="AC8">
+        <v>11.5</v>
+      </c>
+      <c r="AD8">
+        <v>29</v>
+      </c>
+      <c r="AE8">
+        <v>100</v>
+      </c>
+      <c r="AF8">
+        <v>15.5</v>
+      </c>
+      <c r="AG8">
+        <v>15</v>
+      </c>
+      <c r="AH8">
+        <v>32</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>32</v>
+      </c>
+      <c r="AK8">
+        <v>34</v>
+      </c>
+      <c r="AL8">
+        <v>65</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>2.14</v>
+      </c>
+      <c r="AQ8">
+        <v>1.95</v>
+      </c>
+      <c r="AR8">
+        <v>2.04</v>
+      </c>
+      <c r="AS8">
+        <v>2.14</v>
+      </c>
+      <c r="AT8">
+        <v>1.77</v>
+      </c>
+      <c r="AU8">
+        <v>1.8</v>
+      </c>
+      <c r="AV8">
+        <v>1.99</v>
+      </c>
+      <c r="AW8">
+        <v>2.08</v>
+      </c>
+      <c r="AX8">
+        <v>1.88</v>
+      </c>
+      <c r="AY8">
+        <v>1.87</v>
+      </c>
+      <c r="AZ8">
+        <v>2</v>
+      </c>
+      <c r="BA8">
+        <v>2.14</v>
+      </c>
+      <c r="BB8">
+        <v>2</v>
+      </c>
+      <c r="BC8">
+        <v>2</v>
+      </c>
+      <c r="BD8">
+        <v>2.06</v>
+      </c>
+      <c r="BE8">
+        <v>2.14</v>
+      </c>
+      <c r="BF8">
+        <v>2.14</v>
+      </c>
+      <c r="BG8">
+        <v>2.14</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>1.01</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>1.01</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>1.01</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>1.01</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
+        <v>1.01</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>1.01</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F9">
+        <v>2.02</v>
+      </c>
+      <c r="G9">
+        <v>2.14</v>
+      </c>
+      <c r="H9">
+        <v>3.9</v>
+      </c>
+      <c r="I9">
+        <v>4.2</v>
+      </c>
+      <c r="J9">
+        <v>3.6</v>
+      </c>
+      <c r="K9">
+        <v>3.85</v>
+      </c>
+      <c r="L9">
+        <v>1.35</v>
+      </c>
+      <c r="M9">
+        <v>1.03</v>
+      </c>
+      <c r="N9">
+        <v>3.85</v>
+      </c>
+      <c r="O9">
+        <v>1.31</v>
+      </c>
+      <c r="P9">
+        <v>2</v>
+      </c>
+      <c r="Q9">
+        <v>1.9</v>
+      </c>
+      <c r="R9">
+        <v>1.38</v>
+      </c>
+      <c r="S9">
+        <v>3.1</v>
+      </c>
+      <c r="T9">
+        <v>1.73</v>
+      </c>
+      <c r="U9">
+        <v>2.16</v>
+      </c>
+      <c r="V9">
+        <v>1.31</v>
+      </c>
+      <c r="W9">
+        <v>1.91</v>
+      </c>
+      <c r="X9">
+        <v>50</v>
+      </c>
+      <c r="Y9">
+        <v>16</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>100</v>
+      </c>
+      <c r="AB9">
+        <v>10</v>
+      </c>
+      <c r="AC9">
+        <v>8.4</v>
+      </c>
+      <c r="AD9">
+        <v>17</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>14</v>
+      </c>
+      <c r="AG9">
+        <v>19</v>
+      </c>
+      <c r="AH9">
+        <v>19</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>26</v>
+      </c>
+      <c r="AK9">
+        <v>23</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>15</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR9">
+        <v>3.3</v>
+      </c>
+      <c r="AS9">
+        <v>3.2</v>
+      </c>
+      <c r="AT9">
+        <v>8.6</v>
+      </c>
+      <c r="AU9">
+        <v>7.2</v>
+      </c>
+      <c r="AV9">
+        <v>2.78</v>
+      </c>
+      <c r="AW9">
+        <v>3.3</v>
+      </c>
+      <c r="AX9">
+        <v>11</v>
+      </c>
+      <c r="AY9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ9">
+        <v>11</v>
+      </c>
+      <c r="BA9">
+        <v>3.3</v>
+      </c>
+      <c r="BB9">
+        <v>20</v>
+      </c>
+      <c r="BC9">
+        <v>18</v>
+      </c>
+      <c r="BD9">
+        <v>3.3</v>
+      </c>
+      <c r="BE9">
+        <v>3.3</v>
+      </c>
+      <c r="BF9">
+        <v>9.4</v>
+      </c>
+      <c r="BG9">
+        <v>3.3</v>
+      </c>
+      <c r="BH9">
+        <v>4.3</v>
+      </c>
+      <c r="BI9">
+        <v>2.82</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>2.02</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.92</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>3.4</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>2.02</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.92</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.75</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.92</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.92</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.92</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" t="s">
+        <v>159</v>
+      </c>
+      <c r="F10">
+        <v>2.3</v>
+      </c>
+      <c r="G10">
+        <v>2.42</v>
+      </c>
+      <c r="H10">
+        <v>3.05</v>
+      </c>
+      <c r="I10">
+        <v>3.35</v>
+      </c>
+      <c r="J10">
+        <v>3.65</v>
+      </c>
+      <c r="K10">
+        <v>3.85</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>2.12</v>
+      </c>
+      <c r="Q10">
+        <v>1.78</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11">
+        <v>2.72</v>
+      </c>
+      <c r="G11">
+        <v>2.76</v>
+      </c>
+      <c r="H11">
+        <v>2.98</v>
+      </c>
+      <c r="I11">
+        <v>3.05</v>
+      </c>
+      <c r="J11">
+        <v>3.25</v>
+      </c>
+      <c r="K11">
+        <v>3.3</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1.09</v>
+      </c>
+      <c r="N11">
+        <v>3.1</v>
+      </c>
+      <c r="O11">
+        <v>1.44</v>
+      </c>
+      <c r="P11">
+        <v>1.69</v>
+      </c>
+      <c r="Q11">
+        <v>2.38</v>
+      </c>
+      <c r="R11">
+        <v>1.25</v>
+      </c>
+      <c r="S11">
+        <v>4.5</v>
+      </c>
+      <c r="T11">
+        <v>1.98</v>
+      </c>
+      <c r="U11">
+        <v>1.95</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>11.5</v>
+      </c>
+      <c r="Y11">
+        <v>10</v>
+      </c>
+      <c r="Z11">
+        <v>19.5</v>
+      </c>
+      <c r="AA11">
+        <v>55</v>
+      </c>
+      <c r="AB11">
+        <v>9.6</v>
+      </c>
+      <c r="AC11">
+        <v>7.6</v>
+      </c>
+      <c r="AD11">
+        <v>14</v>
+      </c>
+      <c r="AE11">
+        <v>42</v>
+      </c>
+      <c r="AF11">
+        <v>18</v>
+      </c>
+      <c r="AG11">
+        <v>13.5</v>
+      </c>
+      <c r="AH11">
+        <v>21</v>
+      </c>
+      <c r="AI11">
+        <v>60</v>
+      </c>
+      <c r="AJ11">
+        <v>48</v>
+      </c>
+      <c r="AK11">
+        <v>38</v>
+      </c>
+      <c r="AL11">
+        <v>60</v>
+      </c>
+      <c r="AM11">
+        <v>150</v>
+      </c>
+      <c r="AN11">
+        <v>36</v>
+      </c>
+      <c r="AO11">
+        <v>40</v>
+      </c>
+      <c r="AP11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR11">
+        <v>16.5</v>
+      </c>
+      <c r="AS11">
+        <v>42</v>
+      </c>
+      <c r="AT11">
+        <v>8.4</v>
+      </c>
+      <c r="AU11">
+        <v>6.6</v>
+      </c>
+      <c r="AV11">
+        <v>11.5</v>
+      </c>
+      <c r="AW11">
+        <v>32</v>
+      </c>
+      <c r="AX11">
+        <v>15</v>
+      </c>
+      <c r="AY11">
+        <v>11</v>
+      </c>
+      <c r="AZ11">
+        <v>17</v>
+      </c>
+      <c r="BA11">
+        <v>46</v>
+      </c>
+      <c r="BB11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC11">
+        <v>8.4</v>
+      </c>
+      <c r="BD11">
+        <v>44</v>
+      </c>
+      <c r="BE11">
+        <v>9.6</v>
+      </c>
+      <c r="BF11">
+        <v>28</v>
+      </c>
+      <c r="BG11">
+        <v>30</v>
+      </c>
+      <c r="BH11">
+        <v>3</v>
+      </c>
+      <c r="BI11">
+        <v>2.7</v>
+      </c>
+      <c r="BJ11">
+        <v>10.5</v>
+      </c>
+      <c r="BK11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.01</v>
+      </c>
+      <c r="BN11">
+        <v>5.7</v>
+      </c>
+      <c r="BO11">
+        <v>4.9</v>
+      </c>
+      <c r="BP11">
+        <v>25</v>
+      </c>
+      <c r="BQ11">
+        <v>17.5</v>
+      </c>
+      <c r="BR11">
+        <v>42</v>
+      </c>
+      <c r="BS11">
+        <v>30</v>
+      </c>
+      <c r="BT11">
+        <v>6</v>
+      </c>
+      <c r="BU11">
+        <v>5.1</v>
+      </c>
+      <c r="BV11">
+        <v>26</v>
+      </c>
+      <c r="BW11">
+        <v>19</v>
+      </c>
+      <c r="BX11">
+        <v>44</v>
+      </c>
+      <c r="BY11">
+        <v>32</v>
+      </c>
+      <c r="BZ11">
+        <v>40</v>
+      </c>
+      <c r="CA11">
+        <v>29</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" t="s">
+        <v>161</v>
+      </c>
+      <c r="F12">
+        <v>1.25</v>
+      </c>
+      <c r="G12">
+        <v>1000</v>
+      </c>
+      <c r="H12">
+        <v>2.1</v>
+      </c>
+      <c r="I12">
+        <v>1000</v>
+      </c>
+      <c r="J12">
+        <v>1.12</v>
+      </c>
+      <c r="K12">
+        <v>950</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1.01</v>
+      </c>
+      <c r="Q12">
+        <v>1.01</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" t="s">
+        <v>162</v>
+      </c>
+      <c r="F13">
+        <v>1.2</v>
+      </c>
+      <c r="G13">
+        <v>1000</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <v>1000</v>
+      </c>
+      <c r="J13">
+        <v>1.12</v>
+      </c>
+      <c r="K13">
+        <v>950</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1.01</v>
+      </c>
+      <c r="Q13">
+        <v>1.01</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F14">
+        <v>1.13</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
+        <v>1000</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14">
+        <v>950</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1.01</v>
+      </c>
+      <c r="Q14">
+        <v>1.01</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" t="s">
+        <v>164</v>
+      </c>
+      <c r="F15">
+        <v>1.19</v>
+      </c>
+      <c r="G15">
+        <v>110</v>
+      </c>
+      <c r="H15">
+        <v>1.19</v>
+      </c>
+      <c r="I15">
+        <v>110</v>
+      </c>
+      <c r="J15">
+        <v>1.39</v>
+      </c>
+      <c r="K15">
+        <v>950</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>1.05</v>
+      </c>
+      <c r="O15">
+        <v>1.02</v>
+      </c>
+      <c r="P15">
+        <v>1.05</v>
+      </c>
+      <c r="Q15">
+        <v>1.02</v>
+      </c>
+      <c r="R15">
+        <v>1.05</v>
+      </c>
+      <c r="S15">
+        <v>1.03</v>
+      </c>
+      <c r="T15">
+        <v>1.01</v>
+      </c>
+      <c r="U15">
+        <v>1.01</v>
+      </c>
+      <c r="V15">
+        <v>1.16</v>
+      </c>
+      <c r="W15">
+        <v>1.16</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>1000</v>
+      </c>
+      <c r="Z15">
+        <v>1000</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>1000</v>
+      </c>
+      <c r="AC15">
+        <v>1000</v>
+      </c>
+      <c r="AD15">
+        <v>1000</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>1000</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.03</v>
+      </c>
+      <c r="AQ15">
+        <v>1.03</v>
+      </c>
+      <c r="AR15">
+        <v>1.03</v>
+      </c>
+      <c r="AS15">
+        <v>1.03</v>
+      </c>
+      <c r="AT15">
+        <v>1.03</v>
+      </c>
+      <c r="AU15">
+        <v>1.03</v>
+      </c>
+      <c r="AV15">
+        <v>1.03</v>
+      </c>
+      <c r="AW15">
+        <v>1.03</v>
+      </c>
+      <c r="AX15">
+        <v>1.03</v>
+      </c>
+      <c r="AY15">
+        <v>1.03</v>
+      </c>
+      <c r="AZ15">
+        <v>1.03</v>
+      </c>
+      <c r="BA15">
+        <v>1.03</v>
+      </c>
+      <c r="BB15">
+        <v>1.03</v>
+      </c>
+      <c r="BC15">
+        <v>1.03</v>
+      </c>
+      <c r="BD15">
+        <v>1.03</v>
+      </c>
+      <c r="BE15">
+        <v>1.03</v>
+      </c>
+      <c r="BF15">
+        <v>1.01</v>
+      </c>
+      <c r="BG15">
+        <v>1.01</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.01</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.01</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.01</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.01</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.01</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.01</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.01</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
+        <v>1.01</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" t="s">
+        <v>126</v>
+      </c>
+      <c r="E16" t="s">
+        <v>165</v>
+      </c>
+      <c r="F16">
+        <v>1.37</v>
+      </c>
+      <c r="G16">
+        <v>2.68</v>
+      </c>
+      <c r="H16">
+        <v>1.12</v>
+      </c>
+      <c r="I16">
+        <v>3.85</v>
+      </c>
+      <c r="J16">
+        <v>3.05</v>
+      </c>
+      <c r="K16">
+        <v>4.1</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>1.12</v>
+      </c>
+      <c r="Q16">
+        <v>1.98</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" t="s">
+        <v>166</v>
+      </c>
+      <c r="F17">
+        <v>1.55</v>
+      </c>
+      <c r="G17">
+        <v>1.74</v>
+      </c>
+      <c r="H17">
+        <v>4.7</v>
+      </c>
+      <c r="I17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J17">
+        <v>4.3</v>
+      </c>
+      <c r="K17">
+        <v>6.2</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>2.68</v>
+      </c>
+      <c r="Q17">
+        <v>1.32</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" t="s">
+        <v>167</v>
+      </c>
+      <c r="F18">
+        <v>1.18</v>
+      </c>
+      <c r="G18">
+        <v>730</v>
+      </c>
+      <c r="H18">
+        <v>1.18</v>
+      </c>
+      <c r="I18">
+        <v>720</v>
+      </c>
+      <c r="J18">
+        <v>1.36</v>
+      </c>
+      <c r="K18">
+        <v>950</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.01</v>
+      </c>
+      <c r="N18">
+        <v>1.05</v>
+      </c>
+      <c r="O18">
+        <v>1.02</v>
+      </c>
+      <c r="P18">
+        <v>1.05</v>
+      </c>
+      <c r="Q18">
+        <v>1.02</v>
+      </c>
+      <c r="R18">
+        <v>1.05</v>
+      </c>
+      <c r="S18">
+        <v>1.03</v>
+      </c>
+      <c r="T18">
+        <v>1.01</v>
+      </c>
+      <c r="U18">
+        <v>1.01</v>
+      </c>
+      <c r="V18">
+        <v>1.15</v>
+      </c>
+      <c r="W18">
+        <v>1.16</v>
+      </c>
+      <c r="X18">
+        <v>1000</v>
+      </c>
+      <c r="Y18">
+        <v>1000</v>
+      </c>
+      <c r="Z18">
+        <v>1000</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>1000</v>
+      </c>
+      <c r="AC18">
+        <v>1000</v>
+      </c>
+      <c r="AD18">
+        <v>1000</v>
+      </c>
+      <c r="AE18">
+        <v>1000</v>
+      </c>
+      <c r="AF18">
+        <v>1000</v>
+      </c>
+      <c r="AG18">
+        <v>1000</v>
+      </c>
+      <c r="AH18">
+        <v>1000</v>
+      </c>
+      <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>1000</v>
+      </c>
+      <c r="AK18">
+        <v>1000</v>
+      </c>
+      <c r="AL18">
+        <v>1000</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>1000</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>1.03</v>
+      </c>
+      <c r="AQ18">
+        <v>1.03</v>
+      </c>
+      <c r="AR18">
+        <v>1.03</v>
+      </c>
+      <c r="AS18">
+        <v>1.03</v>
+      </c>
+      <c r="AT18">
+        <v>1.03</v>
+      </c>
+      <c r="AU18">
+        <v>1.03</v>
+      </c>
+      <c r="AV18">
+        <v>1.03</v>
+      </c>
+      <c r="AW18">
+        <v>1.03</v>
+      </c>
+      <c r="AX18">
+        <v>1.03</v>
+      </c>
+      <c r="AY18">
+        <v>1.03</v>
+      </c>
+      <c r="AZ18">
+        <v>1.03</v>
+      </c>
+      <c r="BA18">
+        <v>1.03</v>
+      </c>
+      <c r="BB18">
+        <v>1.03</v>
+      </c>
+      <c r="BC18">
+        <v>1.03</v>
+      </c>
+      <c r="BD18">
+        <v>1.03</v>
+      </c>
+      <c r="BE18">
+        <v>1.03</v>
+      </c>
+      <c r="BF18">
+        <v>1.01</v>
+      </c>
+      <c r="BG18">
+        <v>1.01</v>
+      </c>
+      <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>1.01</v>
+      </c>
+      <c r="BJ18">
+        <v>1000</v>
+      </c>
+      <c r="BK18">
+        <v>1.01</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.01</v>
+      </c>
+      <c r="BN18">
+        <v>1000</v>
+      </c>
+      <c r="BO18">
+        <v>1.01</v>
+      </c>
+      <c r="BP18">
+        <v>1000</v>
+      </c>
+      <c r="BQ18">
+        <v>1.01</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
+        <v>1.01</v>
+      </c>
+      <c r="BT18">
+        <v>1000</v>
+      </c>
+      <c r="BU18">
+        <v>1.01</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>1.01</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>1.01</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" t="s">
+        <v>168</v>
+      </c>
+      <c r="F19">
+        <v>2.4</v>
+      </c>
+      <c r="G19">
+        <v>2.42</v>
+      </c>
+      <c r="H19">
+        <v>3.6</v>
+      </c>
+      <c r="I19">
+        <v>3.7</v>
+      </c>
+      <c r="J19">
+        <v>3.15</v>
+      </c>
+      <c r="K19">
+        <v>3.2</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>1.11</v>
+      </c>
+      <c r="N19">
+        <v>2.76</v>
+      </c>
+      <c r="O19">
+        <v>1.49</v>
+      </c>
+      <c r="P19">
+        <v>1.6</v>
+      </c>
+      <c r="Q19">
+        <v>2.5</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>2.02</v>
+      </c>
+      <c r="U19">
+        <v>1.84</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>9.6</v>
+      </c>
+      <c r="Y19">
+        <v>11</v>
+      </c>
+      <c r="Z19">
+        <v>25</v>
+      </c>
+      <c r="AA19">
+        <v>85</v>
+      </c>
+      <c r="AB19">
+        <v>8</v>
+      </c>
+      <c r="AC19">
+        <v>7.4</v>
+      </c>
+      <c r="AD19">
+        <v>16</v>
+      </c>
+      <c r="AE19">
+        <v>65</v>
+      </c>
+      <c r="AF19">
+        <v>14.5</v>
+      </c>
+      <c r="AG19">
+        <v>12.5</v>
+      </c>
+      <c r="AH19">
+        <v>25</v>
+      </c>
+      <c r="AI19">
+        <v>85</v>
+      </c>
+      <c r="AJ19">
+        <v>42</v>
+      </c>
+      <c r="AK19">
+        <v>38</v>
+      </c>
+      <c r="AL19">
+        <v>65</v>
+      </c>
+      <c r="AM19">
+        <v>180</v>
+      </c>
+      <c r="AN19">
+        <v>36</v>
+      </c>
+      <c r="AO19">
+        <v>75</v>
+      </c>
+      <c r="AP19">
+        <v>8.4</v>
+      </c>
+      <c r="AQ19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR19">
+        <v>20</v>
+      </c>
+      <c r="AS19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT19">
+        <v>7</v>
+      </c>
+      <c r="AU19">
+        <v>6.6</v>
+      </c>
+      <c r="AV19">
+        <v>13.5</v>
+      </c>
+      <c r="AW19">
+        <v>44</v>
+      </c>
+      <c r="AX19">
+        <v>12</v>
+      </c>
+      <c r="AY19">
+        <v>10.5</v>
+      </c>
+      <c r="AZ19">
+        <v>19</v>
+      </c>
+      <c r="BA19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB19">
+        <v>29</v>
+      </c>
+      <c r="BC19">
+        <v>27</v>
+      </c>
+      <c r="BD19">
+        <v>44</v>
+      </c>
+      <c r="BE19">
+        <v>10</v>
+      </c>
+      <c r="BF19">
+        <v>24</v>
+      </c>
+      <c r="BG19">
+        <v>9.6</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F20">
+        <v>2.4</v>
+      </c>
+      <c r="G20">
+        <v>2.44</v>
+      </c>
+      <c r="H20">
+        <v>3.55</v>
+      </c>
+      <c r="I20">
+        <v>3.65</v>
+      </c>
+      <c r="J20">
+        <v>3.2</v>
+      </c>
+      <c r="K20">
+        <v>3.3</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>1.61</v>
+      </c>
+      <c r="Q20">
+        <v>2.52</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>2.06</v>
+      </c>
+      <c r="U20">
+        <v>1.85</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>9.6</v>
+      </c>
+      <c r="Y20">
+        <v>10.5</v>
+      </c>
+      <c r="Z20">
+        <v>28</v>
+      </c>
+      <c r="AA20">
+        <v>90</v>
+      </c>
+      <c r="AB20">
+        <v>8</v>
+      </c>
+      <c r="AC20">
+        <v>7.4</v>
+      </c>
+      <c r="AD20">
+        <v>16</v>
+      </c>
+      <c r="AE20">
+        <v>65</v>
+      </c>
+      <c r="AF20">
+        <v>14</v>
+      </c>
+      <c r="AG20">
+        <v>12.5</v>
+      </c>
+      <c r="AH20">
+        <v>24</v>
+      </c>
+      <c r="AI20">
+        <v>80</v>
+      </c>
+      <c r="AJ20">
+        <v>36</v>
+      </c>
+      <c r="AK20">
+        <v>38</v>
+      </c>
+      <c r="AL20">
+        <v>65</v>
+      </c>
+      <c r="AM20">
+        <v>180</v>
+      </c>
+      <c r="AN20">
+        <v>32</v>
+      </c>
+      <c r="AO20">
+        <v>85</v>
+      </c>
+      <c r="AP20">
+        <v>8.6</v>
+      </c>
+      <c r="AQ20">
+        <v>9</v>
+      </c>
+      <c r="AR20">
+        <v>21</v>
+      </c>
+      <c r="AS20">
+        <v>10</v>
+      </c>
+      <c r="AT20">
+        <v>7.2</v>
+      </c>
+      <c r="AU20">
+        <v>6.8</v>
+      </c>
+      <c r="AV20">
+        <v>13.5</v>
+      </c>
+      <c r="AW20">
+        <v>9.6</v>
+      </c>
+      <c r="AX20">
+        <v>12</v>
+      </c>
+      <c r="AY20">
+        <v>10.5</v>
+      </c>
+      <c r="AZ20">
+        <v>20</v>
+      </c>
+      <c r="BA20">
+        <v>10</v>
+      </c>
+      <c r="BB20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC20">
+        <v>9</v>
+      </c>
+      <c r="BD20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE20">
+        <v>10.5</v>
+      </c>
+      <c r="BF20">
+        <v>8.6</v>
+      </c>
+      <c r="BG20">
+        <v>10</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+      <c r="BI20">
+        <v>0</v>
+      </c>
+      <c r="BJ20">
+        <v>0</v>
+      </c>
+      <c r="BK20">
+        <v>0</v>
+      </c>
+      <c r="BL20">
+        <v>0</v>
+      </c>
+      <c r="BM20">
+        <v>0</v>
+      </c>
+      <c r="BN20">
+        <v>0</v>
+      </c>
+      <c r="BO20">
+        <v>0</v>
+      </c>
+      <c r="BP20">
+        <v>0</v>
+      </c>
+      <c r="BQ20">
+        <v>0</v>
+      </c>
+      <c r="BR20">
+        <v>0</v>
+      </c>
+      <c r="BS20">
+        <v>0</v>
+      </c>
+      <c r="BT20">
+        <v>0</v>
+      </c>
+      <c r="BU20">
+        <v>0</v>
+      </c>
+      <c r="BV20">
+        <v>0</v>
+      </c>
+      <c r="BW20">
+        <v>0</v>
+      </c>
+      <c r="BX20">
+        <v>0</v>
+      </c>
+      <c r="BY20">
+        <v>0</v>
+      </c>
+      <c r="BZ20">
+        <v>0</v>
+      </c>
+      <c r="CA20">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" t="s">
+        <v>170</v>
+      </c>
+      <c r="F21">
+        <v>1.3</v>
+      </c>
+      <c r="G21">
+        <v>1.33</v>
+      </c>
+      <c r="H21">
+        <v>12</v>
+      </c>
+      <c r="I21">
+        <v>15</v>
+      </c>
+      <c r="J21">
+        <v>5.9</v>
+      </c>
+      <c r="K21">
+        <v>6.2</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>2.26</v>
+      </c>
+      <c r="Q21">
+        <v>1.71</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>2.22</v>
+      </c>
+      <c r="U21">
+        <v>1.68</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>22</v>
+      </c>
+      <c r="Y21">
+        <v>38</v>
+      </c>
+      <c r="Z21">
+        <v>140</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>9.6</v>
+      </c>
+      <c r="AC21">
+        <v>14</v>
+      </c>
+      <c r="AD21">
+        <v>48</v>
+      </c>
+      <c r="AE21">
+        <v>290</v>
+      </c>
+      <c r="AF21">
+        <v>7.6</v>
+      </c>
+      <c r="AG21">
+        <v>12</v>
+      </c>
+      <c r="AH21">
+        <v>38</v>
+      </c>
+      <c r="AI21">
+        <v>210</v>
+      </c>
+      <c r="AJ21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK21">
+        <v>15.5</v>
+      </c>
+      <c r="AL21">
+        <v>50</v>
+      </c>
+      <c r="AM21">
+        <v>270</v>
+      </c>
+      <c r="AN21">
+        <v>5.1</v>
+      </c>
+      <c r="AO21">
+        <v>450</v>
+      </c>
+      <c r="AP21">
+        <v>18</v>
+      </c>
+      <c r="AQ21">
+        <v>27</v>
+      </c>
+      <c r="AR21">
+        <v>10.5</v>
+      </c>
+      <c r="AS21">
+        <v>11.5</v>
+      </c>
+      <c r="AT21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU21">
+        <v>12</v>
+      </c>
+      <c r="AV21">
+        <v>36</v>
+      </c>
+      <c r="AW21">
+        <v>10.5</v>
+      </c>
+      <c r="AX21">
+        <v>6.4</v>
+      </c>
+      <c r="AY21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA21">
+        <v>10.5</v>
+      </c>
+      <c r="BB21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC21">
+        <v>13</v>
+      </c>
+      <c r="BD21">
+        <v>38</v>
+      </c>
+      <c r="BE21">
+        <v>10.5</v>
+      </c>
+      <c r="BF21">
+        <v>4.1</v>
+      </c>
+      <c r="BG21">
+        <v>11</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>0</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>0</v>
+      </c>
+      <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
+        <v>0</v>
+      </c>
+      <c r="BP21">
+        <v>0</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21">
+        <v>0</v>
+      </c>
+      <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
+        <v>0</v>
+      </c>
+      <c r="BU21">
+        <v>0</v>
+      </c>
+      <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
+        <v>0</v>
+      </c>
+      <c r="BX21">
+        <v>0</v>
+      </c>
+      <c r="BY21">
+        <v>0</v>
+      </c>
+      <c r="BZ21">
+        <v>0</v>
+      </c>
+      <c r="CA21">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" t="s">
+        <v>171</v>
+      </c>
+      <c r="F22">
+        <v>42</v>
+      </c>
+      <c r="G22">
+        <v>44</v>
+      </c>
+      <c r="H22">
+        <v>1.11</v>
+      </c>
+      <c r="I22">
+        <v>1.12</v>
+      </c>
+      <c r="J22">
+        <v>11.5</v>
+      </c>
+      <c r="K22">
+        <v>13</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>2.66</v>
+      </c>
+      <c r="Q22">
+        <v>1.53</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>3.75</v>
+      </c>
+      <c r="U22">
+        <v>1.31</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>40</v>
+      </c>
+      <c r="Y22">
+        <v>9.6</v>
+      </c>
+      <c r="Z22">
+        <v>6.8</v>
+      </c>
+      <c r="AA22">
+        <v>6.6</v>
+      </c>
+      <c r="AB22">
+        <v>110</v>
+      </c>
+      <c r="AC22">
+        <v>38</v>
+      </c>
+      <c r="AD22">
+        <v>22</v>
+      </c>
+      <c r="AE22">
+        <v>24</v>
+      </c>
+      <c r="AF22">
+        <v>1000</v>
+      </c>
+      <c r="AG22">
+        <v>190</v>
+      </c>
+      <c r="AH22">
+        <v>130</v>
+      </c>
+      <c r="AI22">
+        <v>130</v>
+      </c>
+      <c r="AJ22">
+        <v>1000</v>
+      </c>
+      <c r="AK22">
+        <v>1000</v>
+      </c>
+      <c r="AL22">
+        <v>1000</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>1000</v>
+      </c>
+      <c r="AO22">
+        <v>3.1</v>
+      </c>
+      <c r="AP22">
+        <v>7.8</v>
+      </c>
+      <c r="AQ22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR22">
+        <v>5.7</v>
+      </c>
+      <c r="AS22">
+        <v>5.5</v>
+      </c>
+      <c r="AT22">
+        <v>8.6</v>
+      </c>
+      <c r="AU22">
+        <v>7.8</v>
+      </c>
+      <c r="AV22">
+        <v>17.5</v>
+      </c>
+      <c r="AW22">
+        <v>18</v>
+      </c>
+      <c r="AX22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ22">
+        <v>8.6</v>
+      </c>
+      <c r="BA22">
+        <v>8.6</v>
+      </c>
+      <c r="BB22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG22">
+        <v>2.78</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" t="s">
+        <v>133</v>
+      </c>
+      <c r="E23" t="s">
+        <v>172</v>
+      </c>
+      <c r="F23">
+        <v>1.1</v>
+      </c>
+      <c r="G23">
+        <v>1000</v>
+      </c>
+      <c r="H23">
+        <v>1.1</v>
+      </c>
+      <c r="I23">
+        <v>1000</v>
+      </c>
+      <c r="J23">
+        <v>1.12</v>
+      </c>
+      <c r="K23">
+        <v>950</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>1.01</v>
+      </c>
+      <c r="Q23">
+        <v>1.01</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
+      <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
+        <v>0</v>
+      </c>
+      <c r="BU23">
+        <v>0</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+      <c r="BX23">
+        <v>0</v>
+      </c>
+      <c r="BY23">
+        <v>0</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" t="s">
+        <v>173</v>
+      </c>
+      <c r="F24">
+        <v>3.45</v>
+      </c>
+      <c r="G24">
+        <v>3.7</v>
+      </c>
+      <c r="H24">
+        <v>2.22</v>
+      </c>
+      <c r="I24">
+        <v>2.3</v>
+      </c>
+      <c r="J24">
+        <v>3.4</v>
+      </c>
+      <c r="K24">
+        <v>3.65</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>1.82</v>
+      </c>
+      <c r="Q24">
+        <v>2.08</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
+      <c r="AV24">
+        <v>0</v>
+      </c>
+      <c r="AW24">
+        <v>0</v>
+      </c>
+      <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
+        <v>0</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>0</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24">
+        <v>0</v>
+      </c>
+      <c r="BE24">
+        <v>0</v>
+      </c>
+      <c r="BF24">
+        <v>0</v>
+      </c>
+      <c r="BG24">
+        <v>0</v>
+      </c>
+      <c r="BH24">
+        <v>0</v>
+      </c>
+      <c r="BI24">
+        <v>0</v>
+      </c>
+      <c r="BJ24">
+        <v>0</v>
+      </c>
+      <c r="BK24">
+        <v>0</v>
+      </c>
+      <c r="BL24">
+        <v>0</v>
+      </c>
+      <c r="BM24">
+        <v>0</v>
+      </c>
+      <c r="BN24">
+        <v>0</v>
+      </c>
+      <c r="BO24">
+        <v>0</v>
+      </c>
+      <c r="BP24">
+        <v>0</v>
+      </c>
+      <c r="BQ24">
+        <v>0</v>
+      </c>
+      <c r="BR24">
+        <v>0</v>
+      </c>
+      <c r="BS24">
+        <v>0</v>
+      </c>
+      <c r="BT24">
+        <v>0</v>
+      </c>
+      <c r="BU24">
+        <v>0</v>
+      </c>
+      <c r="BV24">
+        <v>0</v>
+      </c>
+      <c r="BW24">
+        <v>0</v>
+      </c>
+      <c r="BX24">
+        <v>0</v>
+      </c>
+      <c r="BY24">
+        <v>0</v>
+      </c>
+      <c r="BZ24">
+        <v>0</v>
+      </c>
+      <c r="CA24">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E25" t="s">
+        <v>174</v>
+      </c>
+      <c r="F25">
+        <v>1.92</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>4.7</v>
+      </c>
+      <c r="I25">
+        <v>5.4</v>
+      </c>
+      <c r="J25">
+        <v>3.3</v>
+      </c>
+      <c r="K25">
+        <v>3.55</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>1.58</v>
+      </c>
+      <c r="Q25">
+        <v>2.44</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25">
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <v>0</v>
+      </c>
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>0</v>
+      </c>
+      <c r="BB25">
+        <v>0</v>
+      </c>
+      <c r="BC25">
+        <v>0</v>
+      </c>
+      <c r="BD25">
+        <v>0</v>
+      </c>
+      <c r="BE25">
+        <v>0</v>
+      </c>
+      <c r="BF25">
+        <v>0</v>
+      </c>
+      <c r="BG25">
+        <v>0</v>
+      </c>
+      <c r="BH25">
+        <v>0</v>
+      </c>
+      <c r="BI25">
+        <v>0</v>
+      </c>
+      <c r="BJ25">
+        <v>0</v>
+      </c>
+      <c r="BK25">
+        <v>0</v>
+      </c>
+      <c r="BL25">
+        <v>0</v>
+      </c>
+      <c r="BM25">
+        <v>0</v>
+      </c>
+      <c r="BN25">
+        <v>0</v>
+      </c>
+      <c r="BO25">
+        <v>0</v>
+      </c>
+      <c r="BP25">
+        <v>0</v>
+      </c>
+      <c r="BQ25">
+        <v>0</v>
+      </c>
+      <c r="BR25">
+        <v>0</v>
+      </c>
+      <c r="BS25">
+        <v>0</v>
+      </c>
+      <c r="BT25">
+        <v>0</v>
+      </c>
+      <c r="BU25">
+        <v>0</v>
+      </c>
+      <c r="BV25">
+        <v>0</v>
+      </c>
+      <c r="BW25">
+        <v>0</v>
+      </c>
+      <c r="BX25">
+        <v>0</v>
+      </c>
+      <c r="BY25">
+        <v>0</v>
+      </c>
+      <c r="BZ25">
+        <v>0</v>
+      </c>
+      <c r="CA25">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" t="s">
+        <v>175</v>
+      </c>
+      <c r="F26">
+        <v>1.94</v>
+      </c>
+      <c r="G26">
+        <v>2.12</v>
+      </c>
+      <c r="H26">
+        <v>3.5</v>
+      </c>
+      <c r="I26">
+        <v>4</v>
+      </c>
+      <c r="J26">
+        <v>3.85</v>
+      </c>
+      <c r="K26">
+        <v>4.5</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>1.04</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>2.32</v>
+      </c>
+      <c r="Q26">
+        <v>1.63</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
+        <v>0</v>
+      </c>
+      <c r="AP26">
+        <v>0</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26">
+        <v>0</v>
+      </c>
+      <c r="AV26">
+        <v>0</v>
+      </c>
+      <c r="AW26">
+        <v>0</v>
+      </c>
+      <c r="AX26">
+        <v>0</v>
+      </c>
+      <c r="AY26">
+        <v>0</v>
+      </c>
+      <c r="AZ26">
+        <v>0</v>
+      </c>
+      <c r="BA26">
+        <v>0</v>
+      </c>
+      <c r="BB26">
+        <v>0</v>
+      </c>
+      <c r="BC26">
+        <v>0</v>
+      </c>
+      <c r="BD26">
+        <v>0</v>
+      </c>
+      <c r="BE26">
+        <v>0</v>
+      </c>
+      <c r="BF26">
+        <v>0</v>
+      </c>
+      <c r="BG26">
+        <v>0</v>
+      </c>
+      <c r="BH26">
+        <v>0</v>
+      </c>
+      <c r="BI26">
+        <v>0</v>
+      </c>
+      <c r="BJ26">
+        <v>0</v>
+      </c>
+      <c r="BK26">
+        <v>0</v>
+      </c>
+      <c r="BL26">
+        <v>0</v>
+      </c>
+      <c r="BM26">
+        <v>0</v>
+      </c>
+      <c r="BN26">
+        <v>0</v>
+      </c>
+      <c r="BO26">
+        <v>0</v>
+      </c>
+      <c r="BP26">
+        <v>0</v>
+      </c>
+      <c r="BQ26">
+        <v>0</v>
+      </c>
+      <c r="BR26">
+        <v>0</v>
+      </c>
+      <c r="BS26">
+        <v>0</v>
+      </c>
+      <c r="BT26">
+        <v>0</v>
+      </c>
+      <c r="BU26">
+        <v>0</v>
+      </c>
+      <c r="BV26">
+        <v>0</v>
+      </c>
+      <c r="BW26">
+        <v>0</v>
+      </c>
+      <c r="BX26">
+        <v>0</v>
+      </c>
+      <c r="BY26">
+        <v>0</v>
+      </c>
+      <c r="BZ26">
+        <v>0</v>
+      </c>
+      <c r="CA26">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27" t="s">
+        <v>176</v>
+      </c>
+      <c r="F27">
+        <v>1.78</v>
+      </c>
+      <c r="G27">
+        <v>1.84</v>
+      </c>
+      <c r="H27">
+        <v>3.85</v>
+      </c>
+      <c r="I27">
+        <v>4.2</v>
+      </c>
+      <c r="J27">
+        <v>4.8</v>
+      </c>
+      <c r="K27">
+        <v>5.5</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>1.01</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>4</v>
+      </c>
+      <c r="Q27">
+        <v>1.29</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+      <c r="AN27">
+        <v>0</v>
+      </c>
+      <c r="AO27">
+        <v>0</v>
+      </c>
+      <c r="AP27">
+        <v>0</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27">
+        <v>0</v>
+      </c>
+      <c r="AV27">
+        <v>0</v>
+      </c>
+      <c r="AW27">
+        <v>0</v>
+      </c>
+      <c r="AX27">
+        <v>0</v>
+      </c>
+      <c r="AY27">
+        <v>0</v>
+      </c>
+      <c r="AZ27">
+        <v>0</v>
+      </c>
+      <c r="BA27">
+        <v>0</v>
+      </c>
+      <c r="BB27">
+        <v>0</v>
+      </c>
+      <c r="BC27">
+        <v>0</v>
+      </c>
+      <c r="BD27">
+        <v>0</v>
+      </c>
+      <c r="BE27">
+        <v>0</v>
+      </c>
+      <c r="BF27">
+        <v>0</v>
+      </c>
+      <c r="BG27">
+        <v>0</v>
+      </c>
+      <c r="BH27">
+        <v>0</v>
+      </c>
+      <c r="BI27">
+        <v>0</v>
+      </c>
+      <c r="BJ27">
+        <v>0</v>
+      </c>
+      <c r="BK27">
+        <v>0</v>
+      </c>
+      <c r="BL27">
+        <v>0</v>
+      </c>
+      <c r="BM27">
+        <v>0</v>
+      </c>
+      <c r="BN27">
+        <v>0</v>
+      </c>
+      <c r="BO27">
+        <v>0</v>
+      </c>
+      <c r="BP27">
+        <v>0</v>
+      </c>
+      <c r="BQ27">
+        <v>0</v>
+      </c>
+      <c r="BR27">
+        <v>0</v>
+      </c>
+      <c r="BS27">
+        <v>0</v>
+      </c>
+      <c r="BT27">
+        <v>0</v>
+      </c>
+      <c r="BU27">
+        <v>0</v>
+      </c>
+      <c r="BV27">
+        <v>0</v>
+      </c>
+      <c r="BW27">
+        <v>0</v>
+      </c>
+      <c r="BX27">
+        <v>0</v>
+      </c>
+      <c r="BY27">
+        <v>0</v>
+      </c>
+      <c r="BZ27">
+        <v>0</v>
+      </c>
+      <c r="CA27">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F28">
+        <v>1.27</v>
+      </c>
+      <c r="G28">
+        <v>1.48</v>
+      </c>
+      <c r="H28">
+        <v>6.8</v>
+      </c>
+      <c r="I28">
+        <v>120</v>
+      </c>
+      <c r="J28">
+        <v>4.9</v>
+      </c>
+      <c r="K28">
+        <v>10</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>1.01</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>2.74</v>
+      </c>
+      <c r="Q28">
+        <v>1.3</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28">
+        <v>0</v>
+      </c>
+      <c r="AV28">
+        <v>0</v>
+      </c>
+      <c r="AW28">
+        <v>0</v>
+      </c>
+      <c r="AX28">
+        <v>0</v>
+      </c>
+      <c r="AY28">
+        <v>0</v>
+      </c>
+      <c r="AZ28">
+        <v>0</v>
+      </c>
+      <c r="BA28">
+        <v>0</v>
+      </c>
+      <c r="BB28">
+        <v>0</v>
+      </c>
+      <c r="BC28">
+        <v>0</v>
+      </c>
+      <c r="BD28">
+        <v>0</v>
+      </c>
+      <c r="BE28">
+        <v>0</v>
+      </c>
+      <c r="BF28">
+        <v>0</v>
+      </c>
+      <c r="BG28">
+        <v>0</v>
+      </c>
+      <c r="BH28">
+        <v>0</v>
+      </c>
+      <c r="BI28">
+        <v>0</v>
+      </c>
+      <c r="BJ28">
+        <v>0</v>
+      </c>
+      <c r="BK28">
+        <v>0</v>
+      </c>
+      <c r="BL28">
+        <v>0</v>
+      </c>
+      <c r="BM28">
+        <v>0</v>
+      </c>
+      <c r="BN28">
+        <v>0</v>
+      </c>
+      <c r="BO28">
+        <v>0</v>
+      </c>
+      <c r="BP28">
+        <v>0</v>
+      </c>
+      <c r="BQ28">
+        <v>0</v>
+      </c>
+      <c r="BR28">
+        <v>0</v>
+      </c>
+      <c r="BS28">
+        <v>0</v>
+      </c>
+      <c r="BT28">
+        <v>0</v>
+      </c>
+      <c r="BU28">
+        <v>0</v>
+      </c>
+      <c r="BV28">
+        <v>0</v>
+      </c>
+      <c r="BW28">
+        <v>0</v>
+      </c>
+      <c r="BX28">
+        <v>0</v>
+      </c>
+      <c r="BY28">
+        <v>0</v>
+      </c>
+      <c r="BZ28">
+        <v>0</v>
+      </c>
+      <c r="CA28">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" t="s">
+        <v>139</v>
+      </c>
+      <c r="E29" t="s">
+        <v>178</v>
+      </c>
+      <c r="F29">
+        <v>1.53</v>
+      </c>
+      <c r="G29">
+        <v>1.66</v>
+      </c>
+      <c r="H29">
+        <v>5</v>
+      </c>
+      <c r="I29">
+        <v>6.6</v>
+      </c>
+      <c r="J29">
+        <v>4.8</v>
+      </c>
+      <c r="K29">
+        <v>5.8</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>1.02</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>3.15</v>
+      </c>
+      <c r="Q29">
+        <v>1.38</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29">
+        <v>0</v>
+      </c>
+      <c r="AV29">
+        <v>0</v>
+      </c>
+      <c r="AW29">
+        <v>0</v>
+      </c>
+      <c r="AX29">
+        <v>0</v>
+      </c>
+      <c r="AY29">
+        <v>0</v>
+      </c>
+      <c r="AZ29">
+        <v>0</v>
+      </c>
+      <c r="BA29">
+        <v>0</v>
+      </c>
+      <c r="BB29">
+        <v>0</v>
+      </c>
+      <c r="BC29">
+        <v>0</v>
+      </c>
+      <c r="BD29">
+        <v>0</v>
+      </c>
+      <c r="BE29">
+        <v>0</v>
+      </c>
+      <c r="BF29">
+        <v>0</v>
+      </c>
+      <c r="BG29">
+        <v>0</v>
+      </c>
+      <c r="BH29">
+        <v>0</v>
+      </c>
+      <c r="BI29">
+        <v>0</v>
+      </c>
+      <c r="BJ29">
+        <v>0</v>
+      </c>
+      <c r="BK29">
+        <v>0</v>
+      </c>
+      <c r="BL29">
+        <v>0</v>
+      </c>
+      <c r="BM29">
+        <v>0</v>
+      </c>
+      <c r="BN29">
+        <v>0</v>
+      </c>
+      <c r="BO29">
+        <v>0</v>
+      </c>
+      <c r="BP29">
+        <v>0</v>
+      </c>
+      <c r="BQ29">
+        <v>0</v>
+      </c>
+      <c r="BR29">
+        <v>0</v>
+      </c>
+      <c r="BS29">
+        <v>0</v>
+      </c>
+      <c r="BT29">
+        <v>0</v>
+      </c>
+      <c r="BU29">
+        <v>0</v>
+      </c>
+      <c r="BV29">
+        <v>0</v>
+      </c>
+      <c r="BW29">
+        <v>0</v>
+      </c>
+      <c r="BX29">
+        <v>0</v>
+      </c>
+      <c r="BY29">
+        <v>0</v>
+      </c>
+      <c r="BZ29">
+        <v>0</v>
+      </c>
+      <c r="CA29">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30" t="s">
+        <v>140</v>
+      </c>
+      <c r="E30" t="s">
+        <v>179</v>
+      </c>
+      <c r="F30">
+        <v>1.1</v>
+      </c>
+      <c r="G30">
+        <v>1000</v>
+      </c>
+      <c r="H30">
+        <v>1.1</v>
+      </c>
+      <c r="I30">
+        <v>1000</v>
+      </c>
+      <c r="J30">
+        <v>1.1</v>
+      </c>
+      <c r="K30">
+        <v>950</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>1.01</v>
+      </c>
+      <c r="Q30">
+        <v>1.01</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>0</v>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+      <c r="AN30">
+        <v>0</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>0</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30">
+        <v>0</v>
+      </c>
+      <c r="AV30">
+        <v>0</v>
+      </c>
+      <c r="AW30">
+        <v>0</v>
+      </c>
+      <c r="AX30">
+        <v>0</v>
+      </c>
+      <c r="AY30">
+        <v>0</v>
+      </c>
+      <c r="AZ30">
+        <v>0</v>
+      </c>
+      <c r="BA30">
+        <v>0</v>
+      </c>
+      <c r="BB30">
+        <v>0</v>
+      </c>
+      <c r="BC30">
+        <v>0</v>
+      </c>
+      <c r="BD30">
+        <v>0</v>
+      </c>
+      <c r="BE30">
+        <v>0</v>
+      </c>
+      <c r="BF30">
+        <v>0</v>
+      </c>
+      <c r="BG30">
+        <v>0</v>
+      </c>
+      <c r="BH30">
+        <v>0</v>
+      </c>
+      <c r="BI30">
+        <v>0</v>
+      </c>
+      <c r="BJ30">
+        <v>0</v>
+      </c>
+      <c r="BK30">
+        <v>0</v>
+      </c>
+      <c r="BL30">
+        <v>0</v>
+      </c>
+      <c r="BM30">
+        <v>0</v>
+      </c>
+      <c r="BN30">
+        <v>0</v>
+      </c>
+      <c r="BO30">
+        <v>0</v>
+      </c>
+      <c r="BP30">
+        <v>0</v>
+      </c>
+      <c r="BQ30">
+        <v>0</v>
+      </c>
+      <c r="BR30">
+        <v>0</v>
+      </c>
+      <c r="BS30">
+        <v>0</v>
+      </c>
+      <c r="BT30">
+        <v>0</v>
+      </c>
+      <c r="BU30">
+        <v>0</v>
+      </c>
+      <c r="BV30">
+        <v>0</v>
+      </c>
+      <c r="BW30">
+        <v>0</v>
+      </c>
+      <c r="BX30">
+        <v>0</v>
+      </c>
+      <c r="BY30">
+        <v>0</v>
+      </c>
+      <c r="BZ30">
+        <v>0</v>
+      </c>
+      <c r="CA30">
+        <v>0</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" t="s">
+        <v>180</v>
+      </c>
+      <c r="F31">
+        <v>2.46</v>
+      </c>
+      <c r="G31">
+        <v>2.92</v>
+      </c>
+      <c r="H31">
+        <v>2.62</v>
+      </c>
+      <c r="I31">
+        <v>3.15</v>
+      </c>
+      <c r="J31">
+        <v>3.5</v>
+      </c>
+      <c r="K31">
+        <v>4.8</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>1.01</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>1.1</v>
+      </c>
+      <c r="Q31">
+        <v>1.67</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+      <c r="AN31">
+        <v>0</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>0</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31">
+        <v>0</v>
+      </c>
+      <c r="AV31">
+        <v>0</v>
+      </c>
+      <c r="AW31">
+        <v>0</v>
+      </c>
+      <c r="AX31">
+        <v>0</v>
+      </c>
+      <c r="AY31">
+        <v>0</v>
+      </c>
+      <c r="AZ31">
+        <v>0</v>
+      </c>
+      <c r="BA31">
+        <v>0</v>
+      </c>
+      <c r="BB31">
+        <v>0</v>
+      </c>
+      <c r="BC31">
+        <v>0</v>
+      </c>
+      <c r="BD31">
+        <v>0</v>
+      </c>
+      <c r="BE31">
+        <v>0</v>
+      </c>
+      <c r="BF31">
+        <v>0</v>
+      </c>
+      <c r="BG31">
+        <v>0</v>
+      </c>
+      <c r="BH31">
+        <v>0</v>
+      </c>
+      <c r="BI31">
+        <v>0</v>
+      </c>
+      <c r="BJ31">
+        <v>0</v>
+      </c>
+      <c r="BK31">
+        <v>0</v>
+      </c>
+      <c r="BL31">
+        <v>0</v>
+      </c>
+      <c r="BM31">
+        <v>0</v>
+      </c>
+      <c r="BN31">
+        <v>0</v>
+      </c>
+      <c r="BO31">
+        <v>0</v>
+      </c>
+      <c r="BP31">
+        <v>0</v>
+      </c>
+      <c r="BQ31">
+        <v>0</v>
+      </c>
+      <c r="BR31">
+        <v>0</v>
+      </c>
+      <c r="BS31">
+        <v>0</v>
+      </c>
+      <c r="BT31">
+        <v>0</v>
+      </c>
+      <c r="BU31">
+        <v>0</v>
+      </c>
+      <c r="BV31">
+        <v>0</v>
+      </c>
+      <c r="BW31">
+        <v>0</v>
+      </c>
+      <c r="BX31">
+        <v>0</v>
+      </c>
+      <c r="BY31">
+        <v>0</v>
+      </c>
+      <c r="BZ31">
+        <v>0</v>
+      </c>
+      <c r="CA31">
+        <v>0</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" t="s">
+        <v>142</v>
+      </c>
+      <c r="E32" t="s">
+        <v>181</v>
+      </c>
+      <c r="F32">
+        <v>3.95</v>
+      </c>
+      <c r="G32">
+        <v>4.5</v>
+      </c>
+      <c r="H32">
+        <v>1.83</v>
+      </c>
+      <c r="I32">
+        <v>1.96</v>
+      </c>
+      <c r="J32">
+        <v>4</v>
+      </c>
+      <c r="K32">
+        <v>4.6</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>2.48</v>
+      </c>
+      <c r="Q32">
+        <v>1.58</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32">
+        <v>0</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>0</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32">
+        <v>0</v>
+      </c>
+      <c r="AV32">
+        <v>0</v>
+      </c>
+      <c r="AW32">
+        <v>0</v>
+      </c>
+      <c r="AX32">
+        <v>0</v>
+      </c>
+      <c r="AY32">
+        <v>0</v>
+      </c>
+      <c r="AZ32">
+        <v>0</v>
+      </c>
+      <c r="BA32">
+        <v>0</v>
+      </c>
+      <c r="BB32">
+        <v>0</v>
+      </c>
+      <c r="BC32">
+        <v>0</v>
+      </c>
+      <c r="BD32">
+        <v>0</v>
+      </c>
+      <c r="BE32">
+        <v>0</v>
+      </c>
+      <c r="BF32">
+        <v>0</v>
+      </c>
+      <c r="BG32">
+        <v>0</v>
+      </c>
+      <c r="BH32">
+        <v>0</v>
+      </c>
+      <c r="BI32">
+        <v>0</v>
+      </c>
+      <c r="BJ32">
+        <v>0</v>
+      </c>
+      <c r="BK32">
+        <v>0</v>
+      </c>
+      <c r="BL32">
+        <v>0</v>
+      </c>
+      <c r="BM32">
+        <v>0</v>
+      </c>
+      <c r="BN32">
+        <v>0</v>
+      </c>
+      <c r="BO32">
+        <v>0</v>
+      </c>
+      <c r="BP32">
+        <v>0</v>
+      </c>
+      <c r="BQ32">
+        <v>0</v>
+      </c>
+      <c r="BR32">
+        <v>0</v>
+      </c>
+      <c r="BS32">
+        <v>0</v>
+      </c>
+      <c r="BT32">
+        <v>0</v>
+      </c>
+      <c r="BU32">
+        <v>0</v>
+      </c>
+      <c r="BV32">
+        <v>0</v>
+      </c>
+      <c r="BW32">
+        <v>0</v>
+      </c>
+      <c r="BX32">
+        <v>0</v>
+      </c>
+      <c r="BY32">
+        <v>0</v>
+      </c>
+      <c r="BZ32">
+        <v>0</v>
+      </c>
+      <c r="CA32">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" t="s">
+        <v>143</v>
+      </c>
+      <c r="E33" t="s">
+        <v>182</v>
+      </c>
+      <c r="F33">
+        <v>1.26</v>
+      </c>
+      <c r="G33">
+        <v>1.28</v>
+      </c>
+      <c r="H33">
+        <v>15.5</v>
+      </c>
+      <c r="I33">
+        <v>18</v>
+      </c>
+      <c r="J33">
+        <v>6.2</v>
+      </c>
+      <c r="K33">
+        <v>6.6</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>2.14</v>
+      </c>
+      <c r="Q33">
+        <v>1.78</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>2.52</v>
+      </c>
+      <c r="U33">
+        <v>1.58</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>20</v>
+      </c>
+      <c r="Y33">
+        <v>42</v>
+      </c>
+      <c r="Z33">
+        <v>210</v>
+      </c>
+      <c r="AA33">
+        <v>1000</v>
+      </c>
+      <c r="AB33">
+        <v>7.6</v>
+      </c>
+      <c r="AC33">
+        <v>15</v>
+      </c>
+      <c r="AD33">
+        <v>65</v>
+      </c>
+      <c r="AE33">
+        <v>470</v>
+      </c>
+      <c r="AF33">
+        <v>6.8</v>
+      </c>
+      <c r="AG33">
+        <v>12</v>
+      </c>
+      <c r="AH33">
+        <v>46</v>
+      </c>
+      <c r="AI33">
+        <v>330</v>
+      </c>
+      <c r="AJ33">
+        <v>9</v>
+      </c>
+      <c r="AK33">
+        <v>19.5</v>
+      </c>
+      <c r="AL33">
+        <v>75</v>
+      </c>
+      <c r="AM33">
+        <v>400</v>
+      </c>
+      <c r="AN33">
+        <v>5.3</v>
+      </c>
+      <c r="AO33">
+        <v>1000</v>
+      </c>
+      <c r="AP33">
+        <v>17</v>
+      </c>
+      <c r="AQ33">
+        <v>34</v>
+      </c>
+      <c r="AR33">
+        <v>11</v>
+      </c>
+      <c r="AS33">
+        <v>12</v>
+      </c>
+      <c r="AT33">
+        <v>6.8</v>
+      </c>
+      <c r="AU33">
+        <v>13</v>
+      </c>
+      <c r="AV33">
+        <v>10</v>
+      </c>
+      <c r="AW33">
+        <v>11.5</v>
+      </c>
+      <c r="AX33">
+        <v>6</v>
+      </c>
+      <c r="AY33">
+        <v>10.5</v>
+      </c>
+      <c r="AZ33">
+        <v>38</v>
+      </c>
+      <c r="BA33">
+        <v>11.5</v>
+      </c>
+      <c r="BB33">
+        <v>7.8</v>
+      </c>
+      <c r="BC33">
+        <v>14</v>
+      </c>
+      <c r="BD33">
+        <v>10</v>
+      </c>
+      <c r="BE33">
+        <v>11.5</v>
+      </c>
+      <c r="BF33">
+        <v>4.8</v>
+      </c>
+      <c r="BG33">
+        <v>12</v>
+      </c>
+      <c r="BH33">
+        <v>0</v>
+      </c>
+      <c r="BI33">
+        <v>0</v>
+      </c>
+      <c r="BJ33">
+        <v>0</v>
+      </c>
+      <c r="BK33">
+        <v>0</v>
+      </c>
+      <c r="BL33">
+        <v>0</v>
+      </c>
+      <c r="BM33">
+        <v>0</v>
+      </c>
+      <c r="BN33">
+        <v>0</v>
+      </c>
+      <c r="BO33">
+        <v>0</v>
+      </c>
+      <c r="BP33">
+        <v>0</v>
+      </c>
+      <c r="BQ33">
+        <v>0</v>
+      </c>
+      <c r="BR33">
+        <v>0</v>
+      </c>
+      <c r="BS33">
+        <v>0</v>
+      </c>
+      <c r="BT33">
+        <v>0</v>
+      </c>
+      <c r="BU33">
+        <v>0</v>
+      </c>
+      <c r="BV33">
+        <v>0</v>
+      </c>
+      <c r="BW33">
+        <v>0</v>
+      </c>
+      <c r="BX33">
+        <v>0</v>
+      </c>
+      <c r="BY33">
+        <v>0</v>
+      </c>
+      <c r="BZ33">
+        <v>0</v>
+      </c>
+      <c r="CA33">
+        <v>0</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="34" spans="1:80">
+      <c r="A34" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" t="s">
+        <v>144</v>
+      </c>
+      <c r="E34" t="s">
+        <v>183</v>
+      </c>
+      <c r="F34">
+        <v>1.52</v>
+      </c>
+      <c r="G34">
+        <v>1.54</v>
+      </c>
+      <c r="H34">
+        <v>8</v>
+      </c>
+      <c r="I34">
+        <v>9</v>
+      </c>
+      <c r="J34">
+        <v>4.2</v>
+      </c>
+      <c r="K34">
+        <v>4.4</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>1.69</v>
+      </c>
+      <c r="Q34">
+        <v>2.26</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>2.42</v>
+      </c>
+      <c r="U34">
+        <v>1.63</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>12</v>
+      </c>
+      <c r="Y34">
+        <v>21</v>
+      </c>
+      <c r="Z34">
+        <v>90</v>
+      </c>
+      <c r="AA34">
+        <v>470</v>
+      </c>
+      <c r="AB34">
+        <v>6.2</v>
+      </c>
+      <c r="AC34">
+        <v>10.5</v>
+      </c>
+      <c r="AD34">
+        <v>42</v>
+      </c>
+      <c r="AE34">
+        <v>230</v>
+      </c>
+      <c r="AF34">
+        <v>7.6</v>
+      </c>
+      <c r="AG34">
+        <v>11</v>
+      </c>
+      <c r="AH34">
+        <v>42</v>
+      </c>
+      <c r="AI34">
+        <v>200</v>
+      </c>
+      <c r="AJ34">
+        <v>13.5</v>
+      </c>
+      <c r="AK34">
+        <v>21</v>
+      </c>
+      <c r="AL34">
+        <v>70</v>
+      </c>
+      <c r="AM34">
+        <v>340</v>
+      </c>
+      <c r="AN34">
+        <v>11.5</v>
+      </c>
+      <c r="AO34">
+        <v>450</v>
+      </c>
+      <c r="AP34">
+        <v>10.5</v>
+      </c>
+      <c r="AQ34">
+        <v>17.5</v>
+      </c>
+      <c r="AR34">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS34">
+        <v>10.5</v>
+      </c>
+      <c r="AT34">
+        <v>5.5</v>
+      </c>
+      <c r="AU34">
+        <v>9</v>
+      </c>
+      <c r="AV34">
+        <v>8.6</v>
+      </c>
+      <c r="AW34">
+        <v>10.5</v>
+      </c>
+      <c r="AX34">
+        <v>6.8</v>
+      </c>
+      <c r="AY34">
+        <v>9.6</v>
+      </c>
+      <c r="AZ34">
+        <v>8.6</v>
+      </c>
+      <c r="BA34">
+        <v>10</v>
+      </c>
+      <c r="BB34">
+        <v>11.5</v>
+      </c>
+      <c r="BC34">
+        <v>17.5</v>
+      </c>
+      <c r="BD34">
+        <v>9.4</v>
+      </c>
+      <c r="BE34">
+        <v>10.5</v>
+      </c>
+      <c r="BF34">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG34">
+        <v>10.5</v>
+      </c>
+      <c r="BH34">
+        <v>0</v>
+      </c>
+      <c r="BI34">
+        <v>0</v>
+      </c>
+      <c r="BJ34">
+        <v>0</v>
+      </c>
+      <c r="BK34">
+        <v>0</v>
+      </c>
+      <c r="BL34">
+        <v>0</v>
+      </c>
+      <c r="BM34">
+        <v>0</v>
+      </c>
+      <c r="BN34">
+        <v>0</v>
+      </c>
+      <c r="BO34">
+        <v>0</v>
+      </c>
+      <c r="BP34">
+        <v>0</v>
+      </c>
+      <c r="BQ34">
+        <v>0</v>
+      </c>
+      <c r="BR34">
+        <v>0</v>
+      </c>
+      <c r="BS34">
+        <v>0</v>
+      </c>
+      <c r="BT34">
+        <v>0</v>
+      </c>
+      <c r="BU34">
+        <v>0</v>
+      </c>
+      <c r="BV34">
+        <v>0</v>
+      </c>
+      <c r="BW34">
+        <v>0</v>
+      </c>
+      <c r="BX34">
+        <v>0</v>
+      </c>
+      <c r="BY34">
+        <v>0</v>
+      </c>
+      <c r="BZ34">
+        <v>0</v>
+      </c>
+      <c r="CA34">
+        <v>0</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="35" spans="1:80">
+      <c r="A35" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" t="s">
+        <v>145</v>
+      </c>
+      <c r="E35" t="s">
+        <v>184</v>
+      </c>
+      <c r="F35">
+        <v>3.05</v>
+      </c>
+      <c r="G35">
+        <v>3.1</v>
+      </c>
+      <c r="H35">
+        <v>2.52</v>
+      </c>
+      <c r="I35">
+        <v>2.56</v>
+      </c>
+      <c r="J35">
+        <v>3.5</v>
+      </c>
+      <c r="K35">
+        <v>3.55</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>1.07</v>
+      </c>
+      <c r="N35">
+        <v>4.1</v>
+      </c>
+      <c r="O35">
+        <v>1.3</v>
+      </c>
+      <c r="P35">
+        <v>2.06</v>
+      </c>
+      <c r="Q35">
+        <v>1.9</v>
+      </c>
+      <c r="R35">
+        <v>1.4</v>
+      </c>
+      <c r="S35">
+        <v>3.3</v>
+      </c>
+      <c r="T35">
+        <v>1.71</v>
+      </c>
+      <c r="U35">
+        <v>2.32</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>15.5</v>
+      </c>
+      <c r="Y35">
+        <v>11.5</v>
+      </c>
+      <c r="Z35">
+        <v>17</v>
+      </c>
+      <c r="AA35">
+        <v>32</v>
+      </c>
+      <c r="AB35">
+        <v>14</v>
+      </c>
+      <c r="AC35">
+        <v>7.6</v>
+      </c>
+      <c r="AD35">
+        <v>11.5</v>
+      </c>
+      <c r="AE35">
+        <v>26</v>
+      </c>
+      <c r="AF35">
+        <v>21</v>
+      </c>
+      <c r="AG35">
+        <v>13</v>
+      </c>
+      <c r="AH35">
+        <v>16</v>
+      </c>
+      <c r="AI35">
+        <v>40</v>
+      </c>
+      <c r="AJ35">
+        <v>60</v>
+      </c>
+      <c r="AK35">
+        <v>32</v>
+      </c>
+      <c r="AL35">
+        <v>40</v>
+      </c>
+      <c r="AM35">
+        <v>80</v>
+      </c>
+      <c r="AN35">
+        <v>29</v>
+      </c>
+      <c r="AO35">
+        <v>20</v>
+      </c>
+      <c r="AP35">
+        <v>14</v>
+      </c>
+      <c r="AQ35">
+        <v>10.5</v>
+      </c>
+      <c r="AR35">
+        <v>15.5</v>
+      </c>
+      <c r="AS35">
+        <v>30</v>
+      </c>
+      <c r="AT35">
+        <v>12.5</v>
+      </c>
+      <c r="AU35">
+        <v>7.4</v>
+      </c>
+      <c r="AV35">
+        <v>11</v>
+      </c>
+      <c r="AW35">
+        <v>23</v>
+      </c>
+      <c r="AX35">
+        <v>18.5</v>
+      </c>
+      <c r="AY35">
+        <v>11.5</v>
+      </c>
+      <c r="AZ35">
+        <v>14.5</v>
+      </c>
+      <c r="BA35">
+        <v>32</v>
+      </c>
+      <c r="BB35">
+        <v>44</v>
+      </c>
+      <c r="BC35">
+        <v>28</v>
+      </c>
+      <c r="BD35">
+        <v>34</v>
+      </c>
+      <c r="BE35">
+        <v>70</v>
+      </c>
+      <c r="BF35">
+        <v>26</v>
+      </c>
+      <c r="BG35">
+        <v>18.5</v>
+      </c>
+      <c r="BH35">
+        <v>1000</v>
+      </c>
+      <c r="BI35">
+        <v>2.96</v>
+      </c>
+      <c r="BJ35">
+        <v>1000</v>
+      </c>
+      <c r="BK35">
+        <v>6.4</v>
+      </c>
+      <c r="BL35">
+        <v>1000</v>
+      </c>
+      <c r="BM35">
+        <v>1.01</v>
+      </c>
+      <c r="BN35">
+        <v>1000</v>
+      </c>
+      <c r="BO35">
+        <v>4.8</v>
+      </c>
+      <c r="BP35">
+        <v>1000</v>
+      </c>
+      <c r="BQ35">
+        <v>1.01</v>
+      </c>
+      <c r="BR35">
+        <v>1000</v>
+      </c>
+      <c r="BS35">
+        <v>1.01</v>
+      </c>
+      <c r="BT35">
+        <v>1000</v>
+      </c>
+      <c r="BU35">
+        <v>4.4</v>
+      </c>
+      <c r="BV35">
+        <v>1000</v>
+      </c>
+      <c r="BW35">
+        <v>1.01</v>
+      </c>
+      <c r="BX35">
+        <v>1000</v>
+      </c>
+      <c r="BY35">
+        <v>1.01</v>
+      </c>
+      <c r="BZ35">
+        <v>1000</v>
+      </c>
+      <c r="CA35">
+        <v>1.01</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36" spans="1:80">
+      <c r="A36" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" t="s">
+        <v>109</v>
+      </c>
+      <c r="D36" t="s">
+        <v>146</v>
+      </c>
+      <c r="E36" t="s">
+        <v>185</v>
+      </c>
+      <c r="F36">
+        <v>3.45</v>
+      </c>
+      <c r="G36">
+        <v>3.55</v>
+      </c>
+      <c r="H36">
+        <v>2.22</v>
+      </c>
+      <c r="I36">
+        <v>2.26</v>
+      </c>
+      <c r="J36">
+        <v>3.65</v>
+      </c>
+      <c r="K36">
+        <v>3.7</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>1.06</v>
+      </c>
+      <c r="N36">
+        <v>4.4</v>
+      </c>
+      <c r="O36">
+        <v>1.27</v>
+      </c>
+      <c r="P36">
+        <v>2.16</v>
+      </c>
+      <c r="Q36">
+        <v>1.82</v>
+      </c>
+      <c r="R36">
+        <v>1.46</v>
+      </c>
+      <c r="S36">
+        <v>3</v>
+      </c>
+      <c r="T36">
+        <v>1.69</v>
+      </c>
+      <c r="U36">
+        <v>2.36</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>17.5</v>
+      </c>
+      <c r="Y36">
+        <v>12</v>
+      </c>
+      <c r="Z36">
+        <v>15.5</v>
+      </c>
+      <c r="AA36">
+        <v>30</v>
+      </c>
+      <c r="AB36">
+        <v>16</v>
+      </c>
+      <c r="AC36">
+        <v>8.4</v>
+      </c>
+      <c r="AD36">
+        <v>11.5</v>
+      </c>
+      <c r="AE36">
+        <v>23</v>
+      </c>
+      <c r="AF36">
+        <v>27</v>
+      </c>
+      <c r="AG36">
+        <v>15.5</v>
+      </c>
+      <c r="AH36">
+        <v>16.5</v>
+      </c>
+      <c r="AI36">
+        <v>36</v>
+      </c>
+      <c r="AJ36">
+        <v>70</v>
+      </c>
+      <c r="AK36">
+        <v>40</v>
+      </c>
+      <c r="AL36">
+        <v>46</v>
+      </c>
+      <c r="AM36">
+        <v>85</v>
+      </c>
+      <c r="AN36">
+        <v>34</v>
+      </c>
+      <c r="AO36">
+        <v>14.5</v>
+      </c>
+      <c r="AP36">
+        <v>15</v>
+      </c>
+      <c r="AQ36">
+        <v>10.5</v>
+      </c>
+      <c r="AR36">
+        <v>13</v>
+      </c>
+      <c r="AS36">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT36">
+        <v>13.5</v>
+      </c>
+      <c r="AU36">
+        <v>7.6</v>
+      </c>
+      <c r="AV36">
+        <v>10</v>
+      </c>
+      <c r="AW36">
+        <v>18.5</v>
+      </c>
+      <c r="AX36">
+        <v>18.5</v>
+      </c>
+      <c r="AY36">
+        <v>12.5</v>
+      </c>
+      <c r="AZ36">
+        <v>14</v>
+      </c>
+      <c r="BA36">
+        <v>30</v>
+      </c>
+      <c r="BB36">
+        <v>9.6</v>
+      </c>
+      <c r="BC36">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD36">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE36">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF36">
+        <v>8.6</v>
+      </c>
+      <c r="BG36">
+        <v>13</v>
+      </c>
+      <c r="BH36">
+        <v>1000</v>
+      </c>
+      <c r="BI36">
+        <v>3.05</v>
+      </c>
+      <c r="BJ36">
+        <v>1000</v>
+      </c>
+      <c r="BK36">
+        <v>6.6</v>
+      </c>
+      <c r="BL36">
+        <v>1000</v>
+      </c>
+      <c r="BM36">
+        <v>1.01</v>
+      </c>
+      <c r="BN36">
+        <v>1000</v>
+      </c>
+      <c r="BO36">
+        <v>5.2</v>
+      </c>
+      <c r="BP36">
+        <v>1000</v>
+      </c>
+      <c r="BQ36">
+        <v>1.01</v>
+      </c>
+      <c r="BR36">
+        <v>1000</v>
+      </c>
+      <c r="BS36">
+        <v>1.01</v>
+      </c>
+      <c r="BT36">
+        <v>1000</v>
+      </c>
+      <c r="BU36">
+        <v>4.2</v>
+      </c>
+      <c r="BV36">
+        <v>1000</v>
+      </c>
+      <c r="BW36">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX36">
+        <v>1000</v>
+      </c>
+      <c r="BY36">
+        <v>1.01</v>
+      </c>
+      <c r="BZ36">
+        <v>1000</v>
+      </c>
+      <c r="CA36">
+        <v>1.01</v>
+      </c>
+      <c r="CB36" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="37" spans="1:80">
+      <c r="A37" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" t="s">
+        <v>109</v>
+      </c>
+      <c r="D37" t="s">
+        <v>147</v>
+      </c>
+      <c r="E37" t="s">
+        <v>186</v>
+      </c>
+      <c r="F37">
+        <v>8.6</v>
+      </c>
+      <c r="G37">
+        <v>9.4</v>
+      </c>
+      <c r="H37">
+        <v>1.44</v>
+      </c>
+      <c r="I37">
+        <v>1.46</v>
+      </c>
+      <c r="J37">
+        <v>5</v>
+      </c>
+      <c r="K37">
+        <v>5.1</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>1.05</v>
+      </c>
+      <c r="N37">
+        <v>4.4</v>
+      </c>
+      <c r="O37">
+        <v>1.27</v>
+      </c>
+      <c r="P37">
+        <v>2.16</v>
+      </c>
+      <c r="Q37">
+        <v>1.8</v>
+      </c>
+      <c r="R37">
+        <v>1.45</v>
+      </c>
+      <c r="S37">
+        <v>3.05</v>
+      </c>
+      <c r="T37">
+        <v>2.1</v>
+      </c>
+      <c r="U37">
+        <v>1.84</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>22</v>
+      </c>
+      <c r="Y37">
+        <v>8.4</v>
+      </c>
+      <c r="Z37">
+        <v>8.4</v>
+      </c>
+      <c r="AA37">
+        <v>12</v>
+      </c>
+      <c r="AB37">
+        <v>27</v>
+      </c>
+      <c r="AC37">
+        <v>11.5</v>
+      </c>
+      <c r="AD37">
+        <v>11</v>
+      </c>
+      <c r="AE37">
+        <v>16</v>
+      </c>
+      <c r="AF37">
+        <v>85</v>
+      </c>
+      <c r="AG37">
+        <v>34</v>
+      </c>
+      <c r="AH37">
+        <v>28</v>
+      </c>
+      <c r="AI37">
+        <v>40</v>
+      </c>
+      <c r="AJ37">
+        <v>400</v>
+      </c>
+      <c r="AK37">
+        <v>180</v>
+      </c>
+      <c r="AL37">
+        <v>150</v>
+      </c>
+      <c r="AM37">
+        <v>210</v>
+      </c>
+      <c r="AN37">
+        <v>260</v>
+      </c>
+      <c r="AO37">
+        <v>6.6</v>
+      </c>
+      <c r="AP37">
+        <v>16</v>
+      </c>
+      <c r="AQ37">
+        <v>7.6</v>
+      </c>
+      <c r="AR37">
+        <v>7.4</v>
+      </c>
+      <c r="AS37">
+        <v>10.5</v>
+      </c>
+      <c r="AT37">
+        <v>15.5</v>
+      </c>
+      <c r="AU37">
+        <v>10</v>
+      </c>
+      <c r="AV37">
+        <v>9.6</v>
+      </c>
+      <c r="AW37">
+        <v>14</v>
+      </c>
+      <c r="AX37">
+        <v>28</v>
+      </c>
+      <c r="AY37">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ37">
+        <v>20</v>
+      </c>
+      <c r="BA37">
+        <v>21</v>
+      </c>
+      <c r="BB37">
+        <v>12</v>
+      </c>
+      <c r="BC37">
+        <v>11.5</v>
+      </c>
+      <c r="BD37">
+        <v>11.5</v>
+      </c>
+      <c r="BE37">
+        <v>11.5</v>
+      </c>
+      <c r="BF37">
+        <v>12</v>
+      </c>
+      <c r="BG37">
+        <v>6</v>
+      </c>
+      <c r="BH37">
+        <v>1000</v>
+      </c>
+      <c r="BI37">
+        <v>3.05</v>
+      </c>
+      <c r="BJ37">
+        <v>1000</v>
+      </c>
+      <c r="BK37">
+        <v>8</v>
+      </c>
+      <c r="BL37">
+        <v>1000</v>
+      </c>
+      <c r="BM37">
+        <v>1.01</v>
+      </c>
+      <c r="BN37">
+        <v>1000</v>
+      </c>
+      <c r="BO37">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BP37">
+        <v>1000</v>
+      </c>
+      <c r="BQ37">
+        <v>1.01</v>
+      </c>
+      <c r="BR37">
+        <v>1000</v>
+      </c>
+      <c r="BS37">
+        <v>1.01</v>
+      </c>
+      <c r="BT37">
+        <v>1000</v>
+      </c>
+      <c r="BU37">
+        <v>3.25</v>
+      </c>
+      <c r="BV37">
+        <v>1000</v>
+      </c>
+      <c r="BW37">
+        <v>6.2</v>
+      </c>
+      <c r="BX37">
+        <v>1000</v>
+      </c>
+      <c r="BY37">
+        <v>1.01</v>
+      </c>
+      <c r="BZ37">
+        <v>1000</v>
+      </c>
+      <c r="CA37">
+        <v>1.01</v>
+      </c>
+      <c r="CB37" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38" spans="1:80">
+      <c r="A38" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" t="s">
+        <v>110</v>
+      </c>
+      <c r="D38" t="s">
+        <v>148</v>
+      </c>
+      <c r="E38" t="s">
+        <v>187</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>1.05</v>
+      </c>
+      <c r="Q38">
+        <v>1.01</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38">
+        <v>0</v>
+      </c>
+      <c r="AI38">
+        <v>0</v>
+      </c>
+      <c r="AJ38">
+        <v>0</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>0</v>
+      </c>
+      <c r="AN38">
+        <v>0</v>
+      </c>
+      <c r="AO38">
+        <v>0</v>
+      </c>
+      <c r="AP38">
+        <v>0</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38">
+        <v>0</v>
+      </c>
+      <c r="AV38">
+        <v>0</v>
+      </c>
+      <c r="AW38">
+        <v>0</v>
+      </c>
+      <c r="AX38">
+        <v>0</v>
+      </c>
+      <c r="AY38">
+        <v>0</v>
+      </c>
+      <c r="AZ38">
+        <v>0</v>
+      </c>
+      <c r="BA38">
+        <v>0</v>
+      </c>
+      <c r="BB38">
+        <v>0</v>
+      </c>
+      <c r="BC38">
+        <v>0</v>
+      </c>
+      <c r="BD38">
+        <v>0</v>
+      </c>
+      <c r="BE38">
+        <v>0</v>
+      </c>
+      <c r="BF38">
+        <v>0</v>
+      </c>
+      <c r="BG38">
+        <v>0</v>
+      </c>
+      <c r="BH38">
+        <v>0</v>
+      </c>
+      <c r="BI38">
+        <v>0</v>
+      </c>
+      <c r="BJ38">
+        <v>0</v>
+      </c>
+      <c r="BK38">
+        <v>0</v>
+      </c>
+      <c r="BL38">
+        <v>0</v>
+      </c>
+      <c r="BM38">
+        <v>0</v>
+      </c>
+      <c r="BN38">
+        <v>0</v>
+      </c>
+      <c r="BO38">
+        <v>0</v>
+      </c>
+      <c r="BP38">
+        <v>0</v>
+      </c>
+      <c r="BQ38">
+        <v>0</v>
+      </c>
+      <c r="BR38">
+        <v>0</v>
+      </c>
+      <c r="BS38">
+        <v>0</v>
+      </c>
+      <c r="BT38">
+        <v>0</v>
+      </c>
+      <c r="BU38">
+        <v>0</v>
+      </c>
+      <c r="BV38">
+        <v>0</v>
+      </c>
+      <c r="BW38">
+        <v>0</v>
+      </c>
+      <c r="BX38">
+        <v>0</v>
+      </c>
+      <c r="BY38">
+        <v>0</v>
+      </c>
+      <c r="BZ38">
+        <v>0</v>
+      </c>
+      <c r="CA38">
+        <v>0</v>
+      </c>
+      <c r="CB38" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="1:80">
+      <c r="A39" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" t="s">
+        <v>110</v>
+      </c>
+      <c r="D39" t="s">
+        <v>149</v>
+      </c>
+      <c r="E39" t="s">
+        <v>188</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>1.05</v>
+      </c>
+      <c r="Q39">
+        <v>1.01</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39">
+        <v>0</v>
+      </c>
+      <c r="AI39">
+        <v>0</v>
+      </c>
+      <c r="AJ39">
+        <v>0</v>
+      </c>
+      <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>0</v>
+      </c>
+      <c r="AN39">
+        <v>0</v>
+      </c>
+      <c r="AO39">
+        <v>0</v>
+      </c>
+      <c r="AP39">
+        <v>0</v>
+      </c>
+      <c r="AQ39">
+        <v>0</v>
+      </c>
+      <c r="AR39">
+        <v>0</v>
+      </c>
+      <c r="AS39">
+        <v>0</v>
+      </c>
+      <c r="AT39">
+        <v>0</v>
+      </c>
+      <c r="AU39">
+        <v>0</v>
+      </c>
+      <c r="AV39">
+        <v>0</v>
+      </c>
+      <c r="AW39">
+        <v>0</v>
+      </c>
+      <c r="AX39">
+        <v>0</v>
+      </c>
+      <c r="AY39">
+        <v>0</v>
+      </c>
+      <c r="AZ39">
+        <v>0</v>
+      </c>
+      <c r="BA39">
+        <v>0</v>
+      </c>
+      <c r="BB39">
+        <v>0</v>
+      </c>
+      <c r="BC39">
+        <v>0</v>
+      </c>
+      <c r="BD39">
+        <v>0</v>
+      </c>
+      <c r="BE39">
+        <v>0</v>
+      </c>
+      <c r="BF39">
+        <v>0</v>
+      </c>
+      <c r="BG39">
+        <v>0</v>
+      </c>
+      <c r="BH39">
+        <v>0</v>
+      </c>
+      <c r="BI39">
+        <v>0</v>
+      </c>
+      <c r="BJ39">
+        <v>0</v>
+      </c>
+      <c r="BK39">
+        <v>0</v>
+      </c>
+      <c r="BL39">
+        <v>0</v>
+      </c>
+      <c r="BM39">
+        <v>0</v>
+      </c>
+      <c r="BN39">
+        <v>0</v>
+      </c>
+      <c r="BO39">
+        <v>0</v>
+      </c>
+      <c r="BP39">
+        <v>0</v>
+      </c>
+      <c r="BQ39">
+        <v>0</v>
+      </c>
+      <c r="BR39">
+        <v>0</v>
+      </c>
+      <c r="BS39">
+        <v>0</v>
+      </c>
+      <c r="BT39">
+        <v>0</v>
+      </c>
+      <c r="BU39">
+        <v>0</v>
+      </c>
+      <c r="BV39">
+        <v>0</v>
+      </c>
+      <c r="BW39">
+        <v>0</v>
+      </c>
+      <c r="BX39">
+        <v>0</v>
+      </c>
+      <c r="BY39">
+        <v>0</v>
+      </c>
+      <c r="BZ39">
+        <v>0</v>
+      </c>
+      <c r="CA39">
+        <v>0</v>
+      </c>
+      <c r="CB39" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="40" spans="1:80">
+      <c r="A40" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" t="s">
+        <v>111</v>
+      </c>
+      <c r="D40" t="s">
+        <v>150</v>
+      </c>
+      <c r="E40" t="s">
+        <v>189</v>
+      </c>
+      <c r="F40">
+        <v>1.88</v>
+      </c>
+      <c r="G40">
+        <v>2.68</v>
+      </c>
+      <c r="H40">
+        <v>1.59</v>
+      </c>
+      <c r="I40">
+        <v>1000</v>
+      </c>
+      <c r="J40">
+        <v>1.59</v>
+      </c>
+      <c r="K40">
+        <v>950</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>1.1</v>
+      </c>
+      <c r="Q40">
+        <v>1.01</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>0</v>
+      </c>
+      <c r="AD40">
+        <v>0</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <v>0</v>
+      </c>
+      <c r="AH40">
+        <v>0</v>
+      </c>
+      <c r="AI40">
+        <v>0</v>
+      </c>
+      <c r="AJ40">
+        <v>0</v>
+      </c>
+      <c r="AK40">
+        <v>0</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>0</v>
+      </c>
+      <c r="AN40">
+        <v>0</v>
+      </c>
+      <c r="AO40">
+        <v>0</v>
+      </c>
+      <c r="AP40">
+        <v>0</v>
+      </c>
+      <c r="AQ40">
+        <v>0</v>
+      </c>
+      <c r="AR40">
+        <v>0</v>
+      </c>
+      <c r="AS40">
+        <v>0</v>
+      </c>
+      <c r="AT40">
+        <v>0</v>
+      </c>
+      <c r="AU40">
+        <v>0</v>
+      </c>
+      <c r="AV40">
+        <v>0</v>
+      </c>
+      <c r="AW40">
+        <v>0</v>
+      </c>
+      <c r="AX40">
+        <v>0</v>
+      </c>
+      <c r="AY40">
+        <v>0</v>
+      </c>
+      <c r="AZ40">
+        <v>0</v>
+      </c>
+      <c r="BA40">
+        <v>0</v>
+      </c>
+      <c r="BB40">
+        <v>0</v>
+      </c>
+      <c r="BC40">
+        <v>0</v>
+      </c>
+      <c r="BD40">
+        <v>0</v>
+      </c>
+      <c r="BE40">
+        <v>0</v>
+      </c>
+      <c r="BF40">
+        <v>0</v>
+      </c>
+      <c r="BG40">
+        <v>0</v>
+      </c>
+      <c r="BH40">
+        <v>0</v>
+      </c>
+      <c r="BI40">
+        <v>0</v>
+      </c>
+      <c r="BJ40">
+        <v>0</v>
+      </c>
+      <c r="BK40">
+        <v>0</v>
+      </c>
+      <c r="BL40">
+        <v>0</v>
+      </c>
+      <c r="BM40">
+        <v>0</v>
+      </c>
+      <c r="BN40">
+        <v>0</v>
+      </c>
+      <c r="BO40">
+        <v>0</v>
+      </c>
+      <c r="BP40">
+        <v>0</v>
+      </c>
+      <c r="BQ40">
+        <v>0</v>
+      </c>
+      <c r="BR40">
+        <v>0</v>
+      </c>
+      <c r="BS40">
+        <v>0</v>
+      </c>
+      <c r="BT40">
+        <v>0</v>
+      </c>
+      <c r="BU40">
+        <v>0</v>
+      </c>
+      <c r="BV40">
+        <v>0</v>
+      </c>
+      <c r="BW40">
+        <v>0</v>
+      </c>
+      <c r="BX40">
+        <v>0</v>
+      </c>
+      <c r="BY40">
+        <v>0</v>
+      </c>
+      <c r="BZ40">
+        <v>0</v>
+      </c>
+      <c r="CA40">
+        <v>0</v>
+      </c>
+      <c r="CB40" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-26.xlsx
@@ -586,7 +586,7 @@
     <t>Atletico Ottawa</t>
   </si>
   <si>
-    <t>2026-09-24 01:37:00</t>
+    <t>2026-09-24 03:51:14</t>
   </si>
 </sst>
 </file>
@@ -1180,166 +1180,166 @@
         <v>151</v>
       </c>
       <c r="F2">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="G2">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="H2">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="I2">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="J2">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
         <v>1.45</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O2">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P2">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="R2">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V2">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W2">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP2">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AQ2">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR2">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AS2">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AT2">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU2">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AW2">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AX2">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY2">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BA2">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BB2">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BC2">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BD2">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BE2">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1422,7 +1422,7 @@
         <v>152</v>
       </c>
       <c r="F3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G3">
         <v>3.45</v>
@@ -1431,7 +1431,7 @@
         <v>2.32</v>
       </c>
       <c r="I3">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="J3">
         <v>3.55</v>
@@ -1446,13 +1446,13 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="O3">
         <v>1.27</v>
       </c>
       <c r="P3">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q3">
         <v>1.81</v>
@@ -1470,19 +1470,19 @@
         <v>2.22</v>
       </c>
       <c r="V3">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="W3">
         <v>1.4</v>
       </c>
       <c r="X3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y3">
         <v>11.5</v>
       </c>
       <c r="Z3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA3">
         <v>30</v>
@@ -1491,7 +1491,7 @@
         <v>15</v>
       </c>
       <c r="AC3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3">
         <v>11.5</v>
@@ -1527,7 +1527,7 @@
         <v>34</v>
       </c>
       <c r="AO3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP3">
         <v>11</v>
@@ -1554,7 +1554,7 @@
         <v>20</v>
       </c>
       <c r="AX3">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AY3">
         <v>1.03</v>
@@ -1566,7 +1566,7 @@
         <v>1.03</v>
       </c>
       <c r="BB3">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BC3">
         <v>25</v>
@@ -1664,61 +1664,61 @@
         <v>153</v>
       </c>
       <c r="F4">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G4">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="I4">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J4">
+        <v>3.3</v>
+      </c>
+      <c r="K4">
+        <v>3.7</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.09</v>
+      </c>
+      <c r="N4">
         <v>3</v>
       </c>
-      <c r="K4">
-        <v>3.75</v>
-      </c>
-      <c r="L4">
-        <v>1.01</v>
-      </c>
-      <c r="M4">
-        <v>1.08</v>
-      </c>
-      <c r="N4">
-        <v>2.88</v>
-      </c>
       <c r="O4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P4">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Q4">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="T4">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U4">
         <v>1.83</v>
       </c>
       <c r="V4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W4">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
         <v>15.5</v>
@@ -1727,7 +1727,7 @@
         <v>46</v>
       </c>
       <c r="AA4">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB4">
         <v>7.6</v>
@@ -1748,16 +1748,16 @@
         <v>11</v>
       </c>
       <c r="AH4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI4">
         <v>110</v>
       </c>
       <c r="AJ4">
+        <v>23</v>
+      </c>
+      <c r="AK4">
         <v>24</v>
-      </c>
-      <c r="AK4">
-        <v>25</v>
       </c>
       <c r="AL4">
         <v>60</v>
@@ -1766,64 +1766,64 @@
         <v>190</v>
       </c>
       <c r="AN4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO4">
         <v>140</v>
       </c>
       <c r="AP4">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ4">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="AR4">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS4">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT4">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="AU4">
-        <v>3.95</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>5.5</v>
+        <v>17</v>
       </c>
       <c r="AW4">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AX4">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY4">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="AZ4">
-        <v>5.7</v>
+        <v>18.5</v>
       </c>
       <c r="BA4">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB4">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BC4">
-        <v>5.7</v>
+        <v>19.5</v>
       </c>
       <c r="BD4">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE4">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF4">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BG4">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH4">
         <v>3.8</v>
@@ -1835,55 +1835,55 @@
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BN4">
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="CB4" t="s">
         <v>190</v>
@@ -2154,7 +2154,7 @@
         <v>4</v>
       </c>
       <c r="H6">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I6">
         <v>2.12</v>
@@ -2163,10 +2163,10 @@
         <v>3.8</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M6">
         <v>1.05</v>
@@ -2193,13 +2193,13 @@
         <v>1.68</v>
       </c>
       <c r="U6">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V6">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="W6">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X6">
         <v>24</v>
@@ -2283,7 +2283,7 @@
         <v>7.4</v>
       </c>
       <c r="AY6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AZ6">
         <v>15</v>
@@ -2295,7 +2295,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BC6">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="BD6">
         <v>8.199999999999999</v>
@@ -2310,64 +2310,64 @@
         <v>11</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI6">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO6">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW6">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="CB6" t="s">
         <v>190</v>
@@ -2390,16 +2390,16 @@
         <v>156</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G7">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I7">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J7">
         <v>3.35</v>
@@ -2414,7 +2414,7 @@
         <v>1.09</v>
       </c>
       <c r="N7">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
         <v>1.4</v>
@@ -2426,16 +2426,16 @@
         <v>2.14</v>
       </c>
       <c r="R7">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S7">
         <v>3.95</v>
       </c>
       <c r="T7">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U7">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V7">
         <v>1.27</v>
@@ -2447,10 +2447,10 @@
         <v>14</v>
       </c>
       <c r="Y7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA7">
         <v>120</v>
@@ -2462,7 +2462,7 @@
         <v>9.4</v>
       </c>
       <c r="AD7">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AE7">
         <v>75</v>
@@ -2474,7 +2474,7 @@
         <v>11.5</v>
       </c>
       <c r="AH7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI7">
         <v>85</v>
@@ -2489,13 +2489,13 @@
         <v>55</v>
       </c>
       <c r="AM7">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO7">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP7">
         <v>10</v>
@@ -2504,10 +2504,10 @@
         <v>11.5</v>
       </c>
       <c r="AR7">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS7">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT7">
         <v>7.2</v>
@@ -2519,7 +2519,7 @@
         <v>15</v>
       </c>
       <c r="AW7">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX7">
         <v>10.5</v>
@@ -2528,28 +2528,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA7">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BB7">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BC7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD7">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE7">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF7">
         <v>16</v>
       </c>
       <c r="BG7">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2632,226 +2632,226 @@
         <v>157</v>
       </c>
       <c r="F8">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="G8">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="H8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I8">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="J8">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K8">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O8">
         <v>1.39</v>
       </c>
       <c r="P8">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="Q8">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R8">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="S8">
+        <v>4</v>
+      </c>
+      <c r="T8">
+        <v>1.94</v>
+      </c>
+      <c r="U8">
+        <v>1.87</v>
+      </c>
+      <c r="V8">
+        <v>1.26</v>
+      </c>
+      <c r="W8">
+        <v>1.92</v>
+      </c>
+      <c r="X8">
+        <v>14</v>
+      </c>
+      <c r="Y8">
+        <v>15</v>
+      </c>
+      <c r="Z8">
+        <v>36</v>
+      </c>
+      <c r="AA8">
+        <v>140</v>
+      </c>
+      <c r="AB8">
+        <v>8</v>
+      </c>
+      <c r="AC8">
+        <v>8.4</v>
+      </c>
+      <c r="AD8">
+        <v>20</v>
+      </c>
+      <c r="AE8">
+        <v>85</v>
+      </c>
+      <c r="AF8">
+        <v>14</v>
+      </c>
+      <c r="AG8">
+        <v>11</v>
+      </c>
+      <c r="AH8">
+        <v>23</v>
+      </c>
+      <c r="AI8">
+        <v>95</v>
+      </c>
+      <c r="AJ8">
+        <v>24</v>
+      </c>
+      <c r="AK8">
+        <v>24</v>
+      </c>
+      <c r="AL8">
+        <v>55</v>
+      </c>
+      <c r="AM8">
+        <v>170</v>
+      </c>
+      <c r="AN8">
+        <v>22</v>
+      </c>
+      <c r="AO8">
+        <v>110</v>
+      </c>
+      <c r="AP8">
+        <v>10</v>
+      </c>
+      <c r="AQ8">
+        <v>12</v>
+      </c>
+      <c r="AR8">
+        <v>5.9</v>
+      </c>
+      <c r="AS8">
+        <v>6.6</v>
+      </c>
+      <c r="AT8">
+        <v>6.6</v>
+      </c>
+      <c r="AU8">
+        <v>6.8</v>
+      </c>
+      <c r="AV8">
+        <v>15.5</v>
+      </c>
+      <c r="AW8">
+        <v>6.4</v>
+      </c>
+      <c r="AX8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ8">
+        <v>18.5</v>
+      </c>
+      <c r="BA8">
+        <v>6.4</v>
+      </c>
+      <c r="BB8">
+        <v>18.5</v>
+      </c>
+      <c r="BC8">
+        <v>19</v>
+      </c>
+      <c r="BD8">
+        <v>6.2</v>
+      </c>
+      <c r="BE8">
+        <v>6.6</v>
+      </c>
+      <c r="BF8">
+        <v>14.5</v>
+      </c>
+      <c r="BG8">
+        <v>6.4</v>
+      </c>
+      <c r="BH8">
+        <v>3.55</v>
+      </c>
+      <c r="BI8">
+        <v>2.5</v>
+      </c>
+      <c r="BJ8">
+        <v>13</v>
+      </c>
+      <c r="BK8">
+        <v>7.8</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>5.2</v>
+      </c>
+      <c r="BO8">
         <v>3.5</v>
       </c>
-      <c r="T8">
-        <v>1.66</v>
-      </c>
-      <c r="U8">
-        <v>1.58</v>
-      </c>
-      <c r="V8">
-        <v>1.22</v>
-      </c>
-      <c r="W8">
-        <v>1.98</v>
-      </c>
-      <c r="X8">
-        <v>1000</v>
-      </c>
-      <c r="Y8">
-        <v>21</v>
-      </c>
-      <c r="Z8">
-        <v>50</v>
-      </c>
-      <c r="AA8">
-        <v>1000</v>
-      </c>
-      <c r="AB8">
+      <c r="BP8">
+        <v>17</v>
+      </c>
+      <c r="BQ8">
         <v>10.5</v>
       </c>
-      <c r="AC8">
-        <v>11.5</v>
-      </c>
-      <c r="AD8">
-        <v>29</v>
-      </c>
-      <c r="AE8">
-        <v>100</v>
-      </c>
-      <c r="AF8">
-        <v>15.5</v>
-      </c>
-      <c r="AG8">
-        <v>15</v>
-      </c>
-      <c r="AH8">
+      <c r="BR8">
+        <v>40</v>
+      </c>
+      <c r="BS8">
+        <v>23</v>
+      </c>
+      <c r="BT8">
+        <v>9.4</v>
+      </c>
+      <c r="BU8">
+        <v>6</v>
+      </c>
+      <c r="BV8">
+        <v>55</v>
+      </c>
+      <c r="BW8">
         <v>32</v>
       </c>
-      <c r="AI8">
-        <v>1000</v>
-      </c>
-      <c r="AJ8">
-        <v>32</v>
-      </c>
-      <c r="AK8">
-        <v>34</v>
-      </c>
-      <c r="AL8">
-        <v>65</v>
-      </c>
-      <c r="AM8">
-        <v>1000</v>
-      </c>
-      <c r="AN8">
-        <v>1000</v>
-      </c>
-      <c r="AO8">
-        <v>1000</v>
-      </c>
-      <c r="AP8">
-        <v>2.14</v>
-      </c>
-      <c r="AQ8">
-        <v>1.95</v>
-      </c>
-      <c r="AR8">
-        <v>2.04</v>
-      </c>
-      <c r="AS8">
-        <v>2.14</v>
-      </c>
-      <c r="AT8">
-        <v>1.77</v>
-      </c>
-      <c r="AU8">
-        <v>1.8</v>
-      </c>
-      <c r="AV8">
-        <v>1.99</v>
-      </c>
-      <c r="AW8">
-        <v>2.08</v>
-      </c>
-      <c r="AX8">
-        <v>1.88</v>
-      </c>
-      <c r="AY8">
-        <v>1.87</v>
-      </c>
-      <c r="AZ8">
-        <v>2</v>
-      </c>
-      <c r="BA8">
-        <v>2.14</v>
-      </c>
-      <c r="BB8">
-        <v>2</v>
-      </c>
-      <c r="BC8">
-        <v>2</v>
-      </c>
-      <c r="BD8">
-        <v>2.06</v>
-      </c>
-      <c r="BE8">
-        <v>2.14</v>
-      </c>
-      <c r="BF8">
-        <v>2.14</v>
-      </c>
-      <c r="BG8">
-        <v>2.14</v>
-      </c>
-      <c r="BH8">
-        <v>1000</v>
-      </c>
-      <c r="BI8">
-        <v>1.01</v>
-      </c>
-      <c r="BJ8">
-        <v>1000</v>
-      </c>
-      <c r="BK8">
-        <v>1.01</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>1.01</v>
-      </c>
-      <c r="BN8">
-        <v>1000</v>
-      </c>
-      <c r="BO8">
-        <v>1.01</v>
-      </c>
-      <c r="BP8">
-        <v>1000</v>
-      </c>
-      <c r="BQ8">
-        <v>1.01</v>
-      </c>
-      <c r="BR8">
-        <v>1000</v>
-      </c>
-      <c r="BS8">
-        <v>1.01</v>
-      </c>
-      <c r="BT8">
-        <v>1000</v>
-      </c>
-      <c r="BU8">
-        <v>1.01</v>
-      </c>
-      <c r="BV8">
-        <v>1000</v>
-      </c>
-      <c r="BW8">
-        <v>1.01</v>
-      </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="CB8" t="s">
         <v>190</v>
@@ -2874,166 +2874,166 @@
         <v>158</v>
       </c>
       <c r="F9">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G9">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H9">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="I9">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J9">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K9">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L9">
         <v>1.35</v>
       </c>
       <c r="M9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N9">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P9">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q9">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R9">
         <v>1.38</v>
       </c>
       <c r="S9">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="T9">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="U9">
         <v>2.16</v>
       </c>
       <c r="V9">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="X9">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="Y9">
+        <v>14.5</v>
+      </c>
+      <c r="Z9">
+        <v>28</v>
+      </c>
+      <c r="AA9">
+        <v>90</v>
+      </c>
+      <c r="AB9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD9">
         <v>16</v>
       </c>
-      <c r="Z9">
-        <v>1000</v>
-      </c>
-      <c r="AA9">
-        <v>100</v>
-      </c>
-      <c r="AB9">
-        <v>10</v>
-      </c>
-      <c r="AC9">
-        <v>8.4</v>
-      </c>
-      <c r="AD9">
-        <v>17</v>
-      </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF9">
         <v>14</v>
       </c>
       <c r="AG9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AH9">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ9">
+        <v>32</v>
+      </c>
+      <c r="AK9">
         <v>26</v>
       </c>
-      <c r="AK9">
-        <v>23</v>
-      </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP9">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AQ9">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AR9">
-        <v>3.3</v>
+        <v>21</v>
       </c>
       <c r="AS9">
-        <v>3.2</v>
+        <v>11</v>
       </c>
       <c r="AT9">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU9">
         <v>7.2</v>
       </c>
       <c r="AV9">
-        <v>2.78</v>
+        <v>14</v>
       </c>
       <c r="AW9">
-        <v>3.3</v>
+        <v>34</v>
       </c>
       <c r="AX9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY9">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="BA9">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="BB9">
         <v>20</v>
       </c>
       <c r="BC9">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD9">
-        <v>3.3</v>
+        <v>9.4</v>
       </c>
       <c r="BE9">
-        <v>3.3</v>
+        <v>11</v>
       </c>
       <c r="BF9">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="BG9">
-        <v>3.3</v>
+        <v>34</v>
       </c>
       <c r="BH9">
         <v>4.3</v>
@@ -3125,7 +3125,7 @@
         <v>3.05</v>
       </c>
       <c r="I10">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J10">
         <v>3.65</v>
@@ -3358,16 +3358,16 @@
         <v>160</v>
       </c>
       <c r="F11">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G11">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="H11">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="I11">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J11">
         <v>3.25</v>
@@ -3379,7 +3379,7 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N11">
         <v>3.1</v>
@@ -3403,7 +3403,7 @@
         <v>1.98</v>
       </c>
       <c r="U11">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -3478,10 +3478,10 @@
         <v>42</v>
       </c>
       <c r="AT11">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU11">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV11">
         <v>11.5</v>
@@ -3511,10 +3511,10 @@
         <v>44</v>
       </c>
       <c r="BE11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF11">
-        <v>28</v>
+        <v>8.4</v>
       </c>
       <c r="BG11">
         <v>30</v>
@@ -4338,7 +4338,7 @@
         <v>110</v>
       </c>
       <c r="J15">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4374,10 +4374,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W15">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4568,22 +4568,22 @@
         <v>165</v>
       </c>
       <c r="F16">
-        <v>1.37</v>
+        <v>2.26</v>
       </c>
       <c r="G16">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="H16">
-        <v>1.12</v>
+        <v>3.3</v>
       </c>
       <c r="I16">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J16">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K16">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4598,10 +4598,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.12</v>
+        <v>1.83</v>
       </c>
       <c r="Q16">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4810,22 +4810,22 @@
         <v>166</v>
       </c>
       <c r="F17">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="G17">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="H17">
+        <v>4.9</v>
+      </c>
+      <c r="I17">
+        <v>5.9</v>
+      </c>
+      <c r="J17">
         <v>4.7</v>
       </c>
-      <c r="I17">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J17">
-        <v>4.3</v>
-      </c>
       <c r="K17">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4840,10 +4840,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="Q17">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>167</v>
       </c>
       <c r="F18">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="G18">
-        <v>730</v>
+        <v>680</v>
       </c>
       <c r="H18">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="I18">
-        <v>720</v>
+        <v>680</v>
       </c>
       <c r="J18">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="K18">
         <v>950</v>
@@ -5100,10 +5100,10 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W18">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5294,7 +5294,7 @@
         <v>168</v>
       </c>
       <c r="F19">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G19">
         <v>2.42</v>
@@ -5306,10 +5306,10 @@
         <v>3.7</v>
       </c>
       <c r="J19">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K19">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5318,13 +5318,13 @@
         <v>1.11</v>
       </c>
       <c r="N19">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="O19">
         <v>1.49</v>
       </c>
       <c r="P19">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -5339,7 +5339,7 @@
         <v>2.02</v>
       </c>
       <c r="U19">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -5348,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="X19">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y19">
         <v>11</v>
@@ -5411,7 +5411,7 @@
         <v>20</v>
       </c>
       <c r="AS19">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT19">
         <v>7</v>
@@ -5423,7 +5423,7 @@
         <v>13.5</v>
       </c>
       <c r="AW19">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AX19">
         <v>12</v>
@@ -5435,16 +5435,16 @@
         <v>19</v>
       </c>
       <c r="BA19">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB19">
         <v>29</v>
       </c>
       <c r="BC19">
-        <v>27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD19">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE19">
         <v>10</v>
@@ -5453,7 +5453,7 @@
         <v>24</v>
       </c>
       <c r="BG19">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH19">
         <v>0</v>
@@ -5539,10 +5539,10 @@
         <v>2.4</v>
       </c>
       <c r="G20">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H20">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I20">
         <v>3.65</v>
@@ -5581,7 +5581,7 @@
         <v>2.06</v>
       </c>
       <c r="U20">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -5638,7 +5638,7 @@
         <v>180</v>
       </c>
       <c r="AN20">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO20">
         <v>85</v>
@@ -5653,19 +5653,19 @@
         <v>21</v>
       </c>
       <c r="AS20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT20">
         <v>7.2</v>
       </c>
       <c r="AU20">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV20">
         <v>13.5</v>
       </c>
       <c r="AW20">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX20">
         <v>12</v>
@@ -5680,16 +5680,16 @@
         <v>10</v>
       </c>
       <c r="BB20">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC20">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD20">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF20">
         <v>8.6</v>
@@ -5787,13 +5787,13 @@
         <v>12</v>
       </c>
       <c r="I21">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="J21">
         <v>5.9</v>
       </c>
       <c r="K21">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5808,7 +5808,7 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q21">
         <v>1.71</v>
@@ -5880,34 +5880,34 @@
         <v>270</v>
       </c>
       <c r="AN21">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AO21">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AP21">
         <v>18</v>
       </c>
       <c r="AQ21">
-        <v>27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS21">
         <v>10.5</v>
       </c>
-      <c r="AS21">
-        <v>11.5</v>
-      </c>
       <c r="AT21">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU21">
         <v>12</v>
       </c>
       <c r="AV21">
-        <v>36</v>
+        <v>8.6</v>
       </c>
       <c r="AW21">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX21">
         <v>6.4</v>
@@ -5916,10 +5916,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ21">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA21">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB21">
         <v>8.199999999999999</v>
@@ -5931,13 +5931,13 @@
         <v>38</v>
       </c>
       <c r="BE21">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF21">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BG21">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH21">
         <v>0</v>
@@ -6032,7 +6032,7 @@
         <v>1.12</v>
       </c>
       <c r="J22">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="K22">
         <v>13</v>
@@ -6050,7 +6050,7 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q22">
         <v>1.53</v>
@@ -6092,7 +6092,7 @@
         <v>38</v>
       </c>
       <c r="AD22">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE22">
         <v>24</v>
@@ -6128,7 +6128,7 @@
         <v>3.1</v>
       </c>
       <c r="AP22">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ22">
         <v>8.199999999999999</v>
@@ -6140,10 +6140,10 @@
         <v>5.5</v>
       </c>
       <c r="AT22">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU22">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV22">
         <v>17.5</v>
@@ -6152,31 +6152,31 @@
         <v>18</v>
       </c>
       <c r="AX22">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY22">
+        <v>8.4</v>
+      </c>
+      <c r="AZ22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB22">
         <v>8.800000000000001</v>
       </c>
-      <c r="AZ22">
-        <v>8.6</v>
-      </c>
-      <c r="BA22">
-        <v>8.6</v>
-      </c>
-      <c r="BB22">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BC22">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD22">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE22">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF22">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG22">
         <v>2.78</v>
@@ -6746,7 +6746,7 @@
         <v>174</v>
       </c>
       <c r="F25">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -6755,13 +6755,13 @@
         <v>4.7</v>
       </c>
       <c r="I25">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J25">
         <v>3.3</v>
       </c>
       <c r="K25">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6776,7 +6776,7 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="Q25">
         <v>2.44</v>
@@ -6988,22 +6988,22 @@
         <v>175</v>
       </c>
       <c r="F26">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G26">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H26">
         <v>3.5</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J26">
         <v>3.85</v>
       </c>
       <c r="K26">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q26">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7230,7 +7230,7 @@
         <v>176</v>
       </c>
       <c r="F27">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G27">
         <v>1.84</v>
@@ -7239,7 +7239,7 @@
         <v>3.85</v>
       </c>
       <c r="I27">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J27">
         <v>4.8</v>
@@ -7263,7 +7263,7 @@
         <v>4</v>
       </c>
       <c r="Q27">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -7475,7 +7475,7 @@
         <v>1.27</v>
       </c>
       <c r="G28">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H28">
         <v>6.8</v>
@@ -7487,7 +7487,7 @@
         <v>4.9</v>
       </c>
       <c r="K28">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -7723,7 +7723,7 @@
         <v>5</v>
       </c>
       <c r="I29">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J29">
         <v>4.8</v>
@@ -7747,7 +7747,7 @@
         <v>3.15</v>
       </c>
       <c r="Q29">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>1.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q31">
         <v>1.67</v>
@@ -8440,22 +8440,22 @@
         <v>181</v>
       </c>
       <c r="F32">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="G32">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H32">
         <v>1.83</v>
       </c>
       <c r="I32">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="J32">
         <v>4</v>
       </c>
       <c r="K32">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -8470,10 +8470,10 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q32">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -8697,7 +8697,7 @@
         <v>6.2</v>
       </c>
       <c r="K33">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -8724,7 +8724,7 @@
         <v>0</v>
       </c>
       <c r="T33">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="U33">
         <v>1.58</v>
@@ -8930,7 +8930,7 @@
         <v>1.54</v>
       </c>
       <c r="H34">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I34">
         <v>9</v>
@@ -8966,7 +8966,7 @@
         <v>0</v>
       </c>
       <c r="T34">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U34">
         <v>1.63</v>
@@ -9026,7 +9026,7 @@
         <v>340</v>
       </c>
       <c r="AN34">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO34">
         <v>450</v>
@@ -9038,22 +9038,22 @@
         <v>17.5</v>
       </c>
       <c r="AR34">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS34">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT34">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU34">
         <v>9</v>
       </c>
       <c r="AV34">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AW34">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX34">
         <v>6.8</v>
@@ -9062,10 +9062,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ34">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BA34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB34">
         <v>11.5</v>
@@ -9074,16 +9074,16 @@
         <v>17.5</v>
       </c>
       <c r="BD34">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BE34">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF34">
         <v>9.800000000000001</v>
       </c>
       <c r="BG34">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH34">
         <v>0</v>
@@ -9172,10 +9172,10 @@
         <v>3.1</v>
       </c>
       <c r="H35">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I35">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J35">
         <v>3.5</v>
@@ -9238,25 +9238,25 @@
         <v>7.6</v>
       </c>
       <c r="AD35">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE35">
         <v>26</v>
       </c>
       <c r="AF35">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG35">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH35">
         <v>16</v>
       </c>
       <c r="AI35">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ35">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK35">
         <v>32</v>
@@ -9271,10 +9271,10 @@
         <v>29</v>
       </c>
       <c r="AO35">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP35">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ35">
         <v>10.5</v>
@@ -9295,7 +9295,7 @@
         <v>11</v>
       </c>
       <c r="AW35">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX35">
         <v>18.5</v>
@@ -9310,7 +9310,7 @@
         <v>32</v>
       </c>
       <c r="BB35">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BC35">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>70</v>
       </c>
       <c r="BF35">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BG35">
         <v>18.5</v>
@@ -9423,7 +9423,7 @@
         <v>3.65</v>
       </c>
       <c r="K36">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -9438,7 +9438,7 @@
         <v>1.27</v>
       </c>
       <c r="P36">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q36">
         <v>1.82</v>
@@ -9447,7 +9447,7 @@
         <v>1.46</v>
       </c>
       <c r="S36">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T36">
         <v>1.69</v>
@@ -9653,19 +9653,19 @@
         <v>8.6</v>
       </c>
       <c r="G37">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H37">
         <v>1.44</v>
       </c>
       <c r="I37">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="J37">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K37">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -9722,7 +9722,7 @@
         <v>11.5</v>
       </c>
       <c r="AD37">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE37">
         <v>16</v>
@@ -9776,7 +9776,7 @@
         <v>10</v>
       </c>
       <c r="AV37">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW37">
         <v>14</v>
@@ -9785,7 +9785,7 @@
         <v>28</v>
       </c>
       <c r="AY37">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ37">
         <v>20</v>
@@ -9794,34 +9794,34 @@
         <v>21</v>
       </c>
       <c r="BB37">
+        <v>12.5</v>
+      </c>
+      <c r="BC37">
         <v>12</v>
       </c>
-      <c r="BC37">
-        <v>11.5</v>
-      </c>
       <c r="BD37">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BE37">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF37">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG37">
         <v>6</v>
       </c>
       <c r="BH37">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI37">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BJ37">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK37">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BL37">
         <v>1000</v>
@@ -9830,46 +9830,46 @@
         <v>1.01</v>
       </c>
       <c r="BN37">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BO37">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BP37">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BQ37">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BR37">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BS37">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BT37">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BU37">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BV37">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BW37">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX37">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY37">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BZ37">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA37">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB37" t="s">
         <v>190</v>
@@ -10376,7 +10376,7 @@
         <v>189</v>
       </c>
       <c r="F40">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="G40">
         <v>2.68</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-26.xlsx
@@ -928,7 +928,7 @@
     <t>Atletico Ottawa</t>
   </si>
   <si>
-    <t>2026-09-24 19:53:31</t>
+    <t>2026-09-24 22:09:25</t>
   </si>
 </sst>
 </file>
@@ -1522,7 +1522,7 @@
         <v>217</v>
       </c>
       <c r="F2">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G2">
         <v>2.02</v>
@@ -1540,19 +1540,19 @@
         <v>3.65</v>
       </c>
       <c r="L2">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M2">
         <v>1.1</v>
       </c>
       <c r="N2">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="O2">
         <v>1.44</v>
       </c>
       <c r="P2">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q2">
         <v>2.3</v>
@@ -1564,10 +1564,10 @@
         <v>4.4</v>
       </c>
       <c r="T2">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U2">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V2">
         <v>1.23</v>
@@ -1579,7 +1579,7 @@
         <v>13.5</v>
       </c>
       <c r="Y2">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z2">
         <v>42</v>
@@ -1591,7 +1591,7 @@
         <v>7.4</v>
       </c>
       <c r="AC2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD2">
         <v>21</v>
@@ -1600,7 +1600,7 @@
         <v>100</v>
       </c>
       <c r="AF2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG2">
         <v>13</v>
@@ -1636,10 +1636,10 @@
         <v>12</v>
       </c>
       <c r="AR2">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AS2">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT2">
         <v>6.4</v>
@@ -1651,7 +1651,7 @@
         <v>17</v>
       </c>
       <c r="AW2">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX2">
         <v>9.4</v>
@@ -1663,7 +1663,7 @@
         <v>19</v>
       </c>
       <c r="BA2">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BB2">
         <v>19.5</v>
@@ -1675,13 +1675,13 @@
         <v>34</v>
       </c>
       <c r="BE2">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF2">
         <v>16</v>
       </c>
       <c r="BG2">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1764,25 +1764,25 @@
         <v>218</v>
       </c>
       <c r="F3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H3">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="I3">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J3">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M3">
         <v>1.06</v>
@@ -1794,13 +1794,13 @@
         <v>1.27</v>
       </c>
       <c r="P3">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q3">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R3">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S3">
         <v>3</v>
@@ -1809,22 +1809,22 @@
         <v>1.67</v>
       </c>
       <c r="U3">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V3">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W3">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X3">
         <v>17</v>
       </c>
       <c r="Y3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z3">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA3">
         <v>27</v>
@@ -1833,7 +1833,7 @@
         <v>16.5</v>
       </c>
       <c r="AC3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3">
         <v>11</v>
@@ -1845,10 +1845,10 @@
         <v>29</v>
       </c>
       <c r="AG3">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI3">
         <v>34</v>
@@ -1857,34 +1857,34 @@
         <v>75</v>
       </c>
       <c r="AK3">
+        <v>48</v>
+      </c>
+      <c r="AL3">
         <v>50</v>
       </c>
-      <c r="AL3">
-        <v>55</v>
-      </c>
       <c r="AM3">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AN3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO3">
         <v>14.5</v>
       </c>
       <c r="AP3">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AQ3">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR3">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS3">
         <v>22</v>
       </c>
       <c r="AT3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU3">
         <v>7.6</v>
@@ -1896,7 +1896,7 @@
         <v>18</v>
       </c>
       <c r="AX3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY3">
         <v>13.5</v>
@@ -1914,7 +1914,7 @@
         <v>30</v>
       </c>
       <c r="BD3">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BE3">
         <v>1.03</v>
@@ -2006,10 +2006,10 @@
         <v>219</v>
       </c>
       <c r="F4">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G4">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H4">
         <v>5.7</v>
@@ -2030,7 +2030,7 @@
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O4">
         <v>1.39</v>
@@ -2048,10 +2048,10 @@
         <v>4</v>
       </c>
       <c r="T4">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U4">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V4">
         <v>1.18</v>
@@ -2084,7 +2084,7 @@
         <v>120</v>
       </c>
       <c r="AF4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
@@ -2123,7 +2123,7 @@
         <v>38</v>
       </c>
       <c r="AS4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT4">
         <v>6.2</v>
@@ -2156,7 +2156,7 @@
         <v>17.5</v>
       </c>
       <c r="BD4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE4">
         <v>10.5</v>
@@ -2248,16 +2248,16 @@
         <v>220</v>
       </c>
       <c r="F5">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="G5">
         <v>1.86</v>
       </c>
       <c r="H5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I5">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="J5">
         <v>3.9</v>
@@ -2278,13 +2278,13 @@
         <v>1.19</v>
       </c>
       <c r="P5">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q5">
         <v>1.6</v>
       </c>
       <c r="R5">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S5">
         <v>2.56</v>
@@ -2296,7 +2296,7 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W5">
         <v>2.16</v>
@@ -2305,7 +2305,7 @@
         <v>1000</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z5">
         <v>1000</v>
@@ -2314,34 +2314,34 @@
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD5">
         <v>1000</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF5">
         <v>1000</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
         <v>1000</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
         <v>1000</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL5">
         <v>1000</v>
@@ -2359,7 +2359,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ5">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AR5">
         <v>1.03</v>
@@ -2368,7 +2368,7 @@
         <v>1.03</v>
       </c>
       <c r="AT5">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5">
         <v>1.03</v>
@@ -2493,7 +2493,7 @@
         <v>3.65</v>
       </c>
       <c r="G6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H6">
         <v>2.04</v>
@@ -2520,7 +2520,7 @@
         <v>1.26</v>
       </c>
       <c r="P6">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
         <v>1.77</v>
@@ -2574,10 +2574,10 @@
         <v>18.5</v>
       </c>
       <c r="AH6">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ6">
         <v>85</v>
@@ -2732,7 +2732,7 @@
         <v>222</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G7">
         <v>2.08</v>
@@ -2762,10 +2762,10 @@
         <v>1.4</v>
       </c>
       <c r="P7">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q7">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R7">
         <v>1.29</v>
@@ -2774,16 +2774,16 @@
         <v>4.1</v>
       </c>
       <c r="T7">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U7">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V7">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W7">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="X7">
         <v>14</v>
@@ -2819,7 +2819,7 @@
         <v>21</v>
       </c>
       <c r="AI7">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ7">
         <v>26</v>
@@ -2828,7 +2828,7 @@
         <v>29</v>
       </c>
       <c r="AL7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM7">
         <v>150</v>
@@ -2846,13 +2846,13 @@
         <v>11.5</v>
       </c>
       <c r="AR7">
+        <v>6.6</v>
+      </c>
+      <c r="AS7">
         <v>6.8</v>
       </c>
-      <c r="AS7">
-        <v>7</v>
-      </c>
       <c r="AT7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU7">
         <v>7</v>
@@ -2876,7 +2876,7 @@
         <v>6.8</v>
       </c>
       <c r="BB7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC7">
         <v>20</v>
@@ -2888,10 +2888,10 @@
         <v>7</v>
       </c>
       <c r="BF7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG7">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2977,7 +2977,7 @@
         <v>1.78</v>
       </c>
       <c r="G8">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="H8">
         <v>4.8</v>
@@ -2989,13 +2989,13 @@
         <v>3.55</v>
       </c>
       <c r="K8">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N8">
         <v>3.15</v>
@@ -3004,10 +3004,10 @@
         <v>1.39</v>
       </c>
       <c r="P8">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q8">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R8">
         <v>1.29</v>
@@ -3016,7 +3016,7 @@
         <v>4</v>
       </c>
       <c r="T8">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U8">
         <v>1.85</v>
@@ -3025,10 +3025,10 @@
         <v>1.22</v>
       </c>
       <c r="W8">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X8">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Y8">
         <v>18.5</v>
@@ -3043,7 +3043,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC8">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD8">
         <v>23</v>
@@ -3052,7 +3052,7 @@
         <v>100</v>
       </c>
       <c r="AF8">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG8">
         <v>13</v>
@@ -3088,7 +3088,7 @@
         <v>13</v>
       </c>
       <c r="AR8">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AS8">
         <v>5.1</v>
@@ -3133,19 +3133,19 @@
         <v>12.5</v>
       </c>
       <c r="BG8">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI8">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -3154,46 +3154,46 @@
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="CB8" t="s">
         <v>304</v>
@@ -3225,7 +3225,7 @@
         <v>3.8</v>
       </c>
       <c r="I9">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J9">
         <v>3.6</v>
@@ -3246,7 +3246,7 @@
         <v>1.31</v>
       </c>
       <c r="P9">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q9">
         <v>1.93</v>
@@ -3255,7 +3255,7 @@
         <v>1.38</v>
       </c>
       <c r="S9">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T9">
         <v>1.79</v>
@@ -3267,7 +3267,7 @@
         <v>1.33</v>
       </c>
       <c r="W9">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X9">
         <v>15</v>
@@ -3276,7 +3276,7 @@
         <v>15</v>
       </c>
       <c r="Z9">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA9">
         <v>85</v>
@@ -3312,7 +3312,7 @@
         <v>23</v>
       </c>
       <c r="AL9">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM9">
         <v>110</v>
@@ -3330,10 +3330,10 @@
         <v>13</v>
       </c>
       <c r="AR9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT9">
         <v>9</v>
@@ -3357,7 +3357,7 @@
         <v>15.5</v>
       </c>
       <c r="BA9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB9">
         <v>22</v>
@@ -3366,10 +3366,10 @@
         <v>19.5</v>
       </c>
       <c r="BD9">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF9">
         <v>13</v>
@@ -3473,7 +3473,7 @@
         <v>3.55</v>
       </c>
       <c r="K10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3703,10 +3703,10 @@
         <v>3.3</v>
       </c>
       <c r="G11">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H11">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="I11">
         <v>2.38</v>
@@ -3715,7 +3715,7 @@
         <v>3.4</v>
       </c>
       <c r="K11">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3736,7 +3736,7 @@
         <v>1.96</v>
       </c>
       <c r="R11">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S11">
         <v>3.25</v>
@@ -3763,7 +3763,7 @@
         <v>16.5</v>
       </c>
       <c r="AA11">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB11">
         <v>16</v>
@@ -3805,7 +3805,7 @@
         <v>50</v>
       </c>
       <c r="AO11">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP11">
         <v>11.5</v>
@@ -3844,19 +3844,19 @@
         <v>29</v>
       </c>
       <c r="BB11">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BC11">
         <v>32</v>
       </c>
       <c r="BD11">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE11">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF11">
-        <v>4.6</v>
+        <v>29</v>
       </c>
       <c r="BG11">
         <v>16</v>
@@ -3942,46 +3942,46 @@
         <v>227</v>
       </c>
       <c r="F12">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="G12">
         <v>1.66</v>
       </c>
       <c r="H12">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>7.4</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K12">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O12">
         <v>1.37</v>
       </c>
       <c r="P12">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q12">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="R12">
         <v>1.32</v>
       </c>
       <c r="S12">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="T12">
         <v>2.1</v>
@@ -3993,10 +3993,10 @@
         <v>1.15</v>
       </c>
       <c r="W12">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X12">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y12">
         <v>19.5</v>
@@ -4011,7 +4011,7 @@
         <v>7.4</v>
       </c>
       <c r="AC12">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD12">
         <v>29</v>
@@ -4020,7 +4020,7 @@
         <v>130</v>
       </c>
       <c r="AF12">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG12">
         <v>10.5</v>
@@ -4044,7 +4044,7 @@
         <v>190</v>
       </c>
       <c r="AN12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO12">
         <v>180</v>
@@ -4056,34 +4056,34 @@
         <v>15</v>
       </c>
       <c r="AR12">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AS12">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT12">
         <v>6.4</v>
       </c>
       <c r="AU12">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV12">
         <v>17</v>
       </c>
       <c r="AW12">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX12">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY12">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ12">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BA12">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB12">
         <v>14</v>
@@ -4092,16 +4092,16 @@
         <v>16</v>
       </c>
       <c r="BD12">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BE12">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BF12">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG12">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -4187,16 +4187,16 @@
         <v>2.64</v>
       </c>
       <c r="G13">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H13">
         <v>2.4</v>
       </c>
       <c r="I13">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="J13">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K13">
         <v>4.4</v>
@@ -4208,7 +4208,7 @@
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="O13">
         <v>1.22</v>
@@ -4232,10 +4232,10 @@
         <v>2.44</v>
       </c>
       <c r="V13">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W13">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4310,7 +4310,7 @@
         <v>1.11</v>
       </c>
       <c r="AV13">
-        <v>1.16</v>
+        <v>8</v>
       </c>
       <c r="AW13">
         <v>1.22</v>
@@ -4426,7 +4426,7 @@
         <v>229</v>
       </c>
       <c r="F14">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G14">
         <v>3.2</v>
@@ -4435,13 +4435,13 @@
         <v>2.7</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J14">
         <v>3.15</v>
       </c>
       <c r="K14">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4450,7 +4450,7 @@
         <v>1.11</v>
       </c>
       <c r="N14">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="O14">
         <v>1.5</v>
@@ -4459,7 +4459,7 @@
         <v>1.6</v>
       </c>
       <c r="Q14">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R14">
         <v>1.23</v>
@@ -4474,7 +4474,7 @@
         <v>1.86</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W14">
         <v>1.46</v>
@@ -4501,7 +4501,7 @@
         <v>14</v>
       </c>
       <c r="AE14">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF14">
         <v>22</v>
@@ -4570,7 +4570,7 @@
         <v>7.2</v>
       </c>
       <c r="BB14">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC14">
         <v>32</v>
@@ -4585,7 +4585,7 @@
         <v>7.2</v>
       </c>
       <c r="BG14">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4773,7 +4773,7 @@
         <v>34</v>
       </c>
       <c r="AO15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP15">
         <v>12.5</v>
@@ -4910,7 +4910,7 @@
         <v>231</v>
       </c>
       <c r="F16">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G16">
         <v>2.34</v>
@@ -4925,7 +4925,7 @@
         <v>3.6</v>
       </c>
       <c r="K16">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -5158,7 +5158,7 @@
         <v>2.88</v>
       </c>
       <c r="H17">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I17">
         <v>3.55</v>
@@ -5167,7 +5167,7 @@
         <v>2.92</v>
       </c>
       <c r="K17">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -5403,7 +5403,7 @@
         <v>2.12</v>
       </c>
       <c r="I18">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="J18">
         <v>3.55</v>
@@ -5427,7 +5427,7 @@
         <v>1.96</v>
       </c>
       <c r="Q18">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R18">
         <v>1.38</v>
@@ -5442,7 +5442,7 @@
         <v>2.16</v>
       </c>
       <c r="V18">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="W18">
         <v>1.35</v>
@@ -5481,7 +5481,7 @@
         <v>18.5</v>
       </c>
       <c r="AI18">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ18">
         <v>80</v>
@@ -5511,7 +5511,7 @@
         <v>12.5</v>
       </c>
       <c r="AS18">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT18">
         <v>12</v>
@@ -5535,13 +5535,13 @@
         <v>15</v>
       </c>
       <c r="BA18">
-        <v>28</v>
+        <v>7.4</v>
       </c>
       <c r="BB18">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC18">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD18">
         <v>38</v>
@@ -6643,7 +6643,7 @@
         <v>1.51</v>
       </c>
       <c r="S23">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="T23">
         <v>1.01</v>
@@ -6870,19 +6870,19 @@
         <v>1.06</v>
       </c>
       <c r="N24">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O24">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P24">
         <v>2.14</v>
       </c>
       <c r="Q24">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R24">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S24">
         <v>3</v>
@@ -6927,7 +6927,7 @@
         <v>16.5</v>
       </c>
       <c r="AG24">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH24">
         <v>17</v>
@@ -7330,7 +7330,7 @@
         <v>241</v>
       </c>
       <c r="F26">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -7820,7 +7820,7 @@
         <v>2.86</v>
       </c>
       <c r="H28">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I28">
         <v>2.92</v>
@@ -7850,13 +7850,13 @@
         <v>2.34</v>
       </c>
       <c r="R28">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S28">
         <v>4.5</v>
       </c>
       <c r="T28">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="U28">
         <v>1.98</v>
@@ -7880,7 +7880,7 @@
         <v>46</v>
       </c>
       <c r="AB28">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC28">
         <v>7.2</v>
@@ -7910,7 +7910,7 @@
         <v>36</v>
       </c>
       <c r="AL28">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM28">
         <v>140</v>
@@ -7940,13 +7940,13 @@
         <v>6.8</v>
       </c>
       <c r="AV28">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW28">
         <v>32</v>
       </c>
       <c r="AX28">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY28">
         <v>12</v>
@@ -7955,10 +7955,10 @@
         <v>19</v>
       </c>
       <c r="BA28">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB28">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BC28">
         <v>32</v>
@@ -7967,13 +7967,13 @@
         <v>48</v>
       </c>
       <c r="BE28">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BF28">
         <v>30</v>
       </c>
       <c r="BG28">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -8791,7 +8791,7 @@
         <v>2.62</v>
       </c>
       <c r="I32">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="J32">
         <v>3.7</v>
@@ -8830,7 +8830,7 @@
         <v>2.38</v>
       </c>
       <c r="V32">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W32">
         <v>1.55</v>
@@ -8899,7 +8899,7 @@
         <v>17</v>
       </c>
       <c r="AS32">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT32">
         <v>12</v>
@@ -8935,10 +8935,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BE32">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF32">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG32">
         <v>16</v>
@@ -9039,7 +9039,7 @@
         <v>5.6</v>
       </c>
       <c r="K33">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L33">
         <v>1.19</v>
@@ -9084,7 +9084,7 @@
         <v>48</v>
       </c>
       <c r="Z33">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AA33">
         <v>240</v>
@@ -9529,7 +9529,7 @@
         <v>1.01</v>
       </c>
       <c r="M35">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N35">
         <v>4.7</v>
@@ -9550,10 +9550,10 @@
         <v>2.16</v>
       </c>
       <c r="T35">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="U35">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="V35">
         <v>1.66</v>
@@ -9619,16 +9619,16 @@
         <v>1.03</v>
       </c>
       <c r="AQ35">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR35">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS35">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AT35">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU35">
         <v>1.01</v>
@@ -9637,10 +9637,10 @@
         <v>1.01</v>
       </c>
       <c r="AW35">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AX35">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY35">
         <v>1.01</v>
@@ -9649,22 +9649,22 @@
         <v>1.01</v>
       </c>
       <c r="BA35">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BB35">
         <v>1.01</v>
       </c>
       <c r="BC35">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD35">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BE35">
         <v>1.01</v>
       </c>
       <c r="BF35">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG35">
         <v>1.01</v>
@@ -9774,10 +9774,10 @@
         <v>1.08</v>
       </c>
       <c r="N36">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O36">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P36">
         <v>1.86</v>
@@ -9786,7 +9786,7 @@
         <v>2.06</v>
       </c>
       <c r="R36">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S36">
         <v>3.85</v>
@@ -9867,7 +9867,7 @@
         <v>29</v>
       </c>
       <c r="AS36">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT36">
         <v>7.4</v>
@@ -10013,13 +10013,13 @@
         <v>1.01</v>
       </c>
       <c r="M37">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N37">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="O37">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="P37">
         <v>2.16</v>
@@ -10028,16 +10028,16 @@
         <v>1.73</v>
       </c>
       <c r="R37">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S37">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="T37">
         <v>1.98</v>
       </c>
       <c r="U37">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="V37">
         <v>3.05</v>
@@ -10049,10 +10049,10 @@
         <v>22</v>
       </c>
       <c r="Y37">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z37">
         <v>9.4</v>
-      </c>
-      <c r="Z37">
-        <v>10</v>
       </c>
       <c r="AA37">
         <v>14.5</v>
@@ -10064,16 +10064,16 @@
         <v>13.5</v>
       </c>
       <c r="AD37">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE37">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AF37">
         <v>85</v>
       </c>
       <c r="AG37">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AH37">
         <v>32</v>
@@ -10097,40 +10097,40 @@
         <v>210</v>
       </c>
       <c r="AO37">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AP37">
         <v>1.01</v>
       </c>
       <c r="AQ37">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR37">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AS37">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AT37">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AU37">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV37">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW37">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AX37">
         <v>1.01</v>
       </c>
       <c r="AY37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ37">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA37">
         <v>1.01</v>
@@ -10151,7 +10151,7 @@
         <v>1.01</v>
       </c>
       <c r="BG37">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -10476,10 +10476,10 @@
         <v>254</v>
       </c>
       <c r="F39">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="G39">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H39">
         <v>2</v>
@@ -10488,40 +10488,40 @@
         <v>2.24</v>
       </c>
       <c r="J39">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="K39">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="L39">
         <v>1.01</v>
       </c>
       <c r="M39">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N39">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="O39">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P39">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q39">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R39">
         <v>1.2</v>
       </c>
       <c r="S39">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T39">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U39">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="V39">
         <v>1.81</v>
@@ -10530,25 +10530,25 @@
         <v>1.26</v>
       </c>
       <c r="X39">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y39">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z39">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA39">
         <v>1000</v>
       </c>
       <c r="AB39">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC39">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD39">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE39">
         <v>1000</v>
@@ -10584,25 +10584,25 @@
         <v>1000</v>
       </c>
       <c r="AP39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39">
         <v>1.03</v>
       </c>
       <c r="AR39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS39">
         <v>1.03</v>
       </c>
       <c r="AT39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU39">
         <v>1.03</v>
       </c>
       <c r="AV39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW39">
         <v>1.03</v>
@@ -10611,7 +10611,7 @@
         <v>1.03</v>
       </c>
       <c r="AY39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ39">
         <v>1.03</v>
@@ -10981,7 +10981,7 @@
         <v>1.01</v>
       </c>
       <c r="M41">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N41">
         <v>6</v>
@@ -11086,7 +11086,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV41">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW41">
         <v>19.5</v>
@@ -11235,7 +11235,7 @@
         <v>2.3</v>
       </c>
       <c r="Q42">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="R42">
         <v>1.49</v>
@@ -11268,7 +11268,7 @@
         <v>170</v>
       </c>
       <c r="AB42">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC42">
         <v>10.5</v>
@@ -11322,7 +11322,7 @@
         <v>12.5</v>
       </c>
       <c r="AT42">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU42">
         <v>9.199999999999999</v>
@@ -11355,13 +11355,13 @@
         <v>26</v>
       </c>
       <c r="BE42">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BF42">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG42">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11477,7 +11477,7 @@
         <v>3.4</v>
       </c>
       <c r="Q43">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R43">
         <v>1.97</v>
@@ -11549,10 +11549,10 @@
         <v>32</v>
       </c>
       <c r="AO43">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AP43">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AQ43">
         <v>14</v>
@@ -11564,7 +11564,7 @@
         <v>16</v>
       </c>
       <c r="AT43">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU43">
         <v>11.5</v>
@@ -11576,7 +11576,7 @@
         <v>12.5</v>
       </c>
       <c r="AX43">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AY43">
         <v>18</v>
@@ -11588,13 +11588,13 @@
         <v>18</v>
       </c>
       <c r="BB43">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC43">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BD43">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE43">
         <v>36</v>
@@ -11692,16 +11692,16 @@
         <v>1.75</v>
       </c>
       <c r="H44">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I44">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J44">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K44">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L44">
         <v>1.01</v>
@@ -11716,19 +11716,19 @@
         <v>1.19</v>
       </c>
       <c r="P44">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="Q44">
         <v>1.57</v>
       </c>
       <c r="R44">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="S44">
         <v>2.44</v>
       </c>
       <c r="T44">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U44">
         <v>2.2</v>
@@ -11934,7 +11934,7 @@
         <v>2.54</v>
       </c>
       <c r="H45">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I45">
         <v>3.6</v>
@@ -11943,7 +11943,7 @@
         <v>3.3</v>
       </c>
       <c r="K45">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L45">
         <v>1.01</v>
@@ -11952,25 +11952,25 @@
         <v>1.02</v>
       </c>
       <c r="N45">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O45">
         <v>1.24</v>
       </c>
       <c r="P45">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q45">
         <v>1.73</v>
       </c>
       <c r="R45">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S45">
         <v>2.78</v>
       </c>
       <c r="T45">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="U45">
         <v>2.2</v>
@@ -12185,7 +12185,7 @@
         <v>3.55</v>
       </c>
       <c r="K46">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L46">
         <v>1.01</v>
@@ -12200,7 +12200,7 @@
         <v>1.31</v>
       </c>
       <c r="P46">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -12209,7 +12209,7 @@
         <v>1.38</v>
       </c>
       <c r="S46">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T46">
         <v>1.75</v>
@@ -12421,7 +12421,7 @@
         <v>2.54</v>
       </c>
       <c r="I47">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J47">
         <v>3.55</v>
@@ -12460,7 +12460,7 @@
         <v>2.26</v>
       </c>
       <c r="V47">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W47">
         <v>1.5</v>
@@ -12654,13 +12654,13 @@
         <v>263</v>
       </c>
       <c r="F48">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G48">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H48">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I48">
         <v>6.4</v>
@@ -12669,7 +12669,7 @@
         <v>4.2</v>
       </c>
       <c r="K48">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L48">
         <v>1.01</v>
@@ -12678,13 +12678,13 @@
         <v>1.02</v>
       </c>
       <c r="N48">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="O48">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P48">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q48">
         <v>1.64</v>
@@ -12693,7 +12693,7 @@
         <v>1.47</v>
       </c>
       <c r="S48">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T48">
         <v>1.72</v>
@@ -12705,7 +12705,7 @@
         <v>1.19</v>
       </c>
       <c r="W48">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X48">
         <v>22</v>
@@ -12804,7 +12804,7 @@
         <v>13.5</v>
       </c>
       <c r="BD48">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE48">
         <v>8.6</v>
@@ -12905,7 +12905,7 @@
         <v>4.5</v>
       </c>
       <c r="I49">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J49">
         <v>4</v>
@@ -12920,7 +12920,7 @@
         <v>1.02</v>
       </c>
       <c r="N49">
-        <v>2.32</v>
+        <v>4.4</v>
       </c>
       <c r="O49">
         <v>1.22</v>
@@ -12935,7 +12935,7 @@
         <v>1.49</v>
       </c>
       <c r="S49">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T49">
         <v>1.64</v>
@@ -12944,118 +12944,118 @@
         <v>2.12</v>
       </c>
       <c r="V49">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W49">
         <v>2.24</v>
       </c>
       <c r="X49">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y49">
+        <v>23</v>
+      </c>
+      <c r="Z49">
+        <v>42</v>
+      </c>
+      <c r="AA49">
+        <v>120</v>
+      </c>
+      <c r="AB49">
+        <v>12</v>
+      </c>
+      <c r="AC49">
+        <v>10.5</v>
+      </c>
+      <c r="AD49">
+        <v>21</v>
+      </c>
+      <c r="AE49">
+        <v>60</v>
+      </c>
+      <c r="AF49">
+        <v>14</v>
+      </c>
+      <c r="AG49">
+        <v>11</v>
+      </c>
+      <c r="AH49">
+        <v>18.5</v>
+      </c>
+      <c r="AI49">
+        <v>60</v>
+      </c>
+      <c r="AJ49">
+        <v>19.5</v>
+      </c>
+      <c r="AK49">
+        <v>18</v>
+      </c>
+      <c r="AL49">
         <v>30</v>
       </c>
-      <c r="Z49">
+      <c r="AM49">
+        <v>80</v>
+      </c>
+      <c r="AN49">
+        <v>8.6</v>
+      </c>
+      <c r="AO49">
         <v>55</v>
       </c>
-      <c r="AA49">
-        <v>1000</v>
-      </c>
-      <c r="AB49">
-        <v>14.5</v>
-      </c>
-      <c r="AC49">
-        <v>12.5</v>
-      </c>
-      <c r="AD49">
-        <v>28</v>
-      </c>
-      <c r="AE49">
-        <v>75</v>
-      </c>
-      <c r="AF49">
+      <c r="AP49">
+        <v>16.5</v>
+      </c>
+      <c r="AQ49">
+        <v>18</v>
+      </c>
+      <c r="AR49">
+        <v>7</v>
+      </c>
+      <c r="AS49">
+        <v>7.6</v>
+      </c>
+      <c r="AT49">
+        <v>9.6</v>
+      </c>
+      <c r="AU49">
+        <v>8.6</v>
+      </c>
+      <c r="AV49">
+        <v>16.5</v>
+      </c>
+      <c r="AW49">
+        <v>7</v>
+      </c>
+      <c r="AX49">
+        <v>10.5</v>
+      </c>
+      <c r="AY49">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ49">
+        <v>15</v>
+      </c>
+      <c r="BA49">
+        <v>7</v>
+      </c>
+      <c r="BB49">
         <v>15.5</v>
       </c>
-      <c r="AG49">
-        <v>13</v>
-      </c>
-      <c r="AH49">
-        <v>25</v>
-      </c>
-      <c r="AI49">
-        <v>75</v>
-      </c>
-      <c r="AJ49">
-        <v>24</v>
-      </c>
-      <c r="AK49">
-        <v>21</v>
-      </c>
-      <c r="AL49">
-        <v>40</v>
-      </c>
-      <c r="AM49">
-        <v>100</v>
-      </c>
-      <c r="AN49">
-        <v>9.6</v>
-      </c>
-      <c r="AO49">
-        <v>70</v>
-      </c>
-      <c r="AP49">
-        <v>3.15</v>
-      </c>
-      <c r="AQ49">
-        <v>15</v>
-      </c>
-      <c r="AR49">
-        <v>3.1</v>
-      </c>
-      <c r="AS49">
-        <v>3.25</v>
-      </c>
-      <c r="AT49">
-        <v>2.66</v>
-      </c>
-      <c r="AU49">
+      <c r="BC49">
+        <v>14</v>
+      </c>
+      <c r="BD49">
+        <v>6.6</v>
+      </c>
+      <c r="BE49">
         <v>7.2</v>
       </c>
-      <c r="AV49">
-        <v>14</v>
-      </c>
-      <c r="AW49">
-        <v>3.1</v>
-      </c>
-      <c r="AX49">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY49">
-        <v>7.6</v>
-      </c>
-      <c r="AZ49">
-        <v>13</v>
-      </c>
-      <c r="BA49">
-        <v>3.1</v>
-      </c>
-      <c r="BB49">
-        <v>13</v>
-      </c>
-      <c r="BC49">
-        <v>12</v>
-      </c>
-      <c r="BD49">
-        <v>17.5</v>
-      </c>
-      <c r="BE49">
-        <v>3.15</v>
-      </c>
       <c r="BF49">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BG49">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="BH49">
         <v>1000</v>
@@ -13141,7 +13141,7 @@
         <v>2.08</v>
       </c>
       <c r="G50">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H50">
         <v>3.3</v>
@@ -13150,7 +13150,7 @@
         <v>3.8</v>
       </c>
       <c r="J50">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K50">
         <v>4.1</v>
@@ -13162,10 +13162,10 @@
         <v>1.05</v>
       </c>
       <c r="N50">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O50">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P50">
         <v>2.1</v>
@@ -13174,28 +13174,28 @@
         <v>1.73</v>
       </c>
       <c r="R50">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S50">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="T50">
         <v>1.64</v>
       </c>
       <c r="U50">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V50">
         <v>1.36</v>
       </c>
       <c r="W50">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="X50">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y50">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="Z50">
         <v>40</v>
@@ -13204,25 +13204,25 @@
         <v>90</v>
       </c>
       <c r="AB50">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC50">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD50">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE50">
         <v>55</v>
       </c>
       <c r="AF50">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AG50">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH50">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AI50">
         <v>65</v>
@@ -13231,7 +13231,7 @@
         <v>40</v>
       </c>
       <c r="AK50">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AL50">
         <v>48</v>
@@ -13240,64 +13240,64 @@
         <v>100</v>
       </c>
       <c r="AN50">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AO50">
         <v>48</v>
       </c>
       <c r="AP50">
-        <v>3.1</v>
+        <v>15</v>
       </c>
       <c r="AQ50">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR50">
         <v>16</v>
       </c>
       <c r="AS50">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AT50">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU50">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV50">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW50">
-        <v>2.96</v>
+        <v>7.4</v>
       </c>
       <c r="AX50">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY50">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AZ50">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA50">
-        <v>2.98</v>
+        <v>7.6</v>
       </c>
       <c r="BB50">
         <v>16.5</v>
       </c>
       <c r="BC50">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BD50">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="BE50">
-        <v>3</v>
+        <v>7.8</v>
       </c>
       <c r="BF50">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BG50">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="BH50">
         <v>1000</v>
@@ -13380,10 +13380,10 @@
         <v>266</v>
       </c>
       <c r="F51">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G51">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H51">
         <v>4.6</v>
@@ -13398,7 +13398,7 @@
         <v>4.3</v>
       </c>
       <c r="L51">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M51">
         <v>1.05</v>
@@ -13410,10 +13410,10 @@
         <v>1.24</v>
       </c>
       <c r="P51">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q51">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R51">
         <v>1.49</v>
@@ -13422,22 +13422,22 @@
         <v>2.7</v>
       </c>
       <c r="T51">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U51">
         <v>2.18</v>
       </c>
       <c r="V51">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W51">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X51">
         <v>21</v>
       </c>
       <c r="Y51">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z51">
         <v>42</v>
@@ -13452,7 +13452,7 @@
         <v>10.5</v>
       </c>
       <c r="AD51">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE51">
         <v>60</v>
@@ -13497,7 +13497,7 @@
         <v>29</v>
       </c>
       <c r="AS51">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT51">
         <v>9.199999999999999</v>
@@ -13509,7 +13509,7 @@
         <v>16.5</v>
       </c>
       <c r="AW51">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX51">
         <v>10.5</v>
@@ -13530,10 +13530,10 @@
         <v>15</v>
       </c>
       <c r="BD51">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE51">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF51">
         <v>7.6</v>
@@ -13545,40 +13545,40 @@
         <v>1000</v>
       </c>
       <c r="BI51">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="BJ51">
         <v>13.5</v>
       </c>
       <c r="BK51">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BL51">
         <v>1000</v>
       </c>
       <c r="BM51">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="BN51">
         <v>6.4</v>
       </c>
       <c r="BO51">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BP51">
         <v>17</v>
       </c>
       <c r="BQ51">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="BR51">
         <v>34</v>
       </c>
       <c r="BS51">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="BT51">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BU51">
         <v>5.3</v>
@@ -13587,19 +13587,19 @@
         <v>1000</v>
       </c>
       <c r="BW51">
+        <v>1.83</v>
+      </c>
+      <c r="BX51">
+        <v>1000</v>
+      </c>
+      <c r="BY51">
         <v>1.84</v>
-      </c>
-      <c r="BX51">
-        <v>1000</v>
-      </c>
-      <c r="BY51">
-        <v>1.85</v>
       </c>
       <c r="BZ51">
         <v>25</v>
       </c>
       <c r="CA51">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CB51" t="s">
         <v>304</v>
@@ -13876,7 +13876,7 @@
         <v>2.82</v>
       </c>
       <c r="J53">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K53">
         <v>4.2</v>
@@ -13888,13 +13888,13 @@
         <v>1.03</v>
       </c>
       <c r="N53">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="O53">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P53">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="Q53">
         <v>1.56</v>
@@ -13906,10 +13906,10 @@
         <v>2.24</v>
       </c>
       <c r="T53">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="U53">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V53">
         <v>1.54</v>
@@ -13918,112 +13918,112 @@
         <v>1.6</v>
       </c>
       <c r="X53">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y53">
+        <v>18</v>
+      </c>
+      <c r="Z53">
+        <v>24</v>
+      </c>
+      <c r="AA53">
+        <v>42</v>
+      </c>
+      <c r="AB53">
+        <v>17</v>
+      </c>
+      <c r="AC53">
+        <v>10.5</v>
+      </c>
+      <c r="AD53">
+        <v>14</v>
+      </c>
+      <c r="AE53">
+        <v>27</v>
+      </c>
+      <c r="AF53">
+        <v>22</v>
+      </c>
+      <c r="AG53">
+        <v>13.5</v>
+      </c>
+      <c r="AH53">
+        <v>15.5</v>
+      </c>
+      <c r="AI53">
+        <v>32</v>
+      </c>
+      <c r="AJ53">
+        <v>36</v>
+      </c>
+      <c r="AK53">
+        <v>25</v>
+      </c>
+      <c r="AL53">
+        <v>32</v>
+      </c>
+      <c r="AM53">
+        <v>60</v>
+      </c>
+      <c r="AN53">
+        <v>14.5</v>
+      </c>
+      <c r="AO53">
+        <v>16</v>
+      </c>
+      <c r="AP53">
+        <v>19</v>
+      </c>
+      <c r="AQ53">
+        <v>14</v>
+      </c>
+      <c r="AR53">
+        <v>18.5</v>
+      </c>
+      <c r="AS53">
+        <v>32</v>
+      </c>
+      <c r="AT53">
+        <v>13.5</v>
+      </c>
+      <c r="AU53">
+        <v>8.6</v>
+      </c>
+      <c r="AV53">
+        <v>11</v>
+      </c>
+      <c r="AW53">
         <v>21</v>
       </c>
-      <c r="Z53">
-        <v>30</v>
-      </c>
-      <c r="AA53">
-        <v>55</v>
-      </c>
-      <c r="AB53">
+      <c r="AX53">
+        <v>17.5</v>
+      </c>
+      <c r="AY53">
+        <v>11</v>
+      </c>
+      <c r="AZ53">
+        <v>12.5</v>
+      </c>
+      <c r="BA53">
+        <v>6.8</v>
+      </c>
+      <c r="BB53">
+        <v>7</v>
+      </c>
+      <c r="BC53">
         <v>20</v>
       </c>
-      <c r="AC53">
-        <v>12</v>
-      </c>
-      <c r="AD53">
-        <v>17</v>
-      </c>
-      <c r="AE53">
-        <v>36</v>
-      </c>
-      <c r="AF53">
-        <v>29</v>
-      </c>
-      <c r="AG53">
-        <v>16</v>
-      </c>
-      <c r="AH53">
-        <v>18.5</v>
-      </c>
-      <c r="AI53">
-        <v>44</v>
-      </c>
-      <c r="AJ53">
-        <v>48</v>
-      </c>
-      <c r="AK53">
-        <v>34</v>
-      </c>
-      <c r="AL53">
-        <v>40</v>
-      </c>
-      <c r="AM53">
-        <v>75</v>
-      </c>
-      <c r="AN53">
-        <v>17</v>
-      </c>
-      <c r="AO53">
-        <v>18.5</v>
-      </c>
-      <c r="AP53">
-        <v>3.25</v>
-      </c>
-      <c r="AQ53">
-        <v>12</v>
-      </c>
-      <c r="AR53">
-        <v>14</v>
-      </c>
-      <c r="AS53">
-        <v>3.1</v>
-      </c>
-      <c r="AT53">
-        <v>12</v>
-      </c>
-      <c r="AU53">
-        <v>7.2</v>
-      </c>
-      <c r="AV53">
-        <v>10</v>
-      </c>
-      <c r="AW53">
-        <v>16.5</v>
-      </c>
-      <c r="AX53">
-        <v>14.5</v>
-      </c>
-      <c r="AY53">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ53">
-        <v>11</v>
-      </c>
-      <c r="BA53">
-        <v>19</v>
-      </c>
-      <c r="BB53">
-        <v>21</v>
-      </c>
-      <c r="BC53">
-        <v>15</v>
-      </c>
       <c r="BD53">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="BE53">
-        <v>3.15</v>
+        <v>7.6</v>
       </c>
       <c r="BF53">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BG53">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BH53">
         <v>1000</v>
@@ -14109,13 +14109,13 @@
         <v>2.22</v>
       </c>
       <c r="G54">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H54">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I54">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J54">
         <v>3.45</v>
@@ -14130,37 +14130,37 @@
         <v>1.08</v>
       </c>
       <c r="N54">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O54">
+        <v>1.37</v>
+      </c>
+      <c r="P54">
+        <v>1.82</v>
+      </c>
+      <c r="Q54">
+        <v>2.1</v>
+      </c>
+      <c r="R54">
+        <v>1.32</v>
+      </c>
+      <c r="S54">
+        <v>3.85</v>
+      </c>
+      <c r="T54">
+        <v>1.86</v>
+      </c>
+      <c r="U54">
+        <v>2.04</v>
+      </c>
+      <c r="V54">
         <v>1.35</v>
       </c>
-      <c r="P54">
-        <v>1.86</v>
-      </c>
-      <c r="Q54">
-        <v>2.02</v>
-      </c>
-      <c r="R54">
-        <v>1.33</v>
-      </c>
-      <c r="S54">
-        <v>3.7</v>
-      </c>
-      <c r="T54">
-        <v>1.81</v>
-      </c>
-      <c r="U54">
-        <v>2.06</v>
-      </c>
-      <c r="V54">
-        <v>1.36</v>
-      </c>
       <c r="W54">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="X54">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y54">
         <v>13</v>
@@ -14172,13 +14172,13 @@
         <v>75</v>
       </c>
       <c r="AB54">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC54">
         <v>8</v>
       </c>
       <c r="AD54">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE54">
         <v>48</v>
@@ -14193,7 +14193,7 @@
         <v>20</v>
       </c>
       <c r="AI54">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ54">
         <v>30</v>
@@ -14208,13 +14208,13 @@
         <v>120</v>
       </c>
       <c r="AN54">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AO54">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AP54">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ54">
         <v>11.5</v>
@@ -14232,40 +14232,40 @@
         <v>7.2</v>
       </c>
       <c r="AV54">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW54">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AX54">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY54">
         <v>10</v>
       </c>
       <c r="AZ54">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA54">
         <v>46</v>
       </c>
       <c r="BB54">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC54">
         <v>22</v>
       </c>
       <c r="BD54">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BE54">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BF54">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BG54">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BH54">
         <v>1000</v>
@@ -14354,16 +14354,16 @@
         <v>1.68</v>
       </c>
       <c r="H55">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I55">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="J55">
         <v>4.7</v>
       </c>
       <c r="K55">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="L55">
         <v>1.01</v>
@@ -14372,10 +14372,10 @@
         <v>1.02</v>
       </c>
       <c r="N55">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O55">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P55">
         <v>3.1</v>
@@ -14384,130 +14384,130 @@
         <v>1.42</v>
       </c>
       <c r="R55">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="S55">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="T55">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="U55">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="V55">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W55">
         <v>2.46</v>
       </c>
       <c r="X55">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Y55">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="Z55">
+        <v>60</v>
+      </c>
+      <c r="AA55">
+        <v>140</v>
+      </c>
+      <c r="AB55">
+        <v>970</v>
+      </c>
+      <c r="AC55">
+        <v>13</v>
+      </c>
+      <c r="AD55">
+        <v>22</v>
+      </c>
+      <c r="AE55">
+        <v>65</v>
+      </c>
+      <c r="AF55">
+        <v>15</v>
+      </c>
+      <c r="AG55">
+        <v>11.5</v>
+      </c>
+      <c r="AH55">
+        <v>17.5</v>
+      </c>
+      <c r="AI55">
+        <v>55</v>
+      </c>
+      <c r="AJ55">
+        <v>970</v>
+      </c>
+      <c r="AK55">
+        <v>15.5</v>
+      </c>
+      <c r="AL55">
+        <v>24</v>
+      </c>
+      <c r="AM55">
         <v>70</v>
       </c>
-      <c r="AA55">
-        <v>1000</v>
-      </c>
-      <c r="AB55">
-        <v>22</v>
-      </c>
-      <c r="AC55">
-        <v>18</v>
-      </c>
-      <c r="AD55">
-        <v>32</v>
-      </c>
-      <c r="AE55">
-        <v>75</v>
-      </c>
-      <c r="AF55">
-        <v>20</v>
-      </c>
-      <c r="AG55">
-        <v>15</v>
-      </c>
-      <c r="AH55">
-        <v>24</v>
-      </c>
-      <c r="AI55">
-        <v>65</v>
-      </c>
-      <c r="AJ55">
-        <v>25</v>
-      </c>
-      <c r="AK55">
-        <v>20</v>
-      </c>
-      <c r="AL55">
-        <v>32</v>
-      </c>
-      <c r="AM55">
-        <v>85</v>
-      </c>
       <c r="AN55">
-        <v>970</v>
+        <v>6.2</v>
       </c>
       <c r="AO55">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AP55">
-        <v>2.02</v>
+        <v>7</v>
       </c>
       <c r="AQ55">
-        <v>18.5</v>
+        <v>6.6</v>
       </c>
       <c r="AR55">
-        <v>2.82</v>
+        <v>7</v>
       </c>
       <c r="AS55">
-        <v>2.94</v>
+        <v>7.4</v>
       </c>
       <c r="AT55">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU55">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AV55">
+        <v>6</v>
+      </c>
+      <c r="AW55">
+        <v>7</v>
+      </c>
+      <c r="AX55">
+        <v>12.5</v>
+      </c>
+      <c r="AY55">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ55">
+        <v>5.6</v>
+      </c>
+      <c r="BA55">
+        <v>6.8</v>
+      </c>
+      <c r="BB55">
         <v>15.5</v>
       </c>
-      <c r="AW55">
-        <v>2.82</v>
-      </c>
-      <c r="AX55">
-        <v>10.5</v>
-      </c>
-      <c r="AY55">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ55">
-        <v>12</v>
-      </c>
-      <c r="BA55">
-        <v>2.8</v>
-      </c>
-      <c r="BB55">
+      <c r="BC55">
         <v>13</v>
       </c>
-      <c r="BC55">
-        <v>11</v>
-      </c>
       <c r="BD55">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="BE55">
-        <v>2.84</v>
+        <v>7</v>
       </c>
       <c r="BF55">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BG55">
-        <v>2.76</v>
+        <v>6.6</v>
       </c>
       <c r="BH55">
         <v>1000</v>
@@ -15074,19 +15074,19 @@
         <v>273</v>
       </c>
       <c r="F58">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G58">
         <v>110</v>
       </c>
       <c r="H58">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="I58">
         <v>110</v>
       </c>
       <c r="J58">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="K58">
         <v>950</v>
@@ -15316,16 +15316,16 @@
         <v>274</v>
       </c>
       <c r="F59">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G59">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H59">
         <v>3.45</v>
       </c>
       <c r="I59">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J59">
         <v>3.15</v>
@@ -15337,7 +15337,7 @@
         <v>1.49</v>
       </c>
       <c r="M59">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N59">
         <v>2.74</v>
@@ -15355,7 +15355,7 @@
         <v>1.21</v>
       </c>
       <c r="S59">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T59">
         <v>2.02</v>
@@ -15364,10 +15364,10 @@
         <v>1.84</v>
       </c>
       <c r="V59">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W59">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X59">
         <v>9.6</v>
@@ -15382,7 +15382,7 @@
         <v>75</v>
       </c>
       <c r="AB59">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC59">
         <v>7.2</v>
@@ -15394,7 +15394,7 @@
         <v>70</v>
       </c>
       <c r="AF59">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG59">
         <v>12.5</v>
@@ -15469,7 +15469,7 @@
         <v>48</v>
       </c>
       <c r="BE59">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF59">
         <v>27</v>
@@ -15478,22 +15478,22 @@
         <v>50</v>
       </c>
       <c r="BH59">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BI59">
         <v>2.44</v>
       </c>
       <c r="BJ59">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK59">
-        <v>8</v>
+        <v>2.62</v>
       </c>
       <c r="BL59">
         <v>1000</v>
       </c>
       <c r="BM59">
-        <v>1.43</v>
+        <v>2.62</v>
       </c>
       <c r="BN59">
         <v>1000</v>
@@ -15502,16 +15502,16 @@
         <v>3.45</v>
       </c>
       <c r="BP59">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ59">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="BR59">
         <v>1000</v>
       </c>
       <c r="BS59">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="BT59">
         <v>1000</v>
@@ -15520,22 +15520,22 @@
         <v>4.5</v>
       </c>
       <c r="BV59">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW59">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="BX59">
         <v>1000</v>
       </c>
       <c r="BY59">
-        <v>4.3</v>
+        <v>2.62</v>
       </c>
       <c r="BZ59">
         <v>1000</v>
       </c>
       <c r="CA59">
-        <v>4.3</v>
+        <v>2.62</v>
       </c>
       <c r="CB59" t="s">
         <v>304</v>
@@ -16093,7 +16093,7 @@
         <v>9.6</v>
       </c>
       <c r="W62">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X62">
         <v>34</v>
@@ -16168,10 +16168,10 @@
         <v>20</v>
       </c>
       <c r="AV62">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AW62">
-        <v>14</v>
+        <v>6.6</v>
       </c>
       <c r="AX62">
         <v>7.4</v>
@@ -16290,7 +16290,7 @@
         <v>1.33</v>
       </c>
       <c r="H63">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="I63">
         <v>14</v>
@@ -16305,7 +16305,7 @@
         <v>1.33</v>
       </c>
       <c r="M63">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N63">
         <v>4.8</v>
@@ -16377,7 +16377,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AK63">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL63">
         <v>48</v>
@@ -16401,7 +16401,7 @@
         <v>14</v>
       </c>
       <c r="AS63">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT63">
         <v>8</v>
@@ -16431,10 +16431,10 @@
         <v>8.6</v>
       </c>
       <c r="BC63">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD63">
-        <v>38</v>
+        <v>11.5</v>
       </c>
       <c r="BE63">
         <v>14</v>
@@ -16529,10 +16529,10 @@
         <v>2.4</v>
       </c>
       <c r="G64">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H64">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I64">
         <v>3.6</v>
@@ -16577,7 +16577,7 @@
         <v>1.38</v>
       </c>
       <c r="W64">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X64">
         <v>9.800000000000001</v>
@@ -16589,7 +16589,7 @@
         <v>23</v>
       </c>
       <c r="AA64">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB64">
         <v>8</v>
@@ -16777,7 +16777,7 @@
         <v>4.5</v>
       </c>
       <c r="I65">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J65">
         <v>3.35</v>
@@ -16786,19 +16786,19 @@
         <v>3.45</v>
       </c>
       <c r="L65">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="M65">
         <v>1.11</v>
       </c>
       <c r="N65">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="O65">
         <v>1.5</v>
       </c>
       <c r="P65">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Q65">
         <v>2.48</v>
@@ -16816,7 +16816,7 @@
         <v>1.79</v>
       </c>
       <c r="V65">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W65">
         <v>1.94</v>
@@ -16825,19 +16825,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y65">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z65">
         <v>32</v>
       </c>
       <c r="AA65">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AB65">
         <v>7.2</v>
       </c>
       <c r="AC65">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD65">
         <v>21</v>
@@ -16852,7 +16852,7 @@
         <v>11.5</v>
       </c>
       <c r="AH65">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI65">
         <v>110</v>
@@ -16864,7 +16864,7 @@
         <v>28</v>
       </c>
       <c r="AL65">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM65">
         <v>210</v>
@@ -16873,7 +16873,7 @@
         <v>23</v>
       </c>
       <c r="AO65">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP65">
         <v>8.6</v>
@@ -16885,7 +16885,7 @@
         <v>27</v>
       </c>
       <c r="AS65">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT65">
         <v>6.4</v>
@@ -16894,10 +16894,10 @@
         <v>7</v>
       </c>
       <c r="AV65">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW65">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX65">
         <v>9.6</v>
@@ -16909,10 +16909,10 @@
         <v>21</v>
       </c>
       <c r="BA65">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BB65">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC65">
         <v>23</v>
@@ -16921,13 +16921,13 @@
         <v>48</v>
       </c>
       <c r="BE65">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF65">
         <v>19</v>
       </c>
       <c r="BG65">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH65">
         <v>1000</v>
@@ -17016,10 +17016,10 @@
         <v>3.4</v>
       </c>
       <c r="H66">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I66">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J66">
         <v>3.35</v>
@@ -17028,19 +17028,19 @@
         <v>3.55</v>
       </c>
       <c r="L66">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M66">
         <v>1.08</v>
       </c>
       <c r="N66">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O66">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P66">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="Q66">
         <v>2.1</v>
@@ -17049,7 +17049,7 @@
         <v>1.31</v>
       </c>
       <c r="S66">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T66">
         <v>1.83</v>
@@ -17067,7 +17067,7 @@
         <v>13</v>
       </c>
       <c r="Y66">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z66">
         <v>15.5</v>
@@ -17076,7 +17076,7 @@
         <v>38</v>
       </c>
       <c r="AB66">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC66">
         <v>7.6</v>
@@ -17103,7 +17103,7 @@
         <v>60</v>
       </c>
       <c r="AK66">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AL66">
         <v>55</v>
@@ -17112,10 +17112,10 @@
         <v>120</v>
       </c>
       <c r="AN66">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AO66">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP66">
         <v>11</v>
@@ -17127,10 +17127,10 @@
         <v>13.5</v>
       </c>
       <c r="AS66">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AT66">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU66">
         <v>6.8</v>
@@ -17139,46 +17139,46 @@
         <v>10.5</v>
       </c>
       <c r="AW66">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="AX66">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY66">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AZ66">
         <v>16.5</v>
       </c>
       <c r="BA66">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB66">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BC66">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD66">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BE66">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BF66">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BG66">
         <v>20</v>
       </c>
       <c r="BH66">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BI66">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="BJ66">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK66">
         <v>7.6</v>
@@ -17187,49 +17187,49 @@
         <v>1000</v>
       </c>
       <c r="BM66">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="BN66">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BO66">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP66">
         <v>38</v>
       </c>
       <c r="BQ66">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="BR66">
         <v>1000</v>
       </c>
       <c r="BS66">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="BT66">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BU66">
-        <v>2.24</v>
+        <v>2.76</v>
       </c>
       <c r="BV66">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW66">
-        <v>3.2</v>
+        <v>1.89</v>
       </c>
       <c r="BX66">
         <v>46</v>
       </c>
       <c r="BY66">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="BZ66">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="CA66">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="CB66" t="s">
         <v>304</v>
@@ -17252,7 +17252,7 @@
         <v>282</v>
       </c>
       <c r="F67">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G67">
         <v>2.92</v>
@@ -17303,7 +17303,7 @@
         <v>1.02</v>
       </c>
       <c r="W67">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X67">
         <v>1000</v>
@@ -17993,7 +17993,7 @@
         <v>4.8</v>
       </c>
       <c r="K70">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L70">
         <v>1.18</v>
@@ -18059,7 +18059,7 @@
         <v>17</v>
       </c>
       <c r="AG70">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH70">
         <v>18.5</v>
@@ -18086,7 +18086,7 @@
         <v>38</v>
       </c>
       <c r="AP70">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ70">
         <v>6.6</v>
@@ -18095,7 +18095,7 @@
         <v>7.2</v>
       </c>
       <c r="AS70">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT70">
         <v>14</v>
@@ -18119,7 +18119,7 @@
         <v>14.5</v>
       </c>
       <c r="BA70">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB70">
         <v>14.5</v>
@@ -18131,13 +18131,13 @@
         <v>19</v>
       </c>
       <c r="BE70">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF70">
         <v>4.3</v>
       </c>
       <c r="BG70">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH70">
         <v>1000</v>
@@ -18223,10 +18223,10 @@
         <v>2.46</v>
       </c>
       <c r="G71">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H71">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="I71">
         <v>3.15</v>
@@ -18250,13 +18250,13 @@
         <v>1.21</v>
       </c>
       <c r="P71">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q71">
         <v>1.67</v>
       </c>
       <c r="R71">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S71">
         <v>2.6</v>
@@ -18268,10 +18268,10 @@
         <v>2.3</v>
       </c>
       <c r="V71">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W71">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X71">
         <v>1000</v>
@@ -18462,7 +18462,7 @@
         <v>287</v>
       </c>
       <c r="F72">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G72">
         <v>1.85</v>
@@ -18486,7 +18486,7 @@
         <v>1.01</v>
       </c>
       <c r="N72">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="O72">
         <v>1.09</v>
@@ -18704,7 +18704,7 @@
         <v>288</v>
       </c>
       <c r="F73">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="G73">
         <v>2.12</v>
@@ -18713,13 +18713,13 @@
         <v>3.55</v>
       </c>
       <c r="I73">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J73">
         <v>3.85</v>
       </c>
       <c r="K73">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L73">
         <v>1.01</v>
@@ -18743,7 +18743,7 @@
         <v>1.53</v>
       </c>
       <c r="S73">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T73">
         <v>1.6</v>
@@ -18752,7 +18752,7 @@
         <v>2.36</v>
       </c>
       <c r="V73">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W73">
         <v>1.89</v>
@@ -18949,7 +18949,7 @@
         <v>1.34</v>
       </c>
       <c r="G74">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H74">
         <v>6.8</v>
@@ -18961,7 +18961,7 @@
         <v>5.4</v>
       </c>
       <c r="K74">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="L74">
         <v>1.01</v>
@@ -19203,7 +19203,7 @@
         <v>3.45</v>
       </c>
       <c r="K75">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L75">
         <v>1.01</v>
@@ -19212,16 +19212,16 @@
         <v>1.08</v>
       </c>
       <c r="N75">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O75">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P75">
         <v>1.75</v>
       </c>
       <c r="Q75">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R75">
         <v>1.28</v>
@@ -19233,7 +19233,7 @@
         <v>1.96</v>
       </c>
       <c r="U75">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V75">
         <v>2.08</v>
@@ -19248,7 +19248,7 @@
         <v>8.4</v>
       </c>
       <c r="Z75">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AA75">
         <v>22</v>
@@ -19284,7 +19284,7 @@
         <v>95</v>
       </c>
       <c r="AL75">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM75">
         <v>1000</v>
@@ -19293,61 +19293,61 @@
         <v>1000</v>
       </c>
       <c r="AO75">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AP75">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="AQ75">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AR75">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AS75">
-        <v>2.22</v>
+        <v>16.5</v>
       </c>
       <c r="AT75">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="AU75">
         <v>6</v>
       </c>
       <c r="AV75">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AW75">
-        <v>2.46</v>
+        <v>17</v>
       </c>
       <c r="AX75">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="AY75">
         <v>16.5</v>
       </c>
       <c r="AZ75">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="BA75">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="BB75">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="BC75">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="BD75">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="BE75">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="BF75">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="BG75">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BH75">
         <v>1000</v>
@@ -19430,13 +19430,13 @@
         <v>291</v>
       </c>
       <c r="F76">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G76">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H76">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="I76">
         <v>1.9</v>
@@ -19451,61 +19451,61 @@
         <v>1.01</v>
       </c>
       <c r="M76">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N76">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O76">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P76">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q76">
         <v>1.58</v>
       </c>
       <c r="R76">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="S76">
         <v>2.42</v>
       </c>
       <c r="T76">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="U76">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="V76">
         <v>2.1</v>
       </c>
       <c r="W76">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X76">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y76">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z76">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA76">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB76">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC76">
+        <v>10.5</v>
+      </c>
+      <c r="AD76">
+        <v>11</v>
+      </c>
+      <c r="AE76">
         <v>970</v>
-      </c>
-      <c r="AD76">
-        <v>11.5</v>
-      </c>
-      <c r="AE76">
-        <v>21</v>
       </c>
       <c r="AF76">
         <v>44</v>
@@ -19514,82 +19514,82 @@
         <v>21</v>
       </c>
       <c r="AH76">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AI76">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AJ76">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK76">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL76">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM76">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN76">
         <v>44</v>
       </c>
       <c r="AO76">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP76">
-        <v>2.16</v>
+        <v>18</v>
       </c>
       <c r="AQ76">
-        <v>2.16</v>
+        <v>11</v>
       </c>
       <c r="AR76">
-        <v>2.16</v>
+        <v>12</v>
       </c>
       <c r="AS76">
-        <v>2.16</v>
+        <v>17.5</v>
       </c>
       <c r="AT76">
-        <v>2.16</v>
+        <v>16</v>
       </c>
       <c r="AU76">
-        <v>1.79</v>
+        <v>9</v>
       </c>
       <c r="AV76">
-        <v>1.82</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW76">
-        <v>1.96</v>
+        <v>15</v>
       </c>
       <c r="AX76">
-        <v>2.06</v>
+        <v>6.4</v>
       </c>
       <c r="AY76">
-        <v>1.96</v>
+        <v>15.5</v>
       </c>
       <c r="AZ76">
-        <v>1.93</v>
+        <v>14</v>
       </c>
       <c r="BA76">
-        <v>2.04</v>
+        <v>10</v>
       </c>
       <c r="BB76">
-        <v>2.16</v>
+        <v>7.2</v>
       </c>
       <c r="BC76">
-        <v>2.16</v>
+        <v>6.8</v>
       </c>
       <c r="BD76">
-        <v>2.16</v>
+        <v>6.8</v>
       </c>
       <c r="BE76">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="BF76">
-        <v>2.06</v>
+        <v>6.4</v>
       </c>
       <c r="BG76">
-        <v>1.72</v>
+        <v>7.2</v>
       </c>
       <c r="BH76">
         <v>1000</v>
@@ -19720,10 +19720,10 @@
         <v>1.01</v>
       </c>
       <c r="V77">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W77">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X77">
         <v>1000</v>
@@ -19914,16 +19914,16 @@
         <v>293</v>
       </c>
       <c r="F78">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G78">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H78">
+        <v>2.42</v>
+      </c>
+      <c r="I78">
         <v>2.46</v>
-      </c>
-      <c r="I78">
-        <v>2.48</v>
       </c>
       <c r="J78">
         <v>3.5</v>
@@ -19962,10 +19962,10 @@
         <v>2.32</v>
       </c>
       <c r="V78">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W78">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X78">
         <v>15</v>
@@ -19974,7 +19974,7 @@
         <v>12</v>
       </c>
       <c r="Z78">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA78">
         <v>32</v>
@@ -20016,19 +20016,19 @@
         <v>80</v>
       </c>
       <c r="AN78">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO78">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP78">
         <v>13.5</v>
       </c>
       <c r="AQ78">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR78">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS78">
         <v>28</v>
@@ -20070,7 +20070,7 @@
         <v>70</v>
       </c>
       <c r="BF78">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG78">
         <v>16.5</v>
@@ -20091,7 +20091,7 @@
         <v>110</v>
       </c>
       <c r="BM78">
-        <v>15.5</v>
+        <v>50</v>
       </c>
       <c r="BN78">
         <v>6.2</v>
@@ -20156,16 +20156,16 @@
         <v>294</v>
       </c>
       <c r="F79">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G79">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H79">
+        <v>2.22</v>
+      </c>
+      <c r="I79">
         <v>2.24</v>
-      </c>
-      <c r="I79">
-        <v>2.28</v>
       </c>
       <c r="J79">
         <v>3.65</v>
@@ -20183,7 +20183,7 @@
         <v>4.3</v>
       </c>
       <c r="O79">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P79">
         <v>2.12</v>
@@ -20204,10 +20204,10 @@
         <v>2.32</v>
       </c>
       <c r="V79">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="W79">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X79">
         <v>16</v>
@@ -20237,7 +20237,7 @@
         <v>26</v>
       </c>
       <c r="AG79">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH79">
         <v>16.5</v>
@@ -20252,13 +20252,13 @@
         <v>38</v>
       </c>
       <c r="AL79">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM79">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN79">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO79">
         <v>15</v>
@@ -20267,7 +20267,7 @@
         <v>15</v>
       </c>
       <c r="AQ79">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR79">
         <v>13.5</v>
@@ -20309,7 +20309,7 @@
         <v>40</v>
       </c>
       <c r="BE79">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BF79">
         <v>28</v>
@@ -20428,13 +20428,13 @@
         <v>1.22</v>
       </c>
       <c r="P80">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q80">
         <v>1.68</v>
       </c>
       <c r="R80">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S80">
         <v>2.72</v>
@@ -20458,7 +20458,7 @@
         <v>48</v>
       </c>
       <c r="Z80">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AA80">
         <v>1000</v>
@@ -20557,67 +20557,67 @@
         <v>4.1</v>
       </c>
       <c r="BG80">
+        <v>14.5</v>
+      </c>
+      <c r="BH80">
+        <v>4.2</v>
+      </c>
+      <c r="BI80">
+        <v>3.25</v>
+      </c>
+      <c r="BJ80">
         <v>15</v>
       </c>
-      <c r="BH80">
-        <v>1000</v>
-      </c>
-      <c r="BI80">
-        <v>1.01</v>
-      </c>
-      <c r="BJ80">
-        <v>1000</v>
-      </c>
       <c r="BK80">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BL80">
         <v>1000</v>
       </c>
       <c r="BM80">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN80">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BO80">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BP80">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BQ80">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BR80">
         <v>1000</v>
       </c>
       <c r="BS80">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BT80">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BU80">
-        <v>9.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="BV80">
         <v>1000</v>
       </c>
       <c r="BW80">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX80">
         <v>1000</v>
       </c>
       <c r="BY80">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ80">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA80">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="CB80" t="s">
         <v>304</v>
@@ -20658,13 +20658,13 @@
         <v>4.3</v>
       </c>
       <c r="L81">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M81">
         <v>1.09</v>
       </c>
       <c r="N81">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O81">
         <v>1.43</v>
@@ -20682,10 +20682,10 @@
         <v>4.4</v>
       </c>
       <c r="T81">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U81">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V81">
         <v>1.13</v>
@@ -20724,7 +20724,7 @@
         <v>11</v>
       </c>
       <c r="AH81">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AI81">
         <v>180</v>
@@ -20802,64 +20802,64 @@
         <v>13.5</v>
       </c>
       <c r="BH81">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI81">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="BJ81">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK81">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BL81">
         <v>1000</v>
       </c>
       <c r="BM81">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN81">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BO81">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="BP81">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ81">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR81">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS81">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BT81">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU81">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BV81">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BW81">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX81">
         <v>1000</v>
       </c>
       <c r="BY81">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ81">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA81">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="CB81" t="s">
         <v>304</v>
@@ -20882,10 +20882,10 @@
         <v>297</v>
       </c>
       <c r="F82">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G82">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="H82">
         <v>1.43</v>
@@ -20894,10 +20894,10 @@
         <v>1.44</v>
       </c>
       <c r="J82">
+        <v>5</v>
+      </c>
+      <c r="K82">
         <v>5.1</v>
-      </c>
-      <c r="K82">
-        <v>5.2</v>
       </c>
       <c r="L82">
         <v>1.36</v>
@@ -20912,7 +20912,7 @@
         <v>1.27</v>
       </c>
       <c r="P82">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q82">
         <v>1.82</v>
@@ -20942,10 +20942,10 @@
         <v>8.4</v>
       </c>
       <c r="Z82">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA82">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AB82">
         <v>30</v>
@@ -20960,7 +20960,7 @@
         <v>15.5</v>
       </c>
       <c r="AF82">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AG82">
         <v>34</v>
@@ -21020,25 +21020,25 @@
         <v>30</v>
       </c>
       <c r="AZ82">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BA82">
         <v>34</v>
       </c>
       <c r="BB82">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BC82">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BD82">
         <v>38</v>
       </c>
       <c r="BE82">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BF82">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG82">
         <v>6.2</v>
@@ -21124,22 +21124,22 @@
         <v>298</v>
       </c>
       <c r="F83">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G83">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="H83">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I83">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J83">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K83">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L83">
         <v>1.35</v>
@@ -21148,142 +21148,142 @@
         <v>1.06</v>
       </c>
       <c r="N83">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O83">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P83">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="Q83">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="R83">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S83">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="T83">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="U83">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="V83">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W83">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X83">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y83">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Z83">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AA83">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB83">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AC83">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AD83">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AE83">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AF83">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AG83">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH83">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AI83">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AJ83">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AK83">
+        <v>27</v>
+      </c>
+      <c r="AL83">
         <v>38</v>
       </c>
-      <c r="AL83">
-        <v>50</v>
-      </c>
       <c r="AM83">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN83">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AO83">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AP83">
-        <v>3.3</v>
+        <v>14</v>
       </c>
       <c r="AQ83">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AR83">
-        <v>2.98</v>
+        <v>18</v>
       </c>
       <c r="AS83">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="AT83">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU83">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV83">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW83">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX83">
-        <v>2.86</v>
+        <v>15</v>
       </c>
       <c r="AY83">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ83">
-        <v>2.84</v>
+        <v>14</v>
       </c>
       <c r="BA83">
-        <v>3.15</v>
+        <v>8.6</v>
       </c>
       <c r="BB83">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC83">
-        <v>3.05</v>
+        <v>7.6</v>
       </c>
       <c r="BD83">
-        <v>3.1</v>
+        <v>8.4</v>
       </c>
       <c r="BE83">
-        <v>3.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF83">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="BG83">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH83">
         <v>1000</v>
@@ -21366,10 +21366,10 @@
         <v>299</v>
       </c>
       <c r="F84">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G84">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H84">
         <v>3.35</v>
@@ -21396,7 +21396,7 @@
         <v>1.42</v>
       </c>
       <c r="P84">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q84">
         <v>2.22</v>
@@ -21411,13 +21411,13 @@
         <v>1.98</v>
       </c>
       <c r="U84">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V84">
         <v>1.3</v>
       </c>
       <c r="W84">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="X84">
         <v>970</v>
@@ -22337,19 +22337,19 @@
         <v>1.85</v>
       </c>
       <c r="G88">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H88">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I88">
         <v>4.5</v>
       </c>
       <c r="J88">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="K88">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="L88">
         <v>1.01</v>
@@ -22361,7 +22361,7 @@
         <v>2.46</v>
       </c>
       <c r="O88">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P88">
         <v>2.46</v>
@@ -22382,10 +22382,10 @@
         <v>1.01</v>
       </c>
       <c r="V88">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W88">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X88">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-26.xlsx
@@ -1042,7 +1042,7 @@
     <t>FC Cincinnati</t>
   </si>
   <si>
-    <t>2026-09-25 00:27:30</t>
+    <t>2026-09-25 02:45:47</t>
   </si>
 </sst>
 </file>
@@ -1639,61 +1639,61 @@
         <v>1.9</v>
       </c>
       <c r="G2">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="H2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I2">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L2">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="O2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P2">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q2">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R2">
         <v>1.25</v>
       </c>
       <c r="S2">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T2">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U2">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V2">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W2">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="X2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z2">
         <v>42</v>
@@ -1765,19 +1765,19 @@
         <v>17</v>
       </c>
       <c r="AW2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX2">
         <v>9.4</v>
       </c>
       <c r="AY2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2">
         <v>19</v>
       </c>
       <c r="BA2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB2">
         <v>19.5</v>
@@ -1795,7 +1795,7 @@
         <v>16</v>
       </c>
       <c r="BG2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1878,25 +1878,25 @@
         <v>242</v>
       </c>
       <c r="F3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="H3">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I3">
         <v>2.2</v>
       </c>
       <c r="J3">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K3">
         <v>3.75</v>
       </c>
       <c r="L3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M3">
         <v>1.06</v>
@@ -1908,19 +1908,19 @@
         <v>1.27</v>
       </c>
       <c r="P3">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q3">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R3">
         <v>1.44</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T3">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U3">
         <v>2.28</v>
@@ -1932,7 +1932,7 @@
         <v>1.36</v>
       </c>
       <c r="X3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y3">
         <v>11.5</v>
@@ -1959,7 +1959,7 @@
         <v>29</v>
       </c>
       <c r="AG3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
         <v>16</v>
@@ -1968,7 +1968,7 @@
         <v>34</v>
       </c>
       <c r="AJ3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK3">
         <v>48</v>
@@ -1989,10 +1989,10 @@
         <v>14</v>
       </c>
       <c r="AQ3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR3">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AS3">
         <v>22</v>
@@ -2025,7 +2025,7 @@
         <v>55</v>
       </c>
       <c r="BC3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BD3">
         <v>1.03</v>
@@ -2034,7 +2034,7 @@
         <v>1.03</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BG3">
         <v>12</v>
@@ -2120,64 +2120,64 @@
         <v>243</v>
       </c>
       <c r="F4">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="G4">
         <v>1.74</v>
       </c>
       <c r="H4">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M4">
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="Q4">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T4">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U4">
         <v>1.8</v>
       </c>
       <c r="V4">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W4">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X4">
         <v>12.5</v>
       </c>
       <c r="Y4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z4">
         <v>50</v>
@@ -2204,13 +2204,13 @@
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI4">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK4">
         <v>21</v>
@@ -2219,25 +2219,25 @@
         <v>46</v>
       </c>
       <c r="AM4">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="AN4">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO4">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AP4">
         <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR4">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="AS4">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT4">
         <v>6.2</v>
@@ -2249,10 +2249,10 @@
         <v>20</v>
       </c>
       <c r="AW4">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AX4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY4">
         <v>9.199999999999999</v>
@@ -2261,10 +2261,10 @@
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC4">
         <v>17.5</v>
@@ -2273,73 +2273,73 @@
         <v>38</v>
       </c>
       <c r="BE4">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF4">
         <v>11.5</v>
       </c>
       <c r="BG4">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI4">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="CB4" t="s">
         <v>342</v>
@@ -2362,166 +2362,166 @@
         <v>244</v>
       </c>
       <c r="F5">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="G5">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="H5">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="I5">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="J5">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="L5">
         <v>1.28</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N5">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="O5">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="P5">
+        <v>2.68</v>
+      </c>
+      <c r="Q5">
+        <v>1.54</v>
+      </c>
+      <c r="R5">
+        <v>1.66</v>
+      </c>
+      <c r="S5">
+        <v>2.36</v>
+      </c>
+      <c r="T5">
+        <v>1.65</v>
+      </c>
+      <c r="U5">
         <v>2.2</v>
       </c>
-      <c r="Q5">
-        <v>1.6</v>
-      </c>
-      <c r="R5">
-        <v>1.46</v>
-      </c>
-      <c r="S5">
-        <v>2.56</v>
-      </c>
-      <c r="T5">
-        <v>1.6</v>
-      </c>
-      <c r="U5">
-        <v>2.16</v>
-      </c>
       <c r="V5">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W5">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y5">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE5">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG5">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI5">
         <v>65</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK5">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP5">
-        <v>1.82</v>
+        <v>18</v>
       </c>
       <c r="AQ5">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AR5">
-        <v>1.82</v>
+        <v>9</v>
       </c>
       <c r="AS5">
-        <v>1.82</v>
+        <v>10</v>
       </c>
       <c r="AT5">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU5">
-        <v>1.57</v>
+        <v>9.4</v>
       </c>
       <c r="AV5">
-        <v>1.82</v>
+        <v>18.5</v>
       </c>
       <c r="AW5">
-        <v>1.77</v>
+        <v>9.6</v>
       </c>
       <c r="AX5">
-        <v>1.6</v>
+        <v>10</v>
       </c>
       <c r="AY5">
-        <v>1.57</v>
+        <v>8</v>
       </c>
       <c r="AZ5">
-        <v>1.82</v>
+        <v>14</v>
       </c>
       <c r="BA5">
-        <v>1.77</v>
+        <v>9.4</v>
       </c>
       <c r="BB5">
-        <v>1.82</v>
+        <v>12.5</v>
       </c>
       <c r="BC5">
-        <v>1.66</v>
+        <v>12</v>
       </c>
       <c r="BD5">
-        <v>1.82</v>
+        <v>21</v>
       </c>
       <c r="BE5">
-        <v>1.82</v>
+        <v>9.6</v>
       </c>
       <c r="BF5">
-        <v>1.82</v>
+        <v>5.4</v>
       </c>
       <c r="BG5">
-        <v>1.82</v>
+        <v>34</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2610,19 +2610,19 @@
         <v>3.85</v>
       </c>
       <c r="H6">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I6">
         <v>2.12</v>
       </c>
       <c r="J6">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K6">
         <v>4</v>
       </c>
       <c r="L6">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="M6">
         <v>1.05</v>
@@ -2637,22 +2637,22 @@
         <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R6">
         <v>1.47</v>
       </c>
       <c r="S6">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T6">
         <v>1.69</v>
       </c>
       <c r="U6">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V6">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W6">
         <v>1.35</v>
@@ -2679,7 +2679,7 @@
         <v>11</v>
       </c>
       <c r="AE6">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AF6">
         <v>32</v>
@@ -2688,13 +2688,13 @@
         <v>18.5</v>
       </c>
       <c r="AH6">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI6">
         <v>36</v>
       </c>
       <c r="AJ6">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK6">
         <v>50</v>
@@ -2724,7 +2724,7 @@
         <v>22</v>
       </c>
       <c r="AT6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU6">
         <v>8</v>
@@ -2736,7 +2736,7 @@
         <v>18</v>
       </c>
       <c r="AX6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY6">
         <v>13.5</v>
@@ -2745,16 +2745,16 @@
         <v>14.5</v>
       </c>
       <c r="BA6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB6">
         <v>7</v>
       </c>
       <c r="BC6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE6">
         <v>7</v>
@@ -2769,7 +2769,7 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
@@ -2787,7 +2787,7 @@
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP6">
         <v>1000</v>
@@ -2805,7 +2805,7 @@
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2864,22 +2864,22 @@
         <v>3.6</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M7">
         <v>1.09</v>
       </c>
       <c r="N7">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
         <v>1.4</v>
       </c>
       <c r="P7">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q7">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R7">
         <v>1.29</v>
@@ -2894,13 +2894,13 @@
         <v>1.97</v>
       </c>
       <c r="V7">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W7">
         <v>1.93</v>
       </c>
       <c r="X7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y7">
         <v>16.5</v>
@@ -2915,7 +2915,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD7">
         <v>19</v>
@@ -2963,19 +2963,19 @@
         <v>26</v>
       </c>
       <c r="AS7">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7">
         <v>7.2</v>
       </c>
       <c r="AU7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV7">
         <v>15.5</v>
       </c>
       <c r="AW7">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX7">
         <v>10.5</v>
@@ -2987,10 +2987,10 @@
         <v>18</v>
       </c>
       <c r="BA7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB7">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC7">
         <v>20</v>
@@ -3005,7 +3005,7 @@
         <v>15.5</v>
       </c>
       <c r="BG7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -3088,76 +3088,76 @@
         <v>247</v>
       </c>
       <c r="F8">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G8">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H8">
         <v>5.1</v>
       </c>
       <c r="I8">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K8">
         <v>3.9</v>
       </c>
       <c r="L8">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M8">
         <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O8">
         <v>1.39</v>
       </c>
       <c r="P8">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q8">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="R8">
         <v>1.28</v>
       </c>
       <c r="S8">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T8">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U8">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V8">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W8">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X8">
         <v>14.5</v>
       </c>
       <c r="Y8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z8">
         <v>44</v>
       </c>
       <c r="AA8">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC8">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD8">
         <v>23</v>
@@ -3169,16 +3169,16 @@
         <v>10.5</v>
       </c>
       <c r="AG8">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI8">
         <v>95</v>
       </c>
       <c r="AJ8">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AK8">
         <v>23</v>
@@ -3190,7 +3190,7 @@
         <v>180</v>
       </c>
       <c r="AN8">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AO8">
         <v>160</v>
@@ -3202,10 +3202,10 @@
         <v>13</v>
       </c>
       <c r="AR8">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AS8">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AT8">
         <v>6.4</v>
@@ -3217,7 +3217,7 @@
         <v>17.5</v>
       </c>
       <c r="AW8">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX8">
         <v>8.800000000000001</v>
@@ -3229,7 +3229,7 @@
         <v>19.5</v>
       </c>
       <c r="BA8">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB8">
         <v>15.5</v>
@@ -3238,16 +3238,16 @@
         <v>18</v>
       </c>
       <c r="BD8">
-        <v>32</v>
+        <v>6.2</v>
       </c>
       <c r="BE8">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG8">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH8">
         <v>3.6</v>
@@ -3268,7 +3268,7 @@
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO8">
         <v>3.3</v>
@@ -3280,13 +3280,13 @@
         <v>9.4</v>
       </c>
       <c r="BR8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS8">
         <v>23</v>
       </c>
       <c r="BT8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU8">
         <v>6.6</v>
@@ -3304,7 +3304,7 @@
         <v>46</v>
       </c>
       <c r="BZ8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA8">
         <v>20</v>
@@ -3330,7 +3330,7 @@
         <v>248</v>
       </c>
       <c r="F9">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G9">
         <v>2.14</v>
@@ -3348,13 +3348,13 @@
         <v>3.8</v>
       </c>
       <c r="L9">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M9">
         <v>1.07</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O9">
         <v>1.32</v>
@@ -3363,25 +3363,25 @@
         <v>2</v>
       </c>
       <c r="Q9">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="R9">
         <v>1.39</v>
       </c>
       <c r="S9">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T9">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U9">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V9">
         <v>1.33</v>
       </c>
       <c r="W9">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="X9">
         <v>15</v>
@@ -3444,7 +3444,7 @@
         <v>13</v>
       </c>
       <c r="AR9">
-        <v>9.6</v>
+        <v>24</v>
       </c>
       <c r="AS9">
         <v>11.5</v>
@@ -3471,7 +3471,7 @@
         <v>15.5</v>
       </c>
       <c r="BA9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB9">
         <v>21</v>
@@ -3480,10 +3480,10 @@
         <v>20</v>
       </c>
       <c r="BD9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF9">
         <v>13</v>
@@ -3572,16 +3572,16 @@
         <v>249</v>
       </c>
       <c r="F10">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G10">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H10">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J10">
         <v>3.55</v>
@@ -3602,19 +3602,19 @@
         <v>1.29</v>
       </c>
       <c r="P10">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q10">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R10">
         <v>1.42</v>
       </c>
       <c r="S10">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T10">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="U10">
         <v>2.28</v>
@@ -3638,7 +3638,7 @@
         <v>55</v>
       </c>
       <c r="AB10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC10">
         <v>8.4</v>
@@ -3674,7 +3674,7 @@
         <v>95</v>
       </c>
       <c r="AN10">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO10">
         <v>30</v>
@@ -3689,7 +3689,7 @@
         <v>17.5</v>
       </c>
       <c r="AS10">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT10">
         <v>10.5</v>
@@ -3701,7 +3701,7 @@
         <v>11</v>
       </c>
       <c r="AW10">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AX10">
         <v>15.5</v>
@@ -3710,22 +3710,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA10">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB10">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BC10">
         <v>20</v>
       </c>
       <c r="BD10">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BE10">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF10">
         <v>18</v>
@@ -3814,31 +3814,31 @@
         <v>250</v>
       </c>
       <c r="F11">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G11">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H11">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I11">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J11">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K11">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M11">
         <v>1.07</v>
       </c>
       <c r="N11">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O11">
         <v>1.32</v>
@@ -3847,37 +3847,37 @@
         <v>1.86</v>
       </c>
       <c r="Q11">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R11">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S11">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T11">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U11">
         <v>2.08</v>
       </c>
       <c r="V11">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W11">
         <v>1.37</v>
       </c>
       <c r="X11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z11">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB11">
         <v>16</v>
@@ -3895,7 +3895,7 @@
         <v>26</v>
       </c>
       <c r="AG11">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AH11">
         <v>22</v>
@@ -3952,22 +3952,22 @@
         <v>12.5</v>
       </c>
       <c r="AZ11">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA11">
         <v>29</v>
       </c>
       <c r="BB11">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BC11">
         <v>32</v>
       </c>
       <c r="BD11">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE11">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF11">
         <v>29</v>
@@ -4056,10 +4056,10 @@
         <v>251</v>
       </c>
       <c r="F12">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="G12">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H12">
         <v>6.2</v>
@@ -4068,7 +4068,7 @@
         <v>7.4</v>
       </c>
       <c r="J12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K12">
         <v>4.5</v>
@@ -4080,34 +4080,34 @@
         <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="O12">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="P12">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="Q12">
+        <v>1.98</v>
+      </c>
+      <c r="R12">
+        <v>1.34</v>
+      </c>
+      <c r="S12">
+        <v>3.5</v>
+      </c>
+      <c r="T12">
         <v>2.06</v>
       </c>
-      <c r="R12">
-        <v>1.33</v>
-      </c>
-      <c r="S12">
-        <v>3.75</v>
-      </c>
-      <c r="T12">
-        <v>2.1</v>
-      </c>
       <c r="U12">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="V12">
         <v>1.15</v>
       </c>
       <c r="W12">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="X12">
         <v>17</v>
@@ -4122,10 +4122,10 @@
         <v>250</v>
       </c>
       <c r="AB12">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD12">
         <v>29</v>
@@ -4134,7 +4134,7 @@
         <v>130</v>
       </c>
       <c r="AF12">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG12">
         <v>10.5</v>
@@ -4146,7 +4146,7 @@
         <v>120</v>
       </c>
       <c r="AJ12">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AK12">
         <v>24</v>
@@ -4158,25 +4158,25 @@
         <v>190</v>
       </c>
       <c r="AN12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO12">
         <v>180</v>
       </c>
       <c r="AP12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ12">
         <v>15</v>
       </c>
       <c r="AR12">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AS12">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT12">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU12">
         <v>8.800000000000001</v>
@@ -4185,7 +4185,7 @@
         <v>17</v>
       </c>
       <c r="AW12">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX12">
         <v>7.8</v>
@@ -4194,28 +4194,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ12">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BA12">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC12">
         <v>16</v>
       </c>
       <c r="BD12">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BE12">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF12">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG12">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -4304,16 +4304,16 @@
         <v>3.05</v>
       </c>
       <c r="H13">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I13">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="J13">
         <v>3.7</v>
       </c>
       <c r="K13">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -4328,13 +4328,13 @@
         <v>1.22</v>
       </c>
       <c r="P13">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q13">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R13">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="S13">
         <v>2.6</v>
@@ -4540,16 +4540,16 @@
         <v>253</v>
       </c>
       <c r="F14">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G14">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H14">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I14">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J14">
         <v>3.15</v>
@@ -4567,52 +4567,52 @@
         <v>2.8</v>
       </c>
       <c r="O14">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P14">
         <v>1.6</v>
       </c>
       <c r="Q14">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R14">
         <v>1.23</v>
       </c>
       <c r="S14">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T14">
         <v>1.96</v>
       </c>
       <c r="U14">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V14">
         <v>1.51</v>
       </c>
       <c r="W14">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y14">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z14">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA14">
         <v>60</v>
       </c>
       <c r="AB14">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC14">
         <v>7.4</v>
       </c>
       <c r="AD14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE14">
         <v>42</v>
@@ -4621,7 +4621,7 @@
         <v>22</v>
       </c>
       <c r="AG14">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH14">
         <v>24</v>
@@ -4633,7 +4633,7 @@
         <v>65</v>
       </c>
       <c r="AK14">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL14">
         <v>70</v>
@@ -4642,10 +4642,10 @@
         <v>170</v>
       </c>
       <c r="AN14">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP14">
         <v>8.4</v>
@@ -4657,49 +4657,49 @@
         <v>15</v>
       </c>
       <c r="AS14">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT14">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU14">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW14">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX14">
         <v>16</v>
       </c>
       <c r="AY14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ14">
         <v>18</v>
       </c>
       <c r="BA14">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BB14">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC14">
         <v>32</v>
       </c>
       <c r="BD14">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BE14">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BF14">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BG14">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4782,22 +4782,22 @@
         <v>254</v>
       </c>
       <c r="F15">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="G15">
         <v>3.05</v>
       </c>
       <c r="H15">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I15">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J15">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K15">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4806,25 +4806,25 @@
         <v>1.07</v>
       </c>
       <c r="N15">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O15">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P15">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q15">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R15">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S15">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T15">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U15">
         <v>2.12</v>
@@ -4836,7 +4836,7 @@
         <v>1.48</v>
       </c>
       <c r="X15">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y15">
         <v>11</v>
@@ -4899,19 +4899,19 @@
         <v>14.5</v>
       </c>
       <c r="AS15">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AT15">
         <v>10</v>
       </c>
       <c r="AU15">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV15">
         <v>10.5</v>
       </c>
       <c r="AW15">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AX15">
         <v>17</v>
@@ -4920,28 +4920,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ15">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA15">
         <v>5.9</v>
       </c>
       <c r="BB15">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BC15">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BD15">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BE15">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF15">
         <v>21</v>
       </c>
       <c r="BG15">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -5024,22 +5024,22 @@
         <v>255</v>
       </c>
       <c r="F16">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G16">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H16">
         <v>3.4</v>
       </c>
       <c r="I16">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J16">
         <v>3.6</v>
       </c>
       <c r="K16">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -5063,10 +5063,10 @@
         <v>1.39</v>
       </c>
       <c r="S16">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T16">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U16">
         <v>2.18</v>
@@ -5075,16 +5075,16 @@
         <v>1.38</v>
       </c>
       <c r="W16">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X16">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Y16">
         <v>14.5</v>
       </c>
       <c r="Z16">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA16">
         <v>75</v>
@@ -5126,7 +5126,7 @@
         <v>110</v>
       </c>
       <c r="AN16">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AO16">
         <v>40</v>
@@ -5141,13 +5141,13 @@
         <v>21</v>
       </c>
       <c r="AS16">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT16">
         <v>9</v>
       </c>
       <c r="AU16">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV16">
         <v>12.5</v>
@@ -5177,10 +5177,10 @@
         <v>6.4</v>
       </c>
       <c r="BE16">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG16">
         <v>6.4</v>
@@ -5281,7 +5281,7 @@
         <v>2.92</v>
       </c>
       <c r="K17">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -5290,7 +5290,7 @@
         <v>1.06</v>
       </c>
       <c r="N17">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="O17">
         <v>1.42</v>
@@ -5514,7 +5514,7 @@
         <v>3.85</v>
       </c>
       <c r="H18">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I18">
         <v>2.3</v>
@@ -5532,7 +5532,7 @@
         <v>1.06</v>
       </c>
       <c r="N18">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O18">
         <v>1.31</v>
@@ -5541,10 +5541,10 @@
         <v>1.96</v>
       </c>
       <c r="Q18">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="R18">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S18">
         <v>3.2</v>
@@ -5577,25 +5577,25 @@
         <v>15</v>
       </c>
       <c r="AC18">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE18">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF18">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG18">
         <v>16</v>
       </c>
       <c r="AH18">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI18">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ18">
         <v>80</v>
@@ -5613,19 +5613,19 @@
         <v>42</v>
       </c>
       <c r="AO18">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP18">
         <v>13</v>
       </c>
       <c r="AQ18">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS18">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT18">
         <v>12</v>
@@ -5637,7 +5637,7 @@
         <v>9.6</v>
       </c>
       <c r="AW18">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX18">
         <v>20</v>
@@ -5649,25 +5649,25 @@
         <v>15</v>
       </c>
       <c r="BA18">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB18">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC18">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD18">
         <v>38</v>
       </c>
       <c r="BE18">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF18">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BG18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5750,19 +5750,19 @@
         <v>258</v>
       </c>
       <c r="F19">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G19">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H19">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I19">
         <v>6.4</v>
       </c>
       <c r="J19">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K19">
         <v>4.6</v>
@@ -5777,22 +5777,22 @@
         <v>4.3</v>
       </c>
       <c r="O19">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P19">
         <v>2.16</v>
       </c>
       <c r="Q19">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R19">
         <v>1.46</v>
       </c>
       <c r="S19">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="T19">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="U19">
         <v>2.06</v>
@@ -5801,7 +5801,7 @@
         <v>1.19</v>
       </c>
       <c r="W19">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X19">
         <v>23</v>
@@ -5816,7 +5816,7 @@
         <v>180</v>
       </c>
       <c r="AB19">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC19">
         <v>10.5</v>
@@ -5828,10 +5828,10 @@
         <v>80</v>
       </c>
       <c r="AF19">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG19">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH19">
         <v>21</v>
@@ -5864,13 +5864,13 @@
         <v>18.5</v>
       </c>
       <c r="AR19">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AS19">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT19">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU19">
         <v>8.800000000000001</v>
@@ -5879,7 +5879,7 @@
         <v>16.5</v>
       </c>
       <c r="AW19">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AX19">
         <v>9.199999999999999</v>
@@ -5891,7 +5891,7 @@
         <v>18</v>
       </c>
       <c r="BA19">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BB19">
         <v>14</v>
@@ -5900,16 +5900,16 @@
         <v>14.5</v>
       </c>
       <c r="BD19">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE19">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF19">
         <v>7.2</v>
       </c>
       <c r="BG19">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -6246,7 +6246,7 @@
         <v>5.9</v>
       </c>
       <c r="J21">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K21">
         <v>6.6</v>
@@ -6258,7 +6258,7 @@
         <v>1.01</v>
       </c>
       <c r="N21">
-        <v>2.48</v>
+        <v>2.96</v>
       </c>
       <c r="O21">
         <v>1.02</v>
@@ -6270,7 +6270,7 @@
         <v>1.48</v>
       </c>
       <c r="R21">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S21">
         <v>2.02</v>
@@ -6476,22 +6476,22 @@
         <v>261</v>
       </c>
       <c r="F22">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="G22">
-        <v>1000</v>
+        <v>1.88</v>
       </c>
       <c r="H22">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="I22">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J22">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="K22">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6500,22 +6500,22 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>1.13</v>
+        <v>2.5</v>
       </c>
       <c r="O22">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="P22">
-        <v>1.13</v>
+        <v>1.8</v>
       </c>
       <c r="Q22">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="R22">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="S22">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -6524,10 +6524,10 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="W22">
-        <v>1.02</v>
+        <v>2.12</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6718,22 +6718,22 @@
         <v>262</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="G23">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="H23">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="I23">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="J23">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K23">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6742,22 +6742,22 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="O23">
         <v>1.02</v>
       </c>
       <c r="P23">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="Q23">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="R23">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S23">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="T23">
         <v>1.01</v>
@@ -6766,10 +6766,10 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="W23">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6969,7 +6969,7 @@
         <v>3.2</v>
       </c>
       <c r="I24">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J24">
         <v>3.7</v>
@@ -7008,7 +7008,7 @@
         <v>2.36</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W24">
         <v>1.72</v>
@@ -7928,16 +7928,16 @@
         <v>267</v>
       </c>
       <c r="F28">
+        <v>2.78</v>
+      </c>
+      <c r="G28">
         <v>2.8</v>
       </c>
-      <c r="G28">
-        <v>2.82</v>
-      </c>
       <c r="H28">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J28">
         <v>3.25</v>
@@ -7946,22 +7946,22 @@
         <v>3.3</v>
       </c>
       <c r="L28">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M28">
         <v>1.1</v>
       </c>
       <c r="N28">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O28">
         <v>1.44</v>
       </c>
       <c r="P28">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q28">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R28">
         <v>1.27</v>
@@ -7970,16 +7970,16 @@
         <v>4.4</v>
       </c>
       <c r="T28">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="U28">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V28">
         <v>1.5</v>
       </c>
       <c r="W28">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X28">
         <v>10.5</v>
@@ -8030,7 +8030,7 @@
         <v>140</v>
       </c>
       <c r="AN28">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO28">
         <v>40</v>
@@ -8081,7 +8081,7 @@
         <v>48</v>
       </c>
       <c r="BE28">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BF28">
         <v>30</v>
@@ -8908,7 +8908,7 @@
         <v>6.4</v>
       </c>
       <c r="J32">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K32">
         <v>4.6</v>
@@ -8920,7 +8920,7 @@
         <v>1.05</v>
       </c>
       <c r="N32">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O32">
         <v>1.24</v>
@@ -8929,19 +8929,19 @@
         <v>2.3</v>
       </c>
       <c r="Q32">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R32">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S32">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T32">
         <v>1.79</v>
       </c>
       <c r="U32">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V32">
         <v>1.18</v>
@@ -9049,13 +9049,13 @@
         <v>26</v>
       </c>
       <c r="BE32">
-        <v>13.5</v>
+        <v>70</v>
       </c>
       <c r="BF32">
         <v>7</v>
       </c>
       <c r="BG32">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -9141,10 +9141,10 @@
         <v>2.68</v>
       </c>
       <c r="G33">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H33">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I33">
         <v>2.76</v>
@@ -9162,37 +9162,37 @@
         <v>1.05</v>
       </c>
       <c r="N33">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O33">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P33">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q33">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R33">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S33">
         <v>2.82</v>
       </c>
       <c r="T33">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U33">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V33">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W33">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X33">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y33">
         <v>14.5</v>
@@ -9201,7 +9201,7 @@
         <v>20</v>
       </c>
       <c r="AA33">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AB33">
         <v>14</v>
@@ -9225,10 +9225,10 @@
         <v>16</v>
       </c>
       <c r="AI33">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ33">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK33">
         <v>29</v>
@@ -9255,7 +9255,7 @@
         <v>17</v>
       </c>
       <c r="AS33">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AT33">
         <v>12</v>
@@ -9282,7 +9282,7 @@
         <v>9.4</v>
       </c>
       <c r="BB33">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC33">
         <v>21</v>
@@ -9291,7 +9291,7 @@
         <v>9.4</v>
       </c>
       <c r="BE33">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF33">
         <v>16.5</v>
@@ -9386,19 +9386,19 @@
         <v>1.43</v>
       </c>
       <c r="H34">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I34">
         <v>8.4</v>
       </c>
       <c r="J34">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K34">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L34">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M34">
         <v>1.02</v>
@@ -9416,16 +9416,16 @@
         <v>1.43</v>
       </c>
       <c r="R34">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="S34">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T34">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U34">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V34">
         <v>1.13</v>
@@ -9494,10 +9494,10 @@
         <v>28</v>
       </c>
       <c r="AR34">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AS34">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT34">
         <v>12.5</v>
@@ -9509,7 +9509,7 @@
         <v>21</v>
       </c>
       <c r="AW34">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX34">
         <v>10.5</v>
@@ -9521,7 +9521,7 @@
         <v>18</v>
       </c>
       <c r="BA34">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB34">
         <v>12</v>
@@ -9533,13 +9533,13 @@
         <v>18.5</v>
       </c>
       <c r="BE34">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF34">
         <v>3.85</v>
       </c>
       <c r="BG34">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9551,7 +9551,7 @@
         <v>1000</v>
       </c>
       <c r="BK34">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BL34">
         <v>1000</v>
@@ -9625,13 +9625,13 @@
         <v>1.75</v>
       </c>
       <c r="G35">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H35">
         <v>1.85</v>
       </c>
       <c r="I35">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J35">
         <v>1.12</v>
@@ -9670,10 +9670,10 @@
         <v>1.01</v>
       </c>
       <c r="V35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -9864,7 +9864,7 @@
         <v>275</v>
       </c>
       <c r="F36">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G36">
         <v>1.95</v>
@@ -9888,7 +9888,7 @@
         <v>1.08</v>
       </c>
       <c r="N36">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O36">
         <v>1.37</v>
@@ -9903,13 +9903,13 @@
         <v>1.31</v>
       </c>
       <c r="S36">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T36">
+        <v>1.99</v>
+      </c>
+      <c r="U36">
         <v>1.96</v>
-      </c>
-      <c r="U36">
-        <v>1.97</v>
       </c>
       <c r="V36">
         <v>1.26</v>
@@ -9966,7 +9966,7 @@
         <v>130</v>
       </c>
       <c r="AN36">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO36">
         <v>80</v>
@@ -10017,7 +10017,7 @@
         <v>34</v>
       </c>
       <c r="BE36">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF36">
         <v>13</v>
@@ -10029,61 +10029,61 @@
         <v>1000</v>
       </c>
       <c r="BI36">
+        <v>1.24</v>
+      </c>
+      <c r="BJ36">
+        <v>1000</v>
+      </c>
+      <c r="BK36">
         <v>1.2</v>
       </c>
-      <c r="BJ36">
-        <v>1000</v>
-      </c>
-      <c r="BK36">
-        <v>1.01</v>
-      </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BN36">
         <v>1000</v>
       </c>
       <c r="BO36">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BP36">
         <v>1000</v>
       </c>
       <c r="BQ36">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BR36">
         <v>1000</v>
       </c>
       <c r="BS36">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BT36">
         <v>1000</v>
       </c>
       <c r="BU36">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BV36">
         <v>1000</v>
       </c>
       <c r="BW36">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BZ36">
         <v>1000</v>
       </c>
       <c r="CA36">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="CB36" t="s">
         <v>342</v>
@@ -10378,7 +10378,7 @@
         <v>1.25</v>
       </c>
       <c r="P38">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -10390,7 +10390,7 @@
         <v>2.92</v>
       </c>
       <c r="T38">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U38">
         <v>1.81</v>
@@ -10399,7 +10399,7 @@
         <v>3.05</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X38">
         <v>22</v>
@@ -10435,7 +10435,7 @@
         <v>32</v>
       </c>
       <c r="AI38">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ38">
         <v>330</v>
@@ -10459,34 +10459,34 @@
         <v>1.01</v>
       </c>
       <c r="AQ38">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR38">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AS38">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AT38">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU38">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV38">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW38">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AX38">
         <v>1.01</v>
       </c>
       <c r="AY38">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ38">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA38">
         <v>1.01</v>
@@ -10507,7 +10507,7 @@
         <v>1.01</v>
       </c>
       <c r="BG38">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH38">
         <v>1000</v>
@@ -10590,7 +10590,7 @@
         <v>278</v>
       </c>
       <c r="F39">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="G39">
         <v>4.8</v>
@@ -10599,10 +10599,10 @@
         <v>2</v>
       </c>
       <c r="I39">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J39">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K39">
         <v>3.6</v>
@@ -10611,37 +10611,37 @@
         <v>1.01</v>
       </c>
       <c r="M39">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N39">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O39">
         <v>1.44</v>
       </c>
       <c r="P39">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Q39">
         <v>2.32</v>
       </c>
       <c r="R39">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S39">
         <v>4.3</v>
       </c>
       <c r="T39">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="U39">
         <v>1.74</v>
       </c>
       <c r="V39">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W39">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X39">
         <v>970</v>
@@ -10698,25 +10698,25 @@
         <v>1000</v>
       </c>
       <c r="AP39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ39">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AR39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS39">
         <v>1.03</v>
       </c>
       <c r="AT39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU39">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW39">
         <v>1.03</v>
@@ -10791,7 +10791,7 @@
         <v>1000</v>
       </c>
       <c r="BU39">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="BV39">
         <v>1000</v>
@@ -10853,7 +10853,7 @@
         <v>1.01</v>
       </c>
       <c r="M40">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N40">
         <v>4.7</v>
@@ -10973,7 +10973,7 @@
         <v>2.32</v>
       </c>
       <c r="BA40">
-        <v>2.44</v>
+        <v>16</v>
       </c>
       <c r="BB40">
         <v>2.52</v>
@@ -11074,16 +11074,16 @@
         <v>280</v>
       </c>
       <c r="F41">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="G41">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="H41">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="I41">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="J41">
         <v>4</v>
@@ -11104,28 +11104,28 @@
         <v>1.17</v>
       </c>
       <c r="P41">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q41">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R41">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="S41">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T41">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U41">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="V41">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W41">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="X41">
         <v>34</v>
@@ -11134,10 +11134,10 @@
         <v>18</v>
       </c>
       <c r="Z41">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA41">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB41">
         <v>19</v>
@@ -11146,16 +11146,16 @@
         <v>13</v>
       </c>
       <c r="AD41">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE41">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF41">
         <v>24</v>
       </c>
       <c r="AG41">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH41">
         <v>15</v>
@@ -11164,7 +11164,7 @@
         <v>28</v>
       </c>
       <c r="AJ41">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AK41">
         <v>26</v>
@@ -11176,22 +11176,22 @@
         <v>60</v>
       </c>
       <c r="AN41">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO41">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AP41">
         <v>20</v>
       </c>
       <c r="AQ41">
-        <v>5.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR41">
         <v>18.5</v>
       </c>
       <c r="AS41">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT41">
         <v>16</v>
@@ -11206,7 +11206,7 @@
         <v>19.5</v>
       </c>
       <c r="AX41">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AY41">
         <v>11</v>
@@ -11215,22 +11215,22 @@
         <v>12.5</v>
       </c>
       <c r="BA41">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB41">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BC41">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BD41">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BE41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BF41">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG41">
         <v>10.5</v>
@@ -11558,19 +11558,19 @@
         <v>282</v>
       </c>
       <c r="F43">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G43">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H43">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="I43">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="J43">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K43">
         <v>5.7</v>
@@ -11597,16 +11597,16 @@
         <v>1.98</v>
       </c>
       <c r="S43">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="T43">
         <v>1.45</v>
       </c>
       <c r="U43">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="V43">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="W43">
         <v>1.23</v>
@@ -11618,7 +11618,7 @@
         <v>19.5</v>
       </c>
       <c r="Z43">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA43">
         <v>23</v>
@@ -11627,13 +11627,13 @@
         <v>36</v>
       </c>
       <c r="AC43">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD43">
         <v>11.5</v>
       </c>
       <c r="AE43">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AF43">
         <v>55</v>
@@ -11666,7 +11666,7 @@
         <v>5</v>
       </c>
       <c r="AP43">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ43">
         <v>16</v>
@@ -11678,19 +11678,19 @@
         <v>16.5</v>
       </c>
       <c r="AT43">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU43">
         <v>12</v>
       </c>
       <c r="AV43">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW43">
         <v>12.5</v>
       </c>
       <c r="AX43">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AY43">
         <v>18</v>
@@ -11702,13 +11702,13 @@
         <v>18</v>
       </c>
       <c r="BB43">
+        <v>7.6</v>
+      </c>
+      <c r="BC43">
+        <v>7.2</v>
+      </c>
+      <c r="BD43">
         <v>6.8</v>
-      </c>
-      <c r="BC43">
-        <v>6.4</v>
-      </c>
-      <c r="BD43">
-        <v>6.2</v>
       </c>
       <c r="BE43">
         <v>36</v>
@@ -11806,10 +11806,10 @@
         <v>1.76</v>
       </c>
       <c r="H44">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I44">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J44">
         <v>4.3</v>
@@ -11824,10 +11824,10 @@
         <v>1.02</v>
       </c>
       <c r="N44">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="O44">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P44">
         <v>2.36</v>
@@ -11839,16 +11839,16 @@
         <v>1.52</v>
       </c>
       <c r="S44">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T44">
         <v>1.62</v>
       </c>
       <c r="U44">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V44">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W44">
         <v>2.3</v>
@@ -11908,16 +11908,16 @@
         <v>1000</v>
       </c>
       <c r="AP44">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AQ44">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AR44">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AS44">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AT44">
         <v>1.32</v>
@@ -11926,40 +11926,40 @@
         <v>6.2</v>
       </c>
       <c r="AV44">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AW44">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AX44">
-        <v>1.32</v>
+        <v>8</v>
       </c>
       <c r="AY44">
         <v>6.4</v>
       </c>
       <c r="AZ44">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BA44">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BB44">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BC44">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BD44">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BE44">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BF44">
         <v>5.2</v>
       </c>
       <c r="BG44">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BH44">
         <v>1000</v>
@@ -12042,22 +12042,22 @@
         <v>284</v>
       </c>
       <c r="F45">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="G45">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="H45">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="I45">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="J45">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="K45">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="L45">
         <v>1.01</v>
@@ -12066,34 +12066,34 @@
         <v>1.02</v>
       </c>
       <c r="N45">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="O45">
         <v>1.24</v>
       </c>
       <c r="P45">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q45">
         <v>1.73</v>
       </c>
       <c r="R45">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S45">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="T45">
         <v>1.62</v>
       </c>
       <c r="U45">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V45">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W45">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="X45">
         <v>1000</v>
@@ -12198,7 +12198,7 @@
         <v>1.08</v>
       </c>
       <c r="BF45">
-        <v>1.08</v>
+        <v>8.4</v>
       </c>
       <c r="BG45">
         <v>1.08</v>
@@ -12287,7 +12287,7 @@
         <v>2.12</v>
       </c>
       <c r="G46">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H46">
         <v>3.6</v>
@@ -12308,13 +12308,13 @@
         <v>1.07</v>
       </c>
       <c r="N46">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O46">
         <v>1.32</v>
       </c>
       <c r="P46">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q46">
         <v>1.92</v>
@@ -12323,7 +12323,7 @@
         <v>1.38</v>
       </c>
       <c r="S46">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T46">
         <v>1.76</v>
@@ -12332,10 +12332,10 @@
         <v>2.14</v>
       </c>
       <c r="V46">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W46">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X46">
         <v>18</v>
@@ -12368,7 +12368,7 @@
         <v>11</v>
       </c>
       <c r="AH46">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AI46">
         <v>65</v>
@@ -12386,7 +12386,7 @@
         <v>110</v>
       </c>
       <c r="AN46">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO46">
         <v>55</v>
@@ -12422,7 +12422,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ46">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA46">
         <v>9</v>
@@ -12440,7 +12440,7 @@
         <v>9.6</v>
       </c>
       <c r="BF46">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG46">
         <v>8.800000000000001</v>
@@ -12526,7 +12526,7 @@
         <v>286</v>
       </c>
       <c r="F47">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G47">
         <v>2.98</v>
@@ -12535,7 +12535,7 @@
         <v>2.54</v>
       </c>
       <c r="I47">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J47">
         <v>3.55</v>
@@ -12550,7 +12550,7 @@
         <v>1.06</v>
       </c>
       <c r="N47">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O47">
         <v>1.3</v>
@@ -12574,13 +12574,13 @@
         <v>2.28</v>
       </c>
       <c r="V47">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W47">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X47">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y47">
         <v>12</v>
@@ -12592,7 +12592,7 @@
         <v>40</v>
       </c>
       <c r="AB47">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC47">
         <v>9.199999999999999</v>
@@ -12607,7 +12607,7 @@
         <v>26</v>
       </c>
       <c r="AG47">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH47">
         <v>16.5</v>
@@ -12643,7 +12643,7 @@
         <v>17.5</v>
       </c>
       <c r="AS47">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT47">
         <v>11</v>
@@ -12655,7 +12655,7 @@
         <v>10</v>
       </c>
       <c r="AW47">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX47">
         <v>19</v>
@@ -12667,19 +12667,19 @@
         <v>13.5</v>
       </c>
       <c r="BA47">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB47">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC47">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BD47">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE47">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF47">
         <v>18</v>
@@ -12768,22 +12768,22 @@
         <v>287</v>
       </c>
       <c r="F48">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="G48">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="H48">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I48">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K48">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L48">
         <v>1.01</v>
@@ -12792,34 +12792,34 @@
         <v>1.02</v>
       </c>
       <c r="N48">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O48">
         <v>1.22</v>
       </c>
       <c r="P48">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q48">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R48">
         <v>1.49</v>
       </c>
       <c r="S48">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T48">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="U48">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V48">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W48">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="X48">
         <v>26</v>
@@ -12831,7 +12831,7 @@
         <v>42</v>
       </c>
       <c r="AA48">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB48">
         <v>12</v>
@@ -12840,13 +12840,13 @@
         <v>10.5</v>
       </c>
       <c r="AD48">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE48">
         <v>60</v>
       </c>
       <c r="AF48">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG48">
         <v>11</v>
@@ -12858,10 +12858,10 @@
         <v>60</v>
       </c>
       <c r="AJ48">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AK48">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL48">
         <v>30</v>
@@ -12870,64 +12870,64 @@
         <v>80</v>
       </c>
       <c r="AN48">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AO48">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP48">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AQ48">
         <v>18</v>
       </c>
       <c r="AR48">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS48">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT48">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU48">
         <v>8.6</v>
       </c>
       <c r="AV48">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW48">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX48">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY48">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ48">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA48">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB48">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC48">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD48">
         <v>7</v>
       </c>
       <c r="BE48">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF48">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG48">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BH48">
         <v>1000</v>
@@ -13016,16 +13016,16 @@
         <v>2.64</v>
       </c>
       <c r="H49">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I49">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="J49">
         <v>3.9</v>
       </c>
       <c r="K49">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L49">
         <v>1.01</v>
@@ -13049,16 +13049,16 @@
         <v>1.64</v>
       </c>
       <c r="S49">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="T49">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="U49">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V49">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W49">
         <v>1.6</v>
@@ -13082,7 +13082,7 @@
         <v>10</v>
       </c>
       <c r="AD49">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE49">
         <v>27</v>
@@ -13091,7 +13091,7 @@
         <v>22</v>
       </c>
       <c r="AG49">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH49">
         <v>15.5</v>
@@ -13112,16 +13112,16 @@
         <v>60</v>
       </c>
       <c r="AN49">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO49">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP49">
         <v>19</v>
       </c>
       <c r="AQ49">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR49">
         <v>18.5</v>
@@ -13130,10 +13130,10 @@
         <v>32</v>
       </c>
       <c r="AT49">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU49">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV49">
         <v>11</v>
@@ -13148,22 +13148,22 @@
         <v>11</v>
       </c>
       <c r="AZ49">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA49">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB49">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC49">
         <v>20</v>
       </c>
       <c r="BD49">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE49">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF49">
         <v>12</v>
@@ -13261,46 +13261,46 @@
         <v>3.3</v>
       </c>
       <c r="I50">
+        <v>3.7</v>
+      </c>
+      <c r="J50">
         <v>3.75</v>
       </c>
-      <c r="J50">
-        <v>3.7</v>
-      </c>
       <c r="K50">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L50">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M50">
         <v>1.05</v>
       </c>
       <c r="N50">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O50">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P50">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q50">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="R50">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S50">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T50">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U50">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V50">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W50">
         <v>1.77</v>
@@ -13309,7 +13309,7 @@
         <v>20</v>
       </c>
       <c r="Y50">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z50">
         <v>40</v>
@@ -13318,25 +13318,25 @@
         <v>90</v>
       </c>
       <c r="AB50">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC50">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD50">
         <v>15.5</v>
       </c>
       <c r="AE50">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AF50">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AG50">
         <v>11.5</v>
       </c>
       <c r="AH50">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI50">
         <v>44</v>
@@ -13345,43 +13345,43 @@
         <v>40</v>
       </c>
       <c r="AK50">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL50">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AM50">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AN50">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO50">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AP50">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ50">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR50">
         <v>16</v>
       </c>
       <c r="AS50">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AT50">
         <v>10</v>
       </c>
       <c r="AU50">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV50">
         <v>12.5</v>
       </c>
       <c r="AW50">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AX50">
         <v>13</v>
@@ -13393,7 +13393,7 @@
         <v>14</v>
       </c>
       <c r="BA50">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="BB50">
         <v>16.5</v>
@@ -13402,16 +13402,16 @@
         <v>18</v>
       </c>
       <c r="BD50">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE50">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF50">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG50">
-        <v>7.8</v>
+        <v>19.5</v>
       </c>
       <c r="BH50">
         <v>1000</v>
@@ -13494,22 +13494,22 @@
         <v>290</v>
       </c>
       <c r="F51">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G51">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H51">
         <v>4.6</v>
       </c>
       <c r="I51">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J51">
         <v>3.95</v>
       </c>
       <c r="K51">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L51">
         <v>1.01</v>
@@ -13524,7 +13524,7 @@
         <v>1.24</v>
       </c>
       <c r="P51">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q51">
         <v>1.69</v>
@@ -13533,10 +13533,10 @@
         <v>1.49</v>
       </c>
       <c r="S51">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T51">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U51">
         <v>2.18</v>
@@ -13584,7 +13584,7 @@
         <v>60</v>
       </c>
       <c r="AJ51">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AK51">
         <v>18.5</v>
@@ -13596,7 +13596,7 @@
         <v>90</v>
       </c>
       <c r="AN51">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO51">
         <v>55</v>
@@ -13611,7 +13611,7 @@
         <v>29</v>
       </c>
       <c r="AS51">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT51">
         <v>9.199999999999999</v>
@@ -13623,7 +13623,7 @@
         <v>16.5</v>
       </c>
       <c r="AW51">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX51">
         <v>10.5</v>
@@ -13644,16 +13644,16 @@
         <v>15</v>
       </c>
       <c r="BD51">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE51">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF51">
         <v>7.6</v>
       </c>
       <c r="BG51">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH51">
         <v>1000</v>
@@ -13736,22 +13736,22 @@
         <v>291</v>
       </c>
       <c r="F52">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G52">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H52">
         <v>5.4</v>
       </c>
       <c r="I52">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J52">
         <v>4.2</v>
       </c>
       <c r="K52">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L52">
         <v>1.01</v>
@@ -13760,31 +13760,31 @@
         <v>1.04</v>
       </c>
       <c r="N52">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O52">
         <v>1.24</v>
       </c>
       <c r="P52">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="Q52">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R52">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S52">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T52">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U52">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V52">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W52">
         <v>2.38</v>
@@ -13826,7 +13826,7 @@
         <v>70</v>
       </c>
       <c r="AJ52">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK52">
         <v>17</v>
@@ -13838,7 +13838,7 @@
         <v>100</v>
       </c>
       <c r="AN52">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO52">
         <v>75</v>
@@ -13850,10 +13850,10 @@
         <v>19.5</v>
       </c>
       <c r="AR52">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="AS52">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT52">
         <v>9</v>
@@ -13865,19 +13865,19 @@
         <v>18.5</v>
       </c>
       <c r="AW52">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AX52">
         <v>9.6</v>
       </c>
       <c r="AY52">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ52">
         <v>16.5</v>
       </c>
       <c r="BA52">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB52">
         <v>15</v>
@@ -13886,16 +13886,16 @@
         <v>14</v>
       </c>
       <c r="BD52">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE52">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF52">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG52">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH52">
         <v>1000</v>
@@ -13978,10 +13978,10 @@
         <v>292</v>
       </c>
       <c r="F53">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G53">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H53">
         <v>3.1</v>
@@ -13990,7 +13990,7 @@
         <v>3.35</v>
       </c>
       <c r="J53">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K53">
         <v>4</v>
@@ -14011,7 +14011,7 @@
         <v>2.3</v>
       </c>
       <c r="Q53">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R53">
         <v>1.54</v>
@@ -14020,7 +14020,7 @@
         <v>2.6</v>
       </c>
       <c r="T53">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U53">
         <v>2.46</v>
@@ -14029,7 +14029,7 @@
         <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X53">
         <v>25</v>
@@ -14059,7 +14059,7 @@
         <v>18</v>
       </c>
       <c r="AG53">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH53">
         <v>16</v>
@@ -14080,22 +14080,22 @@
         <v>75</v>
       </c>
       <c r="AN53">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AO53">
         <v>27</v>
       </c>
       <c r="AP53">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AQ53">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR53">
         <v>19</v>
       </c>
       <c r="AS53">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT53">
         <v>11.5</v>
@@ -14107,19 +14107,19 @@
         <v>12</v>
       </c>
       <c r="AW53">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AX53">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AY53">
         <v>10</v>
       </c>
       <c r="AZ53">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA53">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BB53">
         <v>21</v>
@@ -14128,10 +14128,10 @@
         <v>16.5</v>
       </c>
       <c r="BD53">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BE53">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF53">
         <v>11</v>
@@ -14223,7 +14223,7 @@
         <v>2.24</v>
       </c>
       <c r="G54">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H54">
         <v>3.55</v>
@@ -14244,7 +14244,7 @@
         <v>1.08</v>
       </c>
       <c r="N54">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O54">
         <v>1.36</v>
@@ -14256,7 +14256,7 @@
         <v>2.08</v>
       </c>
       <c r="R54">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S54">
         <v>3.8</v>
@@ -14265,10 +14265,10 @@
         <v>1.86</v>
       </c>
       <c r="U54">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V54">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W54">
         <v>1.76</v>
@@ -14286,7 +14286,7 @@
         <v>75</v>
       </c>
       <c r="AB54">
-        <v>16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC54">
         <v>8</v>
@@ -14325,7 +14325,7 @@
         <v>19.5</v>
       </c>
       <c r="AO54">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AP54">
         <v>11.5</v>
@@ -14358,13 +14358,13 @@
         <v>10</v>
       </c>
       <c r="AZ54">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA54">
         <v>46</v>
       </c>
       <c r="BB54">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BC54">
         <v>22</v>
@@ -14373,10 +14373,10 @@
         <v>36</v>
       </c>
       <c r="BE54">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BF54">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG54">
         <v>36</v>
@@ -14462,10 +14462,10 @@
         <v>294</v>
       </c>
       <c r="F55">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G55">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H55">
         <v>5</v>
@@ -14474,10 +14474,10 @@
         <v>5.6</v>
       </c>
       <c r="J55">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K55">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="L55">
         <v>1.01</v>
@@ -14492,7 +14492,7 @@
         <v>1.13</v>
       </c>
       <c r="P55">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q55">
         <v>1.42</v>
@@ -14504,7 +14504,7 @@
         <v>2.04</v>
       </c>
       <c r="T55">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U55">
         <v>2.62</v>
@@ -14513,7 +14513,7 @@
         <v>1.22</v>
       </c>
       <c r="W55">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X55">
         <v>44</v>
@@ -14528,7 +14528,7 @@
         <v>140</v>
       </c>
       <c r="AB55">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AC55">
         <v>13</v>
@@ -14540,7 +14540,7 @@
         <v>65</v>
       </c>
       <c r="AF55">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AG55">
         <v>11.5</v>
@@ -14552,7 +14552,7 @@
         <v>55</v>
       </c>
       <c r="AJ55">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AK55">
         <v>15.5</v>
@@ -14570,28 +14570,28 @@
         <v>36</v>
       </c>
       <c r="AP55">
+        <v>6.4</v>
+      </c>
+      <c r="AQ55">
+        <v>6</v>
+      </c>
+      <c r="AR55">
         <v>6.6</v>
       </c>
-      <c r="AQ55">
-        <v>6.2</v>
-      </c>
-      <c r="AR55">
+      <c r="AS55">
         <v>7</v>
       </c>
-      <c r="AS55">
-        <v>7.4</v>
-      </c>
       <c r="AT55">
-        <v>5.3</v>
+        <v>14</v>
       </c>
       <c r="AU55">
         <v>11</v>
       </c>
       <c r="AV55">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AW55">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AX55">
         <v>12.5</v>
@@ -14600,10 +14600,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ55">
-        <v>5.4</v>
+        <v>14.5</v>
       </c>
       <c r="BA55">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB55">
         <v>15.5</v>
@@ -14612,16 +14612,16 @@
         <v>13</v>
       </c>
       <c r="BD55">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BE55">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BF55">
         <v>4.7</v>
       </c>
       <c r="BG55">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH55">
         <v>1000</v>
@@ -14949,7 +14949,7 @@
         <v>6</v>
       </c>
       <c r="G57">
-        <v>110</v>
+        <v>11</v>
       </c>
       <c r="H57">
         <v>1.43</v>
@@ -14997,7 +14997,7 @@
         <v>2.62</v>
       </c>
       <c r="W57">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X57">
         <v>1000</v>
@@ -15188,19 +15188,19 @@
         <v>297</v>
       </c>
       <c r="F58">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G58">
         <v>110</v>
       </c>
       <c r="H58">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="I58">
         <v>110</v>
       </c>
       <c r="J58">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="K58">
         <v>950</v>
@@ -15687,7 +15687,7 @@
         <v>11.5</v>
       </c>
       <c r="K60">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="L60">
         <v>1.26</v>
@@ -15705,22 +15705,22 @@
         <v>2.66</v>
       </c>
       <c r="Q60">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="R60">
         <v>1.65</v>
       </c>
       <c r="S60">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="T60">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="U60">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V60">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="W60">
         <v>1.02</v>
@@ -15732,10 +15732,10 @@
         <v>9.6</v>
       </c>
       <c r="Z60">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AA60">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AB60">
         <v>110</v>
@@ -15744,7 +15744,7 @@
         <v>32</v>
       </c>
       <c r="AD60">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE60">
         <v>21</v>
@@ -15756,7 +15756,7 @@
         <v>190</v>
       </c>
       <c r="AH60">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AI60">
         <v>140</v>
@@ -15780,7 +15780,7 @@
         <v>3.1</v>
       </c>
       <c r="AP60">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AQ60">
         <v>8.199999999999999</v>
@@ -15792,106 +15792,106 @@
         <v>5.5</v>
       </c>
       <c r="AT60">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU60">
         <v>20</v>
       </c>
       <c r="AV60">
-        <v>17</v>
+        <v>8.4</v>
       </c>
       <c r="AW60">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="AX60">
+        <v>9.6</v>
+      </c>
+      <c r="AY60">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ60">
+        <v>11</v>
+      </c>
+      <c r="BA60">
+        <v>9</v>
+      </c>
+      <c r="BB60">
+        <v>9.6</v>
+      </c>
+      <c r="BC60">
+        <v>9.6</v>
+      </c>
+      <c r="BD60">
+        <v>9.6</v>
+      </c>
+      <c r="BE60">
+        <v>9.6</v>
+      </c>
+      <c r="BF60">
+        <v>9.6</v>
+      </c>
+      <c r="BG60">
+        <v>2.84</v>
+      </c>
+      <c r="BH60">
+        <v>5.8</v>
+      </c>
+      <c r="BI60">
+        <v>3.8</v>
+      </c>
+      <c r="BJ60">
+        <v>1000</v>
+      </c>
+      <c r="BK60">
+        <v>18</v>
+      </c>
+      <c r="BL60">
+        <v>1000</v>
+      </c>
+      <c r="BM60">
+        <v>21</v>
+      </c>
+      <c r="BN60">
+        <v>1000</v>
+      </c>
+      <c r="BO60">
+        <v>27</v>
+      </c>
+      <c r="BP60">
+        <v>1000</v>
+      </c>
+      <c r="BQ60">
+        <v>21</v>
+      </c>
+      <c r="BR60">
+        <v>1000</v>
+      </c>
+      <c r="BS60">
+        <v>21</v>
+      </c>
+      <c r="BT60">
+        <v>3.35</v>
+      </c>
+      <c r="BU60">
+        <v>2.62</v>
+      </c>
+      <c r="BV60">
+        <v>5.2</v>
+      </c>
+      <c r="BW60">
+        <v>4.4</v>
+      </c>
+      <c r="BX60">
+        <v>36</v>
+      </c>
+      <c r="BY60">
+        <v>26</v>
+      </c>
+      <c r="BZ60">
         <v>7.4</v>
       </c>
-      <c r="AY60">
-        <v>7.2</v>
-      </c>
-      <c r="AZ60">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BA60">
-        <v>7</v>
-      </c>
-      <c r="BB60">
-        <v>7.4</v>
-      </c>
-      <c r="BC60">
-        <v>7.4</v>
-      </c>
-      <c r="BD60">
-        <v>7.4</v>
-      </c>
-      <c r="BE60">
-        <v>7.4</v>
-      </c>
-      <c r="BF60">
-        <v>7.4</v>
-      </c>
-      <c r="BG60">
-        <v>2.82</v>
-      </c>
-      <c r="BH60">
-        <v>1000</v>
-      </c>
-      <c r="BI60">
-        <v>1.01</v>
-      </c>
-      <c r="BJ60">
-        <v>1000</v>
-      </c>
-      <c r="BK60">
-        <v>1.01</v>
-      </c>
-      <c r="BL60">
-        <v>1000</v>
-      </c>
-      <c r="BM60">
-        <v>1.01</v>
-      </c>
-      <c r="BN60">
-        <v>1000</v>
-      </c>
-      <c r="BO60">
-        <v>1.01</v>
-      </c>
-      <c r="BP60">
-        <v>1000</v>
-      </c>
-      <c r="BQ60">
-        <v>1.01</v>
-      </c>
-      <c r="BR60">
-        <v>1000</v>
-      </c>
-      <c r="BS60">
-        <v>1.01</v>
-      </c>
-      <c r="BT60">
-        <v>1000</v>
-      </c>
-      <c r="BU60">
-        <v>2.64</v>
-      </c>
-      <c r="BV60">
-        <v>1000</v>
-      </c>
-      <c r="BW60">
-        <v>1.01</v>
-      </c>
-      <c r="BX60">
-        <v>1000</v>
-      </c>
-      <c r="BY60">
-        <v>1.01</v>
-      </c>
-      <c r="BZ60">
-        <v>1000</v>
-      </c>
       <c r="CA60">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="CB60" t="s">
         <v>342</v>
@@ -15914,16 +15914,16 @@
         <v>300</v>
       </c>
       <c r="F61">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G61">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="H61">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="I61">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J61">
         <v>6</v>
@@ -15944,25 +15944,25 @@
         <v>1.23</v>
       </c>
       <c r="P61">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q61">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R61">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S61">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="T61">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U61">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V61">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W61">
         <v>4</v>
@@ -15977,19 +15977,19 @@
         <v>130</v>
       </c>
       <c r="AA61">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="AB61">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC61">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD61">
         <v>48</v>
       </c>
       <c r="AE61">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AF61">
         <v>7.4</v>
@@ -16001,13 +16001,13 @@
         <v>38</v>
       </c>
       <c r="AI61">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AJ61">
         <v>9.800000000000001</v>
       </c>
       <c r="AK61">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL61">
         <v>48</v>
@@ -16022,16 +16022,16 @@
         <v>380</v>
       </c>
       <c r="AP61">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ61">
         <v>32</v>
       </c>
       <c r="AR61">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS61">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AT61">
         <v>8</v>
@@ -16043,19 +16043,19 @@
         <v>38</v>
       </c>
       <c r="AW61">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX61">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY61">
         <v>10</v>
       </c>
       <c r="AZ61">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BA61">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BB61">
         <v>8.6</v>
@@ -16067,7 +16067,7 @@
         <v>11.5</v>
       </c>
       <c r="BE61">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BF61">
         <v>4.8</v>
@@ -16159,7 +16159,7 @@
         <v>2.4</v>
       </c>
       <c r="G62">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H62">
         <v>3.5</v>
@@ -16180,28 +16180,28 @@
         <v>1.11</v>
       </c>
       <c r="N62">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="O62">
         <v>1.5</v>
       </c>
       <c r="P62">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q62">
         <v>2.52</v>
       </c>
       <c r="R62">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S62">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T62">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U62">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V62">
         <v>1.38</v>
@@ -16249,7 +16249,7 @@
         <v>34</v>
       </c>
       <c r="AK62">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL62">
         <v>60</v>
@@ -16270,10 +16270,10 @@
         <v>9.6</v>
       </c>
       <c r="AR62">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS62">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT62">
         <v>7.6</v>
@@ -16425,13 +16425,13 @@
         <v>2.74</v>
       </c>
       <c r="O63">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P63">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q63">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R63">
         <v>1.21</v>
@@ -16440,7 +16440,7 @@
         <v>5.3</v>
       </c>
       <c r="T63">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U63">
         <v>1.84</v>
@@ -16452,10 +16452,10 @@
         <v>1.64</v>
       </c>
       <c r="X63">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y63">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z63">
         <v>22</v>
@@ -16464,7 +16464,7 @@
         <v>75</v>
       </c>
       <c r="AB63">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC63">
         <v>7.2</v>
@@ -16473,7 +16473,7 @@
         <v>15</v>
       </c>
       <c r="AE63">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF63">
         <v>14.5</v>
@@ -16491,7 +16491,7 @@
         <v>38</v>
       </c>
       <c r="AK63">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL63">
         <v>65</v>
@@ -16506,7 +16506,7 @@
         <v>90</v>
       </c>
       <c r="AP63">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ63">
         <v>9.4</v>
@@ -16551,7 +16551,7 @@
         <v>48</v>
       </c>
       <c r="BE63">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BF63">
         <v>27</v>
@@ -16575,7 +16575,7 @@
         <v>1000</v>
       </c>
       <c r="BM63">
-        <v>2.62</v>
+        <v>1.21</v>
       </c>
       <c r="BN63">
         <v>1000</v>
@@ -16587,13 +16587,13 @@
         <v>1000</v>
       </c>
       <c r="BQ63">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="BR63">
         <v>1000</v>
       </c>
       <c r="BS63">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="BT63">
         <v>1000</v>
@@ -16605,19 +16605,19 @@
         <v>1000</v>
       </c>
       <c r="BW63">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="BX63">
         <v>1000</v>
       </c>
       <c r="BY63">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="BZ63">
         <v>1000</v>
       </c>
       <c r="CA63">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="CB63" t="s">
         <v>342</v>
@@ -16882,16 +16882,16 @@
         <v>304</v>
       </c>
       <c r="F65">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G65">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H65">
         <v>2.42</v>
       </c>
       <c r="I65">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J65">
         <v>3.35</v>
@@ -16900,13 +16900,13 @@
         <v>3.55</v>
       </c>
       <c r="L65">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M65">
         <v>1.08</v>
       </c>
       <c r="N65">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O65">
         <v>1.37</v>
@@ -16930,10 +16930,10 @@
         <v>2.08</v>
       </c>
       <c r="V65">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W65">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X65">
         <v>13</v>
@@ -16945,7 +16945,7 @@
         <v>15.5</v>
       </c>
       <c r="AA65">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB65">
         <v>11.5</v>
@@ -16969,13 +16969,13 @@
         <v>18.5</v>
       </c>
       <c r="AI65">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AJ65">
         <v>60</v>
       </c>
       <c r="AK65">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL65">
         <v>55</v>
@@ -16990,7 +16990,7 @@
         <v>24</v>
       </c>
       <c r="AP65">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ65">
         <v>8.800000000000001</v>
@@ -16999,7 +16999,7 @@
         <v>13.5</v>
       </c>
       <c r="AS65">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT65">
         <v>10</v>
@@ -17011,7 +17011,7 @@
         <v>10.5</v>
       </c>
       <c r="AW65">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX65">
         <v>19.5</v>
@@ -17023,19 +17023,19 @@
         <v>16.5</v>
       </c>
       <c r="BA65">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB65">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC65">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BD65">
         <v>11.5</v>
       </c>
       <c r="BE65">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF65">
         <v>11</v>
@@ -17047,61 +17047,61 @@
         <v>1000</v>
       </c>
       <c r="BI65">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="BJ65">
         <v>11.5</v>
       </c>
       <c r="BK65">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL65">
         <v>1000</v>
       </c>
       <c r="BM65">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="BN65">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO65">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP65">
         <v>38</v>
       </c>
       <c r="BQ65">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="BR65">
         <v>1000</v>
       </c>
       <c r="BS65">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="BT65">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BU65">
-        <v>2.76</v>
+        <v>4.3</v>
       </c>
       <c r="BV65">
         <v>26</v>
       </c>
       <c r="BW65">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="BX65">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BY65">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BZ65">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="CA65">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="CB65" t="s">
         <v>342</v>
@@ -17130,7 +17130,7 @@
         <v>2.06</v>
       </c>
       <c r="H66">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I66">
         <v>4.8</v>
@@ -17148,28 +17148,28 @@
         <v>1.11</v>
       </c>
       <c r="N66">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O66">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P66">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q66">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R66">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S66">
         <v>5</v>
       </c>
       <c r="T66">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U66">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V66">
         <v>1.26</v>
@@ -17178,7 +17178,7 @@
         <v>1.94</v>
       </c>
       <c r="X66">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y66">
         <v>12.5</v>
@@ -17244,7 +17244,7 @@
         <v>12</v>
       </c>
       <c r="AT66">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU66">
         <v>7</v>
@@ -17253,7 +17253,7 @@
         <v>17</v>
       </c>
       <c r="AW66">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX66">
         <v>9.6</v>
@@ -17277,25 +17277,25 @@
         <v>48</v>
       </c>
       <c r="BE66">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF66">
         <v>19</v>
       </c>
       <c r="BG66">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH66">
         <v>1000</v>
       </c>
       <c r="BI66">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BJ66">
         <v>1000</v>
       </c>
       <c r="BK66">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BL66">
         <v>1000</v>
@@ -17313,7 +17313,7 @@
         <v>1000</v>
       </c>
       <c r="BQ66">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="BR66">
         <v>1000</v>
@@ -17331,7 +17331,7 @@
         <v>1000</v>
       </c>
       <c r="BW66">
-        <v>1.32</v>
+        <v>2.22</v>
       </c>
       <c r="BX66">
         <v>1000</v>
@@ -17343,7 +17343,7 @@
         <v>1000</v>
       </c>
       <c r="CA66">
-        <v>1.32</v>
+        <v>2.22</v>
       </c>
       <c r="CB66" t="s">
         <v>342</v>
@@ -17417,7 +17417,7 @@
         <v>1.02</v>
       </c>
       <c r="W67">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X67">
         <v>1000</v>
@@ -17611,19 +17611,19 @@
         <v>4.8</v>
       </c>
       <c r="G68">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H68">
         <v>1.81</v>
       </c>
       <c r="I68">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="J68">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K68">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L68">
         <v>1.01</v>
@@ -17638,13 +17638,13 @@
         <v>1.36</v>
       </c>
       <c r="P68">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q68">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R68">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S68">
         <v>3.7</v>
@@ -17653,10 +17653,10 @@
         <v>1.96</v>
       </c>
       <c r="U68">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V68">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W68">
         <v>1.21</v>
@@ -17671,7 +17671,7 @@
         <v>11.5</v>
       </c>
       <c r="AA68">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AB68">
         <v>970</v>
@@ -17689,7 +17689,7 @@
         <v>1000</v>
       </c>
       <c r="AG68">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH68">
         <v>1000</v>
@@ -17737,7 +17737,7 @@
         <v>1.82</v>
       </c>
       <c r="AW68">
-        <v>2.18</v>
+        <v>17</v>
       </c>
       <c r="AX68">
         <v>2.18</v>
@@ -17865,7 +17865,7 @@
         <v>5.1</v>
       </c>
       <c r="K69">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="L69">
         <v>1.01</v>
@@ -18092,7 +18092,7 @@
         <v>309</v>
       </c>
       <c r="F70">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G70">
         <v>2.12</v>
@@ -18101,13 +18101,13 @@
         <v>3.55</v>
       </c>
       <c r="I70">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J70">
         <v>3.85</v>
       </c>
       <c r="K70">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L70">
         <v>1.01</v>
@@ -18131,7 +18131,7 @@
         <v>1.53</v>
       </c>
       <c r="S70">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T70">
         <v>1.6</v>
@@ -18337,7 +18337,7 @@
         <v>1.76</v>
       </c>
       <c r="G71">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H71">
         <v>3.85</v>
@@ -18349,7 +18349,7 @@
         <v>4.8</v>
       </c>
       <c r="K71">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L71">
         <v>1.01</v>
@@ -18364,13 +18364,13 @@
         <v>1.09</v>
       </c>
       <c r="P71">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q71">
         <v>1.3</v>
       </c>
       <c r="R71">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S71">
         <v>1.74</v>
@@ -18385,7 +18385,7 @@
         <v>1.31</v>
       </c>
       <c r="W71">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X71">
         <v>65</v>
@@ -18436,7 +18436,7 @@
         <v>44</v>
       </c>
       <c r="AN71">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AO71">
         <v>19.5</v>
@@ -18445,13 +18445,13 @@
         <v>5.3</v>
       </c>
       <c r="AQ71">
+        <v>5</v>
+      </c>
+      <c r="AR71">
         <v>5.2</v>
       </c>
-      <c r="AR71">
-        <v>5.3</v>
-      </c>
       <c r="AS71">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT71">
         <v>20</v>
@@ -18585,7 +18585,7 @@
         <v>5.1</v>
       </c>
       <c r="I72">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J72">
         <v>4.8</v>
@@ -18600,13 +18600,13 @@
         <v>1.02</v>
       </c>
       <c r="N72">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O72">
         <v>1.12</v>
       </c>
       <c r="P72">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q72">
         <v>1.36</v>
@@ -19308,7 +19308,7 @@
         <v>2.9</v>
       </c>
       <c r="H75">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I75">
         <v>3.15</v>
@@ -19332,7 +19332,7 @@
         <v>1.21</v>
       </c>
       <c r="P75">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q75">
         <v>1.67</v>
@@ -19344,7 +19344,7 @@
         <v>2.6</v>
       </c>
       <c r="T75">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U75">
         <v>2.3</v>
@@ -19792,10 +19792,10 @@
         <v>4.7</v>
       </c>
       <c r="H77">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="I77">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="J77">
         <v>4.1</v>
@@ -19810,13 +19810,13 @@
         <v>1.04</v>
       </c>
       <c r="N77">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O77">
         <v>1.2</v>
       </c>
       <c r="P77">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q77">
         <v>1.58</v>
@@ -19825,7 +19825,7 @@
         <v>1.6</v>
       </c>
       <c r="S77">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T77">
         <v>1.61</v>
@@ -19834,7 +19834,7 @@
         <v>2.42</v>
       </c>
       <c r="V77">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W77">
         <v>1.27</v>
@@ -19918,7 +19918,7 @@
         <v>15</v>
       </c>
       <c r="AX77">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY77">
         <v>15.5</v>
@@ -19933,7 +19933,7 @@
         <v>7.2</v>
       </c>
       <c r="BC77">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BD77">
         <v>6.8</v>
@@ -19942,7 +19942,7 @@
         <v>7</v>
       </c>
       <c r="BF77">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG77">
         <v>7.2</v>
@@ -20034,7 +20034,7 @@
         <v>1.26</v>
       </c>
       <c r="H78">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="I78">
         <v>20</v>
@@ -20061,19 +20061,19 @@
         <v>2.32</v>
       </c>
       <c r="Q78">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R78">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S78">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T78">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="U78">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V78">
         <v>1.05</v>
@@ -20103,7 +20103,7 @@
         <v>70</v>
       </c>
       <c r="AE78">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="AF78">
         <v>7</v>
@@ -20112,7 +20112,7 @@
         <v>12.5</v>
       </c>
       <c r="AH78">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI78">
         <v>290</v>
@@ -20133,7 +20133,7 @@
         <v>4.5</v>
       </c>
       <c r="AO78">
-        <v>750</v>
+        <v>710</v>
       </c>
       <c r="AP78">
         <v>19.5</v>
@@ -20169,7 +20169,7 @@
         <v>38</v>
       </c>
       <c r="BA78">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BB78">
         <v>7.6</v>
@@ -20178,7 +20178,7 @@
         <v>14.5</v>
       </c>
       <c r="BD78">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BE78">
         <v>15</v>
@@ -20187,10 +20187,10 @@
         <v>4.2</v>
       </c>
       <c r="BG78">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH78">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI78">
         <v>3.25</v>
@@ -20208,7 +20208,7 @@
         <v>21</v>
       </c>
       <c r="BN78">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BO78">
         <v>3.2</v>
@@ -20220,16 +20220,16 @@
         <v>5.8</v>
       </c>
       <c r="BR78">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS78">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BT78">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BU78">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BV78">
         <v>1000</v>
@@ -20294,13 +20294,13 @@
         <v>1.09</v>
       </c>
       <c r="N79">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O79">
         <v>1.43</v>
       </c>
       <c r="P79">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q79">
         <v>2.26</v>
@@ -20315,7 +20315,7 @@
         <v>2.4</v>
       </c>
       <c r="U79">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V79">
         <v>1.13</v>
@@ -20330,7 +20330,7 @@
         <v>21</v>
       </c>
       <c r="Z79">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AA79">
         <v>370</v>
@@ -20390,7 +20390,7 @@
         <v>14.5</v>
       </c>
       <c r="AT79">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU79">
         <v>8.800000000000001</v>
@@ -20411,7 +20411,7 @@
         <v>28</v>
       </c>
       <c r="BA79">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BB79">
         <v>12</v>
@@ -20420,10 +20420,10 @@
         <v>18</v>
       </c>
       <c r="BD79">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BE79">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BF79">
         <v>10</v>
@@ -20474,13 +20474,13 @@
         <v>10</v>
       </c>
       <c r="BV79">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BW79">
         <v>21</v>
       </c>
       <c r="BX79">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BY79">
         <v>21</v>
@@ -20512,13 +20512,13 @@
         <v>319</v>
       </c>
       <c r="F80">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G80">
         <v>3.35</v>
       </c>
       <c r="H80">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I80">
         <v>2.42</v>
@@ -20539,31 +20539,31 @@
         <v>4.2</v>
       </c>
       <c r="O80">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P80">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q80">
         <v>1.87</v>
       </c>
       <c r="R80">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S80">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T80">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U80">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V80">
         <v>1.7</v>
       </c>
       <c r="W80">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X80">
         <v>15</v>
@@ -20587,7 +20587,7 @@
         <v>11.5</v>
       </c>
       <c r="AE80">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF80">
         <v>23</v>
@@ -20596,13 +20596,13 @@
         <v>13.5</v>
       </c>
       <c r="AH80">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI80">
         <v>36</v>
       </c>
       <c r="AJ80">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AK80">
         <v>34</v>
@@ -20617,10 +20617,10 @@
         <v>29</v>
       </c>
       <c r="AO80">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP80">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ80">
         <v>11</v>
@@ -20641,7 +20641,7 @@
         <v>11</v>
       </c>
       <c r="AW80">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX80">
         <v>21</v>
@@ -20671,7 +20671,7 @@
         <v>26</v>
       </c>
       <c r="BG80">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="BH80">
         <v>3.5</v>
@@ -20713,7 +20713,7 @@
         <v>5.5</v>
       </c>
       <c r="BU80">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BV80">
         <v>18</v>
@@ -20769,7 +20769,7 @@
         <v>3.65</v>
       </c>
       <c r="K81">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L81">
         <v>1.37</v>
@@ -20999,7 +20999,7 @@
         <v>9.4</v>
       </c>
       <c r="G82">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="H82">
         <v>1.43</v>
@@ -21008,19 +21008,19 @@
         <v>1.44</v>
       </c>
       <c r="J82">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K82">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L82">
         <v>1.36</v>
       </c>
       <c r="M82">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N82">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O82">
         <v>1.27</v>
@@ -21029,22 +21029,22 @@
         <v>2.16</v>
       </c>
       <c r="Q82">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R82">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S82">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T82">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U82">
         <v>1.84</v>
       </c>
       <c r="V82">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="W82">
         <v>1.11</v>
@@ -21053,7 +21053,7 @@
         <v>18</v>
       </c>
       <c r="Y82">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z82">
         <v>8.199999999999999</v>
@@ -21104,7 +21104,7 @@
         <v>6.6</v>
       </c>
       <c r="AP82">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ82">
         <v>7.8</v>
@@ -21134,25 +21134,25 @@
         <v>30</v>
       </c>
       <c r="AZ82">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA82">
         <v>34</v>
       </c>
       <c r="BB82">
+        <v>17</v>
+      </c>
+      <c r="BC82">
+        <v>16</v>
+      </c>
+      <c r="BD82">
+        <v>16</v>
+      </c>
+      <c r="BE82">
         <v>16.5</v>
       </c>
-      <c r="BC82">
-        <v>15.5</v>
-      </c>
-      <c r="BD82">
-        <v>15</v>
-      </c>
-      <c r="BE82">
-        <v>17</v>
-      </c>
       <c r="BF82">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG82">
         <v>6.2</v>
@@ -21244,7 +21244,7 @@
         <v>2.64</v>
       </c>
       <c r="H83">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="I83">
         <v>3.1</v>
@@ -21253,7 +21253,7 @@
         <v>3.55</v>
       </c>
       <c r="K83">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L83">
         <v>1.35</v>
@@ -21262,7 +21262,7 @@
         <v>1.06</v>
       </c>
       <c r="N83">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O83">
         <v>1.29</v>
@@ -21271,7 +21271,7 @@
         <v>2.04</v>
       </c>
       <c r="Q83">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R83">
         <v>1.41</v>
@@ -21280,7 +21280,7 @@
         <v>3.1</v>
       </c>
       <c r="T83">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U83">
         <v>2.24</v>
@@ -21289,7 +21289,7 @@
         <v>1.47</v>
       </c>
       <c r="W83">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X83">
         <v>20</v>
@@ -21355,10 +21355,10 @@
         <v>18</v>
       </c>
       <c r="AS83">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT83">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU83">
         <v>7.4</v>
@@ -21367,7 +21367,7 @@
         <v>11.5</v>
       </c>
       <c r="AW83">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX83">
         <v>15</v>
@@ -21379,7 +21379,7 @@
         <v>14</v>
       </c>
       <c r="BA83">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB83">
         <v>8.199999999999999</v>
@@ -21388,10 +21388,10 @@
         <v>7.6</v>
       </c>
       <c r="BD83">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE83">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF83">
         <v>16.5</v>
@@ -21483,13 +21483,13 @@
         <v>2.08</v>
       </c>
       <c r="G84">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="H84">
         <v>3.35</v>
       </c>
       <c r="I84">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J84">
         <v>3</v>
@@ -21531,7 +21531,7 @@
         <v>1.3</v>
       </c>
       <c r="W84">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="X84">
         <v>970</v>
@@ -21561,7 +21561,7 @@
         <v>24</v>
       </c>
       <c r="AG84">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH84">
         <v>1000</v>
@@ -21964,22 +21964,22 @@
         <v>325</v>
       </c>
       <c r="F86">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="G86">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="H86">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I86">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J86">
-        <v>2.98</v>
+        <v>1.1</v>
       </c>
       <c r="K86">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="L86">
         <v>1.01</v>
@@ -21991,13 +21991,13 @@
         <v>2.46</v>
       </c>
       <c r="O86">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P86">
         <v>2.46</v>
       </c>
       <c r="Q86">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R86">
         <v>1.61</v>
@@ -22015,7 +22015,7 @@
         <v>1.29</v>
       </c>
       <c r="W86">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="X86">
         <v>1000</v>
@@ -22699,7 +22699,7 @@
         <v>2.24</v>
       </c>
       <c r="I89">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J89">
         <v>3.35</v>
@@ -22723,19 +22723,19 @@
         <v>1.77</v>
       </c>
       <c r="Q89">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R89">
         <v>1.29</v>
       </c>
       <c r="S89">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T89">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="U89">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="V89">
         <v>1.73</v>
@@ -22744,7 +22744,7 @@
         <v>1.35</v>
       </c>
       <c r="X89">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y89">
         <v>8.800000000000001</v>
@@ -22765,7 +22765,7 @@
         <v>12</v>
       </c>
       <c r="AE89">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF89">
         <v>30</v>
@@ -22795,7 +22795,7 @@
         <v>65</v>
       </c>
       <c r="AO89">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP89">
         <v>10.5</v>
@@ -22807,7 +22807,7 @@
         <v>12</v>
       </c>
       <c r="AS89">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT89">
         <v>10.5</v>
@@ -22819,7 +22819,7 @@
         <v>10</v>
       </c>
       <c r="AW89">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX89">
         <v>20</v>
@@ -22834,22 +22834,22 @@
         <v>6.8</v>
       </c>
       <c r="BB89">
+        <v>7.2</v>
+      </c>
+      <c r="BC89">
         <v>7</v>
       </c>
-      <c r="BC89">
-        <v>6.8</v>
-      </c>
       <c r="BD89">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE89">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF89">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG89">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BH89">
         <v>1000</v>
@@ -22935,7 +22935,7 @@
         <v>2.64</v>
       </c>
       <c r="G90">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H90">
         <v>3.05</v>
@@ -22944,49 +22944,49 @@
         <v>3.3</v>
       </c>
       <c r="J90">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K90">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L90">
         <v>1.55</v>
       </c>
       <c r="M90">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N90">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O90">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="P90">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="Q90">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="R90">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S90">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T90">
         <v>2.12</v>
       </c>
       <c r="U90">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V90">
         <v>1.43</v>
       </c>
       <c r="W90">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X90">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y90">
         <v>9</v>
@@ -22995,13 +22995,13 @@
         <v>23</v>
       </c>
       <c r="AA90">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB90">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC90">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD90">
         <v>19</v>
@@ -23010,10 +23010,10 @@
         <v>60</v>
       </c>
       <c r="AF90">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AG90">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH90">
         <v>30</v>
@@ -23025,22 +23025,22 @@
         <v>60</v>
       </c>
       <c r="AK90">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL90">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM90">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AN90">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO90">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP90">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AQ90">
         <v>7.8</v>
@@ -23049,7 +23049,7 @@
         <v>16.5</v>
       </c>
       <c r="AS90">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT90">
         <v>7.2</v>
@@ -23058,10 +23058,10 @@
         <v>6.4</v>
       </c>
       <c r="AV90">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW90">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX90">
         <v>14</v>
@@ -23070,34 +23070,34 @@
         <v>12</v>
       </c>
       <c r="AZ90">
-        <v>6.2</v>
+        <v>19.5</v>
       </c>
       <c r="BA90">
+        <v>7.6</v>
+      </c>
+      <c r="BB90">
+        <v>7.4</v>
+      </c>
+      <c r="BC90">
         <v>7</v>
       </c>
-      <c r="BB90">
-        <v>6.8</v>
-      </c>
-      <c r="BC90">
-        <v>6.6</v>
-      </c>
       <c r="BD90">
+        <v>7.6</v>
+      </c>
+      <c r="BE90">
+        <v>8</v>
+      </c>
+      <c r="BF90">
         <v>7.2</v>
       </c>
-      <c r="BE90">
-        <v>7.6</v>
-      </c>
-      <c r="BF90">
-        <v>6.8</v>
-      </c>
       <c r="BG90">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH90">
         <v>1000</v>
       </c>
       <c r="BI90">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BJ90">
         <v>1000</v>
@@ -23174,22 +23174,22 @@
         <v>330</v>
       </c>
       <c r="F91">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G91">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="H91">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="I91">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="J91">
         <v>4.6</v>
       </c>
       <c r="K91">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L91">
         <v>1.29</v>
@@ -23198,34 +23198,34 @@
         <v>1.02</v>
       </c>
       <c r="N91">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O91">
         <v>1.26</v>
       </c>
       <c r="P91">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="Q91">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="R91">
         <v>1.34</v>
       </c>
       <c r="S91">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T91">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="U91">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="V91">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="W91">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="X91">
         <v>1000</v>
@@ -23661,19 +23661,19 @@
         <v>2.1</v>
       </c>
       <c r="G93">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H93">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I93">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="J93">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="K93">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="L93">
         <v>1.38</v>
@@ -23682,7 +23682,7 @@
         <v>1.01</v>
       </c>
       <c r="N93">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O93">
         <v>1.37</v>
@@ -23691,13 +23691,13 @@
         <v>1.62</v>
       </c>
       <c r="Q93">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R93">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="S93">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="T93">
         <v>1.01</v>
@@ -23706,10 +23706,10 @@
         <v>1.01</v>
       </c>
       <c r="V93">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W93">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="X93">
         <v>1000</v>
@@ -23900,16 +23900,16 @@
         <v>333</v>
       </c>
       <c r="F94">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G94">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="H94">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="I94">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="J94">
         <v>3.65</v>
@@ -23951,7 +23951,7 @@
         <v>1.56</v>
       </c>
       <c r="W94">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X94">
         <v>22</v>
@@ -24005,7 +24005,7 @@
         <v>17.5</v>
       </c>
       <c r="AO94">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP94">
         <v>18.5</v>
@@ -24020,7 +24020,7 @@
         <v>7.6</v>
       </c>
       <c r="AT94">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU94">
         <v>8</v>
@@ -24157,7 +24157,7 @@
         <v>3.75</v>
       </c>
       <c r="K95">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L95">
         <v>1.01</v>
@@ -24166,13 +24166,13 @@
         <v>1.05</v>
       </c>
       <c r="N95">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O95">
         <v>1.24</v>
       </c>
       <c r="P95">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="Q95">
         <v>1.66</v>
@@ -24181,7 +24181,7 @@
         <v>1.42</v>
       </c>
       <c r="S95">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="T95">
         <v>1.69</v>
@@ -24399,7 +24399,7 @@
         <v>5.5</v>
       </c>
       <c r="K96">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L96">
         <v>1.25</v>
@@ -24411,10 +24411,10 @@
         <v>5.5</v>
       </c>
       <c r="O96">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P96">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q96">
         <v>1.58</v>
@@ -24423,7 +24423,7 @@
         <v>1.62</v>
       </c>
       <c r="S96">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="T96">
         <v>1.83</v>
@@ -24432,7 +24432,7 @@
         <v>2.06</v>
       </c>
       <c r="V96">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W96">
         <v>3.15</v>
@@ -24626,22 +24626,22 @@
         <v>336</v>
       </c>
       <c r="F97">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="G97">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H97">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I97">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J97">
         <v>3.3</v>
       </c>
       <c r="K97">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L97">
         <v>1.01</v>
@@ -24650,19 +24650,19 @@
         <v>1.09</v>
       </c>
       <c r="N97">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O97">
         <v>1.43</v>
       </c>
       <c r="P97">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q97">
         <v>2.22</v>
       </c>
       <c r="R97">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S97">
         <v>4.2</v>
@@ -24671,13 +24671,13 @@
         <v>1.93</v>
       </c>
       <c r="U97">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="V97">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W97">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X97">
         <v>11.5</v>
@@ -24698,13 +24698,13 @@
         <v>8.6</v>
       </c>
       <c r="AD97">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE97">
         <v>55</v>
       </c>
       <c r="AF97">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG97">
         <v>12</v>
@@ -24740,13 +24740,13 @@
         <v>10</v>
       </c>
       <c r="AR97">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS97">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT97">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU97">
         <v>7</v>
@@ -24755,10 +24755,10 @@
         <v>13</v>
       </c>
       <c r="AW97">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX97">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY97">
         <v>10</v>
@@ -24767,25 +24767,25 @@
         <v>17.5</v>
       </c>
       <c r="BA97">
+        <v>7.6</v>
+      </c>
+      <c r="BB97">
+        <v>7</v>
+      </c>
+      <c r="BC97">
+        <v>6.8</v>
+      </c>
+      <c r="BD97">
+        <v>7.4</v>
+      </c>
+      <c r="BE97">
         <v>8</v>
       </c>
-      <c r="BB97">
+      <c r="BF97">
+        <v>6.6</v>
+      </c>
+      <c r="BG97">
         <v>7.4</v>
-      </c>
-      <c r="BC97">
-        <v>7</v>
-      </c>
-      <c r="BD97">
-        <v>7.8</v>
-      </c>
-      <c r="BE97">
-        <v>8.4</v>
-      </c>
-      <c r="BF97">
-        <v>6.8</v>
-      </c>
-      <c r="BG97">
-        <v>7.8</v>
       </c>
       <c r="BH97">
         <v>1000</v>
@@ -24880,7 +24880,7 @@
         <v>3.2</v>
       </c>
       <c r="J98">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K98">
         <v>4.4</v>
@@ -24898,7 +24898,7 @@
         <v>1.17</v>
       </c>
       <c r="P98">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Q98">
         <v>1.5</v>
@@ -24916,7 +24916,7 @@
         <v>2.86</v>
       </c>
       <c r="V98">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W98">
         <v>1.79</v>
@@ -25137,7 +25137,7 @@
         <v>4.7</v>
       </c>
       <c r="O99">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P99">
         <v>2.24</v>
@@ -25179,7 +25179,7 @@
         <v>13</v>
       </c>
       <c r="AC99">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD99">
         <v>14</v>
@@ -25221,13 +25221,13 @@
         <v>16</v>
       </c>
       <c r="AQ99">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR99">
         <v>20</v>
       </c>
       <c r="AS99">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT99">
         <v>11</v>
@@ -25239,7 +25239,7 @@
         <v>12</v>
       </c>
       <c r="AW99">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX99">
         <v>14.5</v>
@@ -25251,19 +25251,19 @@
         <v>14</v>
       </c>
       <c r="BA99">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB99">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC99">
         <v>20</v>
       </c>
       <c r="BD99">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE99">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF99">
         <v>13.5</v>
@@ -25352,7 +25352,7 @@
         <v>339</v>
       </c>
       <c r="F100">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G100">
         <v>3.6</v>
@@ -25367,7 +25367,7 @@
         <v>4.2</v>
       </c>
       <c r="K100">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L100">
         <v>1.25</v>
@@ -25382,13 +25382,13 @@
         <v>1.15</v>
       </c>
       <c r="P100">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q100">
         <v>1.46</v>
       </c>
       <c r="R100">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="S100">
         <v>2.14</v>
@@ -25397,7 +25397,7 @@
         <v>1.47</v>
       </c>
       <c r="U100">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="V100">
         <v>1.92</v>
@@ -25421,7 +25421,7 @@
         <v>25</v>
       </c>
       <c r="AC100">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD100">
         <v>11.5</v>
@@ -25451,7 +25451,7 @@
         <v>34</v>
       </c>
       <c r="AM100">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN100">
         <v>19</v>
@@ -25463,7 +25463,7 @@
         <v>28</v>
       </c>
       <c r="AQ100">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR100">
         <v>15.5</v>
@@ -25487,10 +25487,10 @@
         <v>20</v>
       </c>
       <c r="AY100">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ100">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA100">
         <v>20</v>
@@ -25499,7 +25499,7 @@
         <v>30</v>
       </c>
       <c r="BC100">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD100">
         <v>21</v>
@@ -25594,7 +25594,7 @@
         <v>340</v>
       </c>
       <c r="F101">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G101">
         <v>1.48</v>
@@ -25618,28 +25618,28 @@
         <v>1.01</v>
       </c>
       <c r="N101">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="O101">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P101">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q101">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R101">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="S101">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="T101">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="U101">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="V101">
         <v>1.16</v>
@@ -25651,7 +25651,7 @@
         <v>55</v>
       </c>
       <c r="Y101">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="Z101">
         <v>1000</v>
@@ -25660,19 +25660,19 @@
         <v>210</v>
       </c>
       <c r="AB101">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AC101">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AD101">
         <v>29</v>
       </c>
       <c r="AE101">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF101">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG101">
         <v>12</v>
@@ -25681,34 +25681,34 @@
         <v>18</v>
       </c>
       <c r="AI101">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AJ101">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK101">
         <v>13</v>
       </c>
       <c r="AL101">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM101">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="AN101">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="AO101">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP101">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ101">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AR101">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AS101">
         <v>46</v>
@@ -25717,28 +25717,28 @@
         <v>18</v>
       </c>
       <c r="AU101">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AV101">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW101">
         <v>55</v>
       </c>
       <c r="AX101">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY101">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ101">
         <v>16</v>
       </c>
       <c r="BA101">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BB101">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC101">
         <v>12</v>
@@ -25747,10 +25747,10 @@
         <v>18</v>
       </c>
       <c r="BE101">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF101">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BG101">
         <v>27</v>
@@ -25759,7 +25759,7 @@
         <v>1000</v>
       </c>
       <c r="BI101">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BJ101">
         <v>1000</v>
@@ -25777,7 +25777,7 @@
         <v>1000</v>
       </c>
       <c r="BO101">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BP101">
         <v>1000</v>
@@ -25789,13 +25789,13 @@
         <v>1000</v>
       </c>
       <c r="BS101">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT101">
         <v>1000</v>
       </c>
       <c r="BU101">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BV101">
         <v>1000</v>
@@ -25875,7 +25875,7 @@
         <v>1.84</v>
       </c>
       <c r="S102">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T102">
         <v>1.44</v>
@@ -25914,7 +25914,7 @@
         <v>23</v>
       </c>
       <c r="AF102">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG102">
         <v>14</v>
@@ -25944,7 +25944,7 @@
         <v>10.5</v>
       </c>
       <c r="AP102">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ102">
         <v>17.5</v>
@@ -25986,10 +25986,10 @@
         <v>21</v>
       </c>
       <c r="BD102">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE102">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF102">
         <v>10.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-26.xlsx
@@ -1042,7 +1042,7 @@
     <t>FC Cincinnati</t>
   </si>
   <si>
-    <t>2026-09-25 02:45:47</t>
+    <t>2026-09-25 03:59:38</t>
   </si>
 </sst>
 </file>
@@ -1636,7 +1636,7 @@
         <v>241</v>
       </c>
       <c r="F2">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G2">
         <v>1.98</v>
@@ -1681,7 +1681,7 @@
         <v>2.04</v>
       </c>
       <c r="U2">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V2">
         <v>1.24</v>
@@ -1690,7 +1690,7 @@
         <v>2.02</v>
       </c>
       <c r="X2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y2">
         <v>14</v>
@@ -1819,7 +1819,7 @@
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP2">
         <v>1000</v>
@@ -1878,7 +1878,7 @@
         <v>242</v>
       </c>
       <c r="F3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G3">
         <v>3.8</v>
@@ -1914,13 +1914,13 @@
         <v>1.81</v>
       </c>
       <c r="R3">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S3">
         <v>3.05</v>
       </c>
       <c r="T3">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U3">
         <v>2.28</v>
@@ -2004,7 +2004,7 @@
         <v>7.6</v>
       </c>
       <c r="AV3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW3">
         <v>18</v>
@@ -2028,28 +2028,28 @@
         <v>34</v>
       </c>
       <c r="BD3">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BE3">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BF3">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="BG3">
         <v>12</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -2058,46 +2058,46 @@
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="CB3" t="s">
         <v>342</v>
@@ -2132,7 +2132,7 @@
         <v>6.4</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K4">
         <v>3.95</v>
@@ -2153,7 +2153,7 @@
         <v>1.78</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
         <v>1.29</v>
@@ -2162,10 +2162,10 @@
         <v>4.1</v>
       </c>
       <c r="T4">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U4">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V4">
         <v>1.18</v>
@@ -2222,7 +2222,7 @@
         <v>180</v>
       </c>
       <c r="AN4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO4">
         <v>160</v>
@@ -2240,7 +2240,7 @@
         <v>12</v>
       </c>
       <c r="AT4">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU4">
         <v>7.8</v>
@@ -2261,7 +2261,7 @@
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB4">
         <v>14.5</v>
@@ -2273,7 +2273,7 @@
         <v>38</v>
       </c>
       <c r="BE4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF4">
         <v>11.5</v>
@@ -2282,16 +2282,16 @@
         <v>12.5</v>
       </c>
       <c r="BH4">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="BJ4">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -2300,43 +2300,43 @@
         <v>5</v>
       </c>
       <c r="BN4">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
         <v>3.25</v>
       </c>
       <c r="BP4">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
         <v>4.5</v>
       </c>
       <c r="BT4">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
         <v>4.8</v>
       </c>
       <c r="BX4">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
         <v>4.9</v>
       </c>
       <c r="BZ4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
         <v>4.5</v>
@@ -2362,61 +2362,61 @@
         <v>244</v>
       </c>
       <c r="F5">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G5">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="H5">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L5">
         <v>1.28</v>
       </c>
       <c r="M5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N5">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P5">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="Q5">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="R5">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="S5">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="T5">
         <v>1.65</v>
       </c>
       <c r="U5">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V5">
         <v>1.19</v>
       </c>
       <c r="W5">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="X5">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Y5">
         <v>29</v>
@@ -2428,7 +2428,7 @@
         <v>150</v>
       </c>
       <c r="AB5">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC5">
         <v>12</v>
@@ -2440,13 +2440,13 @@
         <v>80</v>
       </c>
       <c r="AF5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AI5">
         <v>65</v>
@@ -2464,7 +2464,7 @@
         <v>95</v>
       </c>
       <c r="AN5">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AO5">
         <v>60</v>
@@ -2476,112 +2476,112 @@
         <v>18.5</v>
       </c>
       <c r="AR5">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AS5">
+        <v>8.4</v>
+      </c>
+      <c r="AT5">
+        <v>11</v>
+      </c>
+      <c r="AU5">
         <v>10</v>
-      </c>
-      <c r="AT5">
-        <v>10</v>
-      </c>
-      <c r="AU5">
-        <v>9.4</v>
       </c>
       <c r="AV5">
         <v>18.5</v>
       </c>
       <c r="AW5">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AX5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY5">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
         <v>14</v>
       </c>
       <c r="BA5">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB5">
         <v>12.5</v>
       </c>
       <c r="BC5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD5">
         <v>21</v>
       </c>
       <c r="BE5">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BF5">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BG5">
         <v>34</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB5" t="s">
         <v>342</v>
@@ -2610,7 +2610,7 @@
         <v>3.85</v>
       </c>
       <c r="H6">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I6">
         <v>2.12</v>
@@ -2622,7 +2622,7 @@
         <v>4</v>
       </c>
       <c r="L6">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M6">
         <v>1.05</v>
@@ -2652,7 +2652,7 @@
         <v>2.34</v>
       </c>
       <c r="V6">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W6">
         <v>1.35</v>
@@ -2670,7 +2670,7 @@
         <v>30</v>
       </c>
       <c r="AB6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AC6">
         <v>8.800000000000001</v>
@@ -2685,10 +2685,10 @@
         <v>32</v>
       </c>
       <c r="AG6">
+        <v>17</v>
+      </c>
+      <c r="AH6">
         <v>18.5</v>
-      </c>
-      <c r="AH6">
-        <v>19.5</v>
       </c>
       <c r="AI6">
         <v>36</v>
@@ -2697,19 +2697,19 @@
         <v>70</v>
       </c>
       <c r="AK6">
+        <v>48</v>
+      </c>
+      <c r="AL6">
         <v>50</v>
-      </c>
-      <c r="AL6">
-        <v>55</v>
       </c>
       <c r="AM6">
         <v>75</v>
       </c>
       <c r="AN6">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP6">
         <v>16.5</v>
@@ -2718,10 +2718,10 @@
         <v>10</v>
       </c>
       <c r="AR6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT6">
         <v>15</v>
@@ -2736,7 +2736,7 @@
         <v>18</v>
       </c>
       <c r="AX6">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY6">
         <v>13.5</v>
@@ -2745,19 +2745,19 @@
         <v>14.5</v>
       </c>
       <c r="BA6">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB6">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC6">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD6">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE6">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF6">
         <v>30</v>
@@ -2766,64 +2766,64 @@
         <v>11</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI6">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK6">
+        <v>8</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>22</v>
+      </c>
+      <c r="BN6">
+        <v>7.2</v>
+      </c>
+      <c r="BO6">
         <v>6.4</v>
       </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>1.01</v>
-      </c>
-      <c r="BN6">
-        <v>1000</v>
-      </c>
-      <c r="BO6">
-        <v>5.4</v>
-      </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU6">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="CB6" t="s">
         <v>342</v>
@@ -2864,34 +2864,34 @@
         <v>3.6</v>
       </c>
       <c r="L7">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M7">
         <v>1.09</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O7">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P7">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="Q7">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R7">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S7">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T7">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U7">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V7">
         <v>1.28</v>
@@ -2900,10 +2900,10 @@
         <v>1.93</v>
       </c>
       <c r="X7">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z7">
         <v>34</v>
@@ -2912,13 +2912,13 @@
         <v>120</v>
       </c>
       <c r="AB7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC7">
         <v>8</v>
       </c>
       <c r="AD7">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE7">
         <v>75</v>
@@ -2927,13 +2927,13 @@
         <v>12.5</v>
       </c>
       <c r="AG7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH7">
         <v>21</v>
       </c>
       <c r="AI7">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ7">
         <v>26</v>
@@ -2948,13 +2948,13 @@
         <v>150</v>
       </c>
       <c r="AN7">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AO7">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
         <v>11.5</v>
@@ -2966,10 +2966,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV7">
         <v>15.5</v>
@@ -2990,7 +2990,7 @@
         <v>8.4</v>
       </c>
       <c r="BB7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC7">
         <v>20</v>
@@ -2999,7 +2999,7 @@
         <v>34</v>
       </c>
       <c r="BE7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF7">
         <v>15.5</v>
@@ -3091,7 +3091,7 @@
         <v>1.78</v>
       </c>
       <c r="G8">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H8">
         <v>5.1</v>
@@ -3118,7 +3118,7 @@
         <v>1.39</v>
       </c>
       <c r="P8">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q8">
         <v>2.22</v>
@@ -3130,7 +3130,7 @@
         <v>4.2</v>
       </c>
       <c r="T8">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U8">
         <v>1.82</v>
@@ -3145,7 +3145,7 @@
         <v>14.5</v>
       </c>
       <c r="Y8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z8">
         <v>44</v>
@@ -3154,10 +3154,10 @@
         <v>190</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AC8">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8">
         <v>23</v>
@@ -3178,7 +3178,7 @@
         <v>95</v>
       </c>
       <c r="AJ8">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AK8">
         <v>23</v>
@@ -3202,10 +3202,10 @@
         <v>13</v>
       </c>
       <c r="AR8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS8">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT8">
         <v>6.4</v>
@@ -3217,7 +3217,7 @@
         <v>17.5</v>
       </c>
       <c r="AW8">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX8">
         <v>8.800000000000001</v>
@@ -3229,7 +3229,7 @@
         <v>19.5</v>
       </c>
       <c r="BA8">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB8">
         <v>15.5</v>
@@ -3238,16 +3238,16 @@
         <v>18</v>
       </c>
       <c r="BD8">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE8">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF8">
         <v>12.5</v>
       </c>
       <c r="BG8">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH8">
         <v>3.6</v>
@@ -3259,13 +3259,13 @@
         <v>13.5</v>
       </c>
       <c r="BK8">
-        <v>8.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BN8">
         <v>5</v>
@@ -3277,37 +3277,37 @@
         <v>15.5</v>
       </c>
       <c r="BQ8">
-        <v>9.4</v>
+        <v>3.7</v>
       </c>
       <c r="BR8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS8">
-        <v>23</v>
+        <v>4.3</v>
       </c>
       <c r="BT8">
         <v>10.5</v>
       </c>
       <c r="BU8">
-        <v>6.6</v>
+        <v>3.35</v>
       </c>
       <c r="BV8">
         <v>65</v>
       </c>
       <c r="BW8">
-        <v>38</v>
+        <v>4.5</v>
       </c>
       <c r="BX8">
         <v>80</v>
       </c>
       <c r="BY8">
-        <v>46</v>
+        <v>4.6</v>
       </c>
       <c r="BZ8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA8">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="CB8" t="s">
         <v>342</v>
@@ -3363,13 +3363,13 @@
         <v>2</v>
       </c>
       <c r="Q9">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R9">
         <v>1.39</v>
       </c>
       <c r="S9">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T9">
         <v>1.8</v>
@@ -3381,7 +3381,7 @@
         <v>1.33</v>
       </c>
       <c r="W9">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X9">
         <v>15</v>
@@ -3605,13 +3605,13 @@
         <v>2.04</v>
       </c>
       <c r="Q10">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R10">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S10">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T10">
         <v>1.71</v>
@@ -3632,7 +3632,7 @@
         <v>13</v>
       </c>
       <c r="Z10">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AA10">
         <v>55</v>
@@ -3647,7 +3647,7 @@
         <v>13</v>
       </c>
       <c r="AE10">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF10">
         <v>22</v>
@@ -3689,7 +3689,7 @@
         <v>17.5</v>
       </c>
       <c r="AS10">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT10">
         <v>10.5</v>
@@ -3701,7 +3701,7 @@
         <v>11</v>
       </c>
       <c r="AW10">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX10">
         <v>15.5</v>
@@ -3713,19 +3713,19 @@
         <v>14.5</v>
       </c>
       <c r="BA10">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB10">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BC10">
         <v>20</v>
       </c>
       <c r="BD10">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE10">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF10">
         <v>18</v>
@@ -3841,7 +3841,7 @@
         <v>3.6</v>
       </c>
       <c r="O11">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P11">
         <v>1.86</v>
@@ -3859,7 +3859,7 @@
         <v>1.8</v>
       </c>
       <c r="U11">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V11">
         <v>1.73</v>
@@ -3871,7 +3871,7 @@
         <v>16.5</v>
       </c>
       <c r="Y11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z11">
         <v>17.5</v>
@@ -3889,13 +3889,13 @@
         <v>14</v>
       </c>
       <c r="AE11">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF11">
         <v>26</v>
       </c>
       <c r="AG11">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AH11">
         <v>22</v>
@@ -3919,7 +3919,7 @@
         <v>50</v>
       </c>
       <c r="AO11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP11">
         <v>11.5</v>
@@ -3958,7 +3958,7 @@
         <v>29</v>
       </c>
       <c r="BB11">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC11">
         <v>32</v>
@@ -3979,37 +3979,37 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BN11">
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BT11">
         <v>1000</v>
@@ -4021,19 +4021,19 @@
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="CB11" t="s">
         <v>342</v>
@@ -4062,7 +4062,7 @@
         <v>1.64</v>
       </c>
       <c r="H12">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I12">
         <v>7.4</v>
@@ -4074,31 +4074,31 @@
         <v>4.5</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M12">
         <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O12">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P12">
         <v>1.88</v>
       </c>
       <c r="Q12">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R12">
         <v>1.34</v>
       </c>
       <c r="S12">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="T12">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U12">
         <v>1.83</v>
@@ -4122,10 +4122,10 @@
         <v>250</v>
       </c>
       <c r="AB12">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD12">
         <v>29</v>
@@ -4146,7 +4146,7 @@
         <v>120</v>
       </c>
       <c r="AJ12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK12">
         <v>24</v>
@@ -4167,13 +4167,13 @@
         <v>13</v>
       </c>
       <c r="AQ12">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AR12">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS12">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT12">
         <v>6.6</v>
@@ -4185,7 +4185,7 @@
         <v>17</v>
       </c>
       <c r="AW12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX12">
         <v>7.8</v>
@@ -4194,10 +4194,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ12">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA12">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB12">
         <v>13.5</v>
@@ -4206,76 +4206,76 @@
         <v>16</v>
       </c>
       <c r="BD12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG12">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BO12">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ12">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB12" t="s">
         <v>342</v>
@@ -4304,10 +4304,10 @@
         <v>3.05</v>
       </c>
       <c r="H13">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="I13">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J13">
         <v>3.7</v>
@@ -4322,13 +4322,13 @@
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O13">
         <v>1.22</v>
       </c>
       <c r="P13">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q13">
         <v>1.63</v>
@@ -4570,7 +4570,7 @@
         <v>1.49</v>
       </c>
       <c r="P14">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4582,10 +4582,10 @@
         <v>4.7</v>
       </c>
       <c r="T14">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U14">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V14">
         <v>1.51</v>
@@ -4618,13 +4618,13 @@
         <v>42</v>
       </c>
       <c r="AF14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG14">
         <v>14</v>
       </c>
       <c r="AH14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI14">
         <v>70</v>
@@ -4648,16 +4648,16 @@
         <v>46</v>
       </c>
       <c r="AP14">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ14">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR14">
         <v>15</v>
       </c>
       <c r="AS14">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT14">
         <v>8.199999999999999</v>
@@ -4669,7 +4669,7 @@
         <v>11.5</v>
       </c>
       <c r="AW14">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX14">
         <v>16</v>
@@ -4681,25 +4681,25 @@
         <v>18</v>
       </c>
       <c r="BA14">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB14">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC14">
         <v>32</v>
       </c>
       <c r="BD14">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF14">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG14">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4800,13 +4800,13 @@
         <v>3.8</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M15">
         <v>1.07</v>
       </c>
       <c r="N15">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O15">
         <v>1.34</v>
@@ -4821,7 +4821,7 @@
         <v>1.36</v>
       </c>
       <c r="S15">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T15">
         <v>1.79</v>
@@ -4944,64 +4944,64 @@
         <v>5.3</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB15" t="s">
         <v>342</v>
@@ -5051,25 +5051,25 @@
         <v>3.85</v>
       </c>
       <c r="O16">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P16">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q16">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="R16">
         <v>1.39</v>
       </c>
       <c r="S16">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T16">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U16">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V16">
         <v>1.38</v>
@@ -5081,7 +5081,7 @@
         <v>17.5</v>
       </c>
       <c r="Y16">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Z16">
         <v>29</v>
@@ -5090,13 +5090,13 @@
         <v>75</v>
       </c>
       <c r="AB16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC16">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD16">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE16">
         <v>44</v>
@@ -5126,7 +5126,7 @@
         <v>110</v>
       </c>
       <c r="AN16">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO16">
         <v>40</v>
@@ -5141,16 +5141,16 @@
         <v>21</v>
       </c>
       <c r="AS16">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT16">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU16">
         <v>7.4</v>
       </c>
       <c r="AV16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW16">
         <v>30</v>
@@ -5159,31 +5159,31 @@
         <v>12.5</v>
       </c>
       <c r="AY16">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ16">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA16">
+        <v>7.4</v>
+      </c>
+      <c r="BB16">
         <v>6.8</v>
-      </c>
-      <c r="BB16">
-        <v>6.2</v>
       </c>
       <c r="BC16">
         <v>18</v>
       </c>
       <c r="BD16">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE16">
+        <v>7.8</v>
+      </c>
+      <c r="BF16">
+        <v>14</v>
+      </c>
+      <c r="BG16">
         <v>7</v>
-      </c>
-      <c r="BF16">
-        <v>13.5</v>
-      </c>
-      <c r="BG16">
-        <v>6.4</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -5266,19 +5266,19 @@
         <v>256</v>
       </c>
       <c r="F17">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="G17">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="H17">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I17">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="J17">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="K17">
         <v>3.35</v>
@@ -5287,145 +5287,145 @@
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N17">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="O17">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P17">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="Q17">
         <v>2.24</v>
       </c>
       <c r="R17">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S17">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T17">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="U17">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X17">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Y17">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB17">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC17">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP17">
-        <v>1.27</v>
+        <v>9.4</v>
       </c>
       <c r="AQ17">
-        <v>1.29</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR17">
-        <v>1.39</v>
+        <v>17</v>
       </c>
       <c r="AS17">
-        <v>1.39</v>
+        <v>4.8</v>
       </c>
       <c r="AT17">
-        <v>1.27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU17">
-        <v>1.22</v>
+        <v>6.6</v>
       </c>
       <c r="AV17">
-        <v>1.39</v>
+        <v>12</v>
       </c>
       <c r="AW17">
-        <v>1.39</v>
+        <v>4.7</v>
       </c>
       <c r="AX17">
-        <v>1.39</v>
+        <v>14.5</v>
       </c>
       <c r="AY17">
-        <v>1.39</v>
+        <v>11</v>
       </c>
       <c r="AZ17">
-        <v>1.39</v>
+        <v>16.5</v>
       </c>
       <c r="BA17">
-        <v>1.39</v>
+        <v>4.8</v>
       </c>
       <c r="BB17">
-        <v>1.39</v>
+        <v>4.7</v>
       </c>
       <c r="BC17">
-        <v>1.39</v>
+        <v>4.6</v>
       </c>
       <c r="BD17">
-        <v>1.39</v>
+        <v>4.7</v>
       </c>
       <c r="BE17">
-        <v>1.39</v>
+        <v>5</v>
       </c>
       <c r="BF17">
-        <v>1.39</v>
+        <v>4.5</v>
       </c>
       <c r="BG17">
-        <v>1.39</v>
+        <v>4.7</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5511,7 +5511,7 @@
         <v>3.4</v>
       </c>
       <c r="G18">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="H18">
         <v>2.16</v>
@@ -5529,43 +5529,43 @@
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N18">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O18">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P18">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q18">
         <v>1.91</v>
       </c>
       <c r="R18">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S18">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T18">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="U18">
         <v>2.16</v>
       </c>
       <c r="V18">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="W18">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X18">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y18">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z18">
         <v>15</v>
@@ -5574,10 +5574,10 @@
         <v>34</v>
       </c>
       <c r="AB18">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC18">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD18">
         <v>11.5</v>
@@ -5586,10 +5586,10 @@
         <v>26</v>
       </c>
       <c r="AF18">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG18">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH18">
         <v>18</v>
@@ -5613,7 +5613,7 @@
         <v>42</v>
       </c>
       <c r="AO18">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AP18">
         <v>13</v>
@@ -5622,22 +5622,22 @@
         <v>9</v>
       </c>
       <c r="AR18">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS18">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT18">
         <v>12</v>
       </c>
       <c r="AU18">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV18">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW18">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX18">
         <v>20</v>
@@ -5646,28 +5646,28 @@
         <v>13</v>
       </c>
       <c r="AZ18">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA18">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="BB18">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC18">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BD18">
         <v>38</v>
       </c>
       <c r="BE18">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BF18">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG18">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5768,7 +5768,7 @@
         <v>4.6</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M19">
         <v>1.05</v>
@@ -5801,7 +5801,7 @@
         <v>1.19</v>
       </c>
       <c r="W19">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X19">
         <v>23</v>
@@ -5912,64 +5912,64 @@
         <v>8</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="CB19" t="s">
         <v>342</v>
@@ -6234,7 +6234,7 @@
         <v>260</v>
       </c>
       <c r="F21">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="G21">
         <v>2.18</v>
@@ -6246,10 +6246,10 @@
         <v>5.9</v>
       </c>
       <c r="J21">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K21">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -6476,163 +6476,163 @@
         <v>261</v>
       </c>
       <c r="F22">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="G22">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="H22">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="I22">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J22">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="K22">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="L22">
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N22">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="O22">
         <v>1.26</v>
       </c>
       <c r="P22">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="Q22">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="R22">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S22">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V22">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W22">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP22">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AQ22">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AR22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU22">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV22">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AW22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX22">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AY22">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AZ22">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB22">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BC22">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BD22">
         <v>1.03</v>
       </c>
       <c r="BE22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG22">
         <v>1.01</v>
@@ -6727,7 +6727,7 @@
         <v>1.68</v>
       </c>
       <c r="I23">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="J23">
         <v>3.1</v>
@@ -6766,7 +6766,7 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="W23">
         <v>1.13</v>
@@ -6978,7 +6978,7 @@
         <v>3.75</v>
       </c>
       <c r="L24">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M24">
         <v>1.06</v>
@@ -7011,7 +7011,7 @@
         <v>1.43</v>
       </c>
       <c r="W24">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X24">
         <v>18</v>
@@ -7122,64 +7122,64 @@
         <v>23</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI24">
-        <v>1.51</v>
+        <v>3.4</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK24">
-        <v>2.04</v>
+        <v>8</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>2.38</v>
+        <v>15</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO24">
-        <v>1.76</v>
+        <v>4.8</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ24">
-        <v>2.38</v>
+        <v>8.6</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS24">
-        <v>2.38</v>
+        <v>10.5</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU24">
-        <v>1.88</v>
+        <v>5.9</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW24">
-        <v>2.38</v>
+        <v>10</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY24">
-        <v>2.38</v>
+        <v>11.5</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA24">
-        <v>2.38</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB24" t="s">
         <v>342</v>
@@ -7928,16 +7928,16 @@
         <v>267</v>
       </c>
       <c r="F28">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="G28">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="H28">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I28">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J28">
         <v>3.25</v>
@@ -7946,7 +7946,7 @@
         <v>3.3</v>
       </c>
       <c r="L28">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M28">
         <v>1.1</v>
@@ -7970,16 +7970,16 @@
         <v>4.4</v>
       </c>
       <c r="T28">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U28">
         <v>1.97</v>
       </c>
       <c r="V28">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W28">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X28">
         <v>10.5</v>
@@ -7991,7 +7991,7 @@
         <v>18</v>
       </c>
       <c r="AA28">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB28">
         <v>9.6</v>
@@ -8006,7 +8006,7 @@
         <v>40</v>
       </c>
       <c r="AF28">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG28">
         <v>13</v>
@@ -8045,10 +8045,10 @@
         <v>17</v>
       </c>
       <c r="AS28">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AT28">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU28">
         <v>6.8</v>
@@ -8060,7 +8060,7 @@
         <v>34</v>
       </c>
       <c r="AX28">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY28">
         <v>12</v>
@@ -8072,16 +8072,16 @@
         <v>50</v>
       </c>
       <c r="BB28">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BC28">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD28">
         <v>48</v>
       </c>
       <c r="BE28">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BF28">
         <v>30</v>
@@ -8090,7 +8090,7 @@
         <v>34</v>
       </c>
       <c r="BH28">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI28">
         <v>2.5</v>
@@ -8418,16 +8418,16 @@
         <v>1.79</v>
       </c>
       <c r="H30">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I30">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J30">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K30">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8660,7 +8660,7 @@
         <v>1.79</v>
       </c>
       <c r="H31">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I31">
         <v>15</v>
@@ -8669,7 +8669,7 @@
         <v>3.85</v>
       </c>
       <c r="K31">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8899,7 +8899,7 @@
         <v>1.62</v>
       </c>
       <c r="G32">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H32">
         <v>5.9</v>
@@ -8935,7 +8935,7 @@
         <v>1.52</v>
       </c>
       <c r="S32">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T32">
         <v>1.79</v>
@@ -8947,7 +8947,7 @@
         <v>1.18</v>
       </c>
       <c r="W32">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X32">
         <v>24</v>
@@ -9055,7 +9055,7 @@
         <v>7</v>
       </c>
       <c r="BG32">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -9141,10 +9141,10 @@
         <v>2.68</v>
       </c>
       <c r="G33">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H33">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="I33">
         <v>2.76</v>
@@ -9162,7 +9162,7 @@
         <v>1.05</v>
       </c>
       <c r="N33">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O33">
         <v>1.24</v>
@@ -9180,13 +9180,13 @@
         <v>2.82</v>
       </c>
       <c r="T33">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U33">
         <v>2.46</v>
       </c>
       <c r="V33">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
         <v>1.56</v>
@@ -9273,13 +9273,13 @@
         <v>17.5</v>
       </c>
       <c r="AY33">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AZ33">
         <v>13.5</v>
       </c>
       <c r="BA33">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB33">
         <v>8.6</v>
@@ -9288,7 +9288,7 @@
         <v>21</v>
       </c>
       <c r="BD33">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE33">
         <v>9.6</v>
@@ -9327,7 +9327,7 @@
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BR33">
         <v>1000</v>
@@ -9345,7 +9345,7 @@
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BX33">
         <v>1000</v>
@@ -9380,7 +9380,7 @@
         <v>273</v>
       </c>
       <c r="F34">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G34">
         <v>1.43</v>
@@ -9392,10 +9392,10 @@
         <v>8.4</v>
       </c>
       <c r="J34">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K34">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>1.2</v>
@@ -9422,13 +9422,13 @@
         <v>2.08</v>
       </c>
       <c r="T34">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U34">
         <v>2.38</v>
       </c>
       <c r="V34">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W34">
         <v>3.3</v>
@@ -9497,7 +9497,7 @@
         <v>7.4</v>
       </c>
       <c r="AS34">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT34">
         <v>12.5</v>
@@ -9545,7 +9545,7 @@
         <v>1000</v>
       </c>
       <c r="BI34">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BJ34">
         <v>1000</v>
@@ -9557,49 +9557,49 @@
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BN34">
         <v>1000</v>
       </c>
       <c r="BO34">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BP34">
         <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BT34">
         <v>1000</v>
       </c>
       <c r="BU34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BX34">
         <v>1000</v>
       </c>
       <c r="BY34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BZ34">
         <v>1000</v>
       </c>
       <c r="CA34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="CB34" t="s">
         <v>342</v>
@@ -9637,7 +9637,7 @@
         <v>1.12</v>
       </c>
       <c r="K35">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L35">
         <v>1.01</v>
@@ -9655,13 +9655,13 @@
         <v>1.09</v>
       </c>
       <c r="Q35">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="R35">
         <v>1.07</v>
       </c>
       <c r="S35">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="T35">
         <v>1.01</v>
@@ -9864,16 +9864,16 @@
         <v>275</v>
       </c>
       <c r="F36">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G36">
         <v>1.95</v>
       </c>
       <c r="H36">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I36">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J36">
         <v>3.7</v>
@@ -9882,7 +9882,7 @@
         <v>3.8</v>
       </c>
       <c r="L36">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M36">
         <v>1.08</v>
@@ -9900,19 +9900,19 @@
         <v>2.12</v>
       </c>
       <c r="R36">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S36">
         <v>3.85</v>
       </c>
       <c r="T36">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U36">
         <v>1.96</v>
       </c>
       <c r="V36">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W36">
         <v>2.04</v>
@@ -9933,7 +9933,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC36">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD36">
         <v>18.5</v>
@@ -9981,7 +9981,7 @@
         <v>29</v>
       </c>
       <c r="AS36">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT36">
         <v>7.8</v>
@@ -10017,7 +10017,7 @@
         <v>34</v>
       </c>
       <c r="BE36">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF36">
         <v>13</v>
@@ -10026,64 +10026,64 @@
         <v>55</v>
       </c>
       <c r="BH36">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI36">
-        <v>1.24</v>
+        <v>2.92</v>
       </c>
       <c r="BJ36">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK36">
-        <v>1.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="BN36">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO36">
-        <v>1.42</v>
+        <v>4</v>
       </c>
       <c r="BP36">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ36">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="BR36">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS36">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="BT36">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU36">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="BV36">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW36">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="BZ36">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA36">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="CB36" t="s">
         <v>342</v>
@@ -10115,7 +10115,7 @@
         <v>2.06</v>
       </c>
       <c r="I37">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="J37">
         <v>3.5</v>
@@ -10154,7 +10154,7 @@
         <v>1.01</v>
       </c>
       <c r="V37">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="W37">
         <v>1.35</v>
@@ -10378,10 +10378,10 @@
         <v>1.25</v>
       </c>
       <c r="P38">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="Q38">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R38">
         <v>1.41</v>
@@ -10468,7 +10468,7 @@
         <v>9.6</v>
       </c>
       <c r="AT38">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AU38">
         <v>8.800000000000001</v>
@@ -10590,7 +10590,7 @@
         <v>278</v>
       </c>
       <c r="F39">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="G39">
         <v>4.8</v>
@@ -10599,13 +10599,13 @@
         <v>2</v>
       </c>
       <c r="I39">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="J39">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K39">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L39">
         <v>1.01</v>
@@ -10614,19 +10614,19 @@
         <v>1.1</v>
       </c>
       <c r="N39">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O39">
         <v>1.44</v>
       </c>
       <c r="P39">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="Q39">
         <v>2.32</v>
       </c>
       <c r="R39">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S39">
         <v>4.3</v>
@@ -10638,7 +10638,7 @@
         <v>1.74</v>
       </c>
       <c r="V39">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="W39">
         <v>1.27</v>
@@ -10647,7 +10647,7 @@
         <v>970</v>
       </c>
       <c r="Y39">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="Z39">
         <v>970</v>
@@ -10659,7 +10659,7 @@
         <v>23</v>
       </c>
       <c r="AC39">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AD39">
         <v>23</v>
@@ -10668,7 +10668,7 @@
         <v>1000</v>
       </c>
       <c r="AF39">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG39">
         <v>1000</v>
@@ -10698,58 +10698,58 @@
         <v>1000</v>
       </c>
       <c r="AP39">
-        <v>1.03</v>
+        <v>1.76</v>
       </c>
       <c r="AQ39">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AR39">
-        <v>1.03</v>
+        <v>1.78</v>
       </c>
       <c r="AS39">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="AT39">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="AU39">
         <v>5.9</v>
       </c>
       <c r="AV39">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW39">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="AX39">
-        <v>1.03</v>
+        <v>1.85</v>
       </c>
       <c r="AY39">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="AZ39">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="BA39">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="BB39">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="BC39">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="BD39">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="BE39">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="BF39">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BG39">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BH39">
         <v>3.45</v>
@@ -10761,7 +10761,7 @@
         <v>1000</v>
       </c>
       <c r="BK39">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="BL39">
         <v>1000</v>
@@ -10835,7 +10835,7 @@
         <v>2.76</v>
       </c>
       <c r="G40">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="H40">
         <v>2.18</v>
@@ -10844,7 +10844,7 @@
         <v>2.5</v>
       </c>
       <c r="J40">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="K40">
         <v>4.7</v>
@@ -10853,10 +10853,10 @@
         <v>1.01</v>
       </c>
       <c r="M40">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N40">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O40">
         <v>1.11</v>
@@ -10865,10 +10865,10 @@
         <v>2.62</v>
       </c>
       <c r="Q40">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="R40">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="S40">
         <v>2.16</v>
@@ -10883,7 +10883,7 @@
         <v>1.66</v>
       </c>
       <c r="W40">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="X40">
         <v>1000</v>
@@ -10955,10 +10955,10 @@
         <v>12</v>
       </c>
       <c r="AU40">
-        <v>2.24</v>
+        <v>6.6</v>
       </c>
       <c r="AV40">
-        <v>2.28</v>
+        <v>7.6</v>
       </c>
       <c r="AW40">
         <v>13</v>
@@ -10967,16 +10967,16 @@
         <v>15.5</v>
       </c>
       <c r="AY40">
-        <v>2.3</v>
+        <v>8.4</v>
       </c>
       <c r="AZ40">
-        <v>2.32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA40">
         <v>16</v>
       </c>
       <c r="BB40">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BC40">
         <v>16.5</v>
@@ -10991,7 +10991,7 @@
         <v>9.6</v>
       </c>
       <c r="BG40">
-        <v>2.24</v>
+        <v>6.8</v>
       </c>
       <c r="BH40">
         <v>1000</v>
@@ -11077,13 +11077,13 @@
         <v>2.54</v>
       </c>
       <c r="G41">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="H41">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I41">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J41">
         <v>4</v>
@@ -11104,34 +11104,34 @@
         <v>1.17</v>
       </c>
       <c r="P41">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="Q41">
         <v>1.5</v>
       </c>
       <c r="R41">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S41">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="T41">
         <v>1.5</v>
       </c>
       <c r="U41">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="V41">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W41">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="X41">
         <v>34</v>
       </c>
       <c r="Y41">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z41">
         <v>24</v>
@@ -11140,7 +11140,7 @@
         <v>38</v>
       </c>
       <c r="AB41">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC41">
         <v>13</v>
@@ -11191,7 +11191,7 @@
         <v>18.5</v>
       </c>
       <c r="AS41">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AT41">
         <v>16</v>
@@ -11215,10 +11215,10 @@
         <v>12.5</v>
       </c>
       <c r="BA41">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BB41">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BC41">
         <v>17</v>
@@ -11227,13 +11227,13 @@
         <v>20</v>
       </c>
       <c r="BE41">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BF41">
         <v>11.5</v>
       </c>
       <c r="BG41">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -11561,10 +11561,10 @@
         <v>5</v>
       </c>
       <c r="G43">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H43">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I43">
         <v>1.68</v>
@@ -11573,7 +11573,7 @@
         <v>4.8</v>
       </c>
       <c r="K43">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L43">
         <v>1.01</v>
@@ -11588,10 +11588,10 @@
         <v>1.11</v>
       </c>
       <c r="P43">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q43">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R43">
         <v>1.98</v>
@@ -11609,7 +11609,7 @@
         <v>2.46</v>
       </c>
       <c r="W43">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X43">
         <v>55</v>
@@ -11621,7 +11621,7 @@
         <v>18</v>
       </c>
       <c r="AA43">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB43">
         <v>36</v>
@@ -11663,10 +11663,10 @@
         <v>32</v>
       </c>
       <c r="AO43">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AP43">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ43">
         <v>16</v>
@@ -11678,13 +11678,13 @@
         <v>16.5</v>
       </c>
       <c r="AT43">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU43">
         <v>12</v>
       </c>
       <c r="AV43">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW43">
         <v>12.5</v>
@@ -11705,16 +11705,16 @@
         <v>7.6</v>
       </c>
       <c r="BC43">
+        <v>7.4</v>
+      </c>
+      <c r="BD43">
         <v>7.2</v>
-      </c>
-      <c r="BD43">
-        <v>6.8</v>
       </c>
       <c r="BE43">
         <v>36</v>
       </c>
       <c r="BF43">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="BG43">
         <v>4.3</v>
@@ -11809,7 +11809,7 @@
         <v>4.9</v>
       </c>
       <c r="I44">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J44">
         <v>4.3</v>
@@ -11824,142 +11824,142 @@
         <v>1.02</v>
       </c>
       <c r="N44">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="O44">
         <v>1.2</v>
       </c>
       <c r="P44">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="Q44">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="R44">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="S44">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T44">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="U44">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="V44">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W44">
         <v>2.3</v>
       </c>
       <c r="X44">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y44">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z44">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA44">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB44">
-        <v>30</v>
+        <v>12.5</v>
       </c>
       <c r="AC44">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD44">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE44">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF44">
-        <v>29</v>
+        <v>12.5</v>
       </c>
       <c r="AG44">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH44">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI44">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ44">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK44">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL44">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM44">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN44">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AO44">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP44">
-        <v>1.4</v>
+        <v>17.5</v>
       </c>
       <c r="AQ44">
-        <v>1.4</v>
+        <v>17</v>
       </c>
       <c r="AR44">
-        <v>1.4</v>
+        <v>9.4</v>
       </c>
       <c r="AS44">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT44">
-        <v>1.32</v>
+        <v>10.5</v>
       </c>
       <c r="AU44">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AV44">
-        <v>1.4</v>
+        <v>16.5</v>
       </c>
       <c r="AW44">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="AX44">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AY44">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AZ44">
-        <v>1.4</v>
+        <v>15</v>
       </c>
       <c r="BA44">
-        <v>1.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB44">
-        <v>1.4</v>
+        <v>15</v>
       </c>
       <c r="BC44">
-        <v>1.4</v>
+        <v>14</v>
       </c>
       <c r="BD44">
-        <v>1.4</v>
+        <v>20</v>
       </c>
       <c r="BE44">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="BF44">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG44">
-        <v>1.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH44">
         <v>1000</v>
@@ -12042,10 +12042,10 @@
         <v>284</v>
       </c>
       <c r="F45">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G45">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H45">
         <v>3.15</v>
@@ -12054,10 +12054,10 @@
         <v>3.5</v>
       </c>
       <c r="J45">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="K45">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="L45">
         <v>1.01</v>
@@ -12081,16 +12081,16 @@
         <v>1.42</v>
       </c>
       <c r="S45">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="T45">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U45">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V45">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W45">
         <v>1.73</v>
@@ -12293,13 +12293,13 @@
         <v>3.6</v>
       </c>
       <c r="I46">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J46">
         <v>3.55</v>
       </c>
       <c r="K46">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L46">
         <v>1.01</v>
@@ -12329,7 +12329,7 @@
         <v>1.76</v>
       </c>
       <c r="U46">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V46">
         <v>1.35</v>
@@ -12526,16 +12526,16 @@
         <v>286</v>
       </c>
       <c r="F47">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G47">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H47">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I47">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J47">
         <v>3.55</v>
@@ -12550,7 +12550,7 @@
         <v>1.06</v>
       </c>
       <c r="N47">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O47">
         <v>1.3</v>
@@ -12559,7 +12559,7 @@
         <v>2.08</v>
       </c>
       <c r="Q47">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R47">
         <v>1.42</v>
@@ -12574,7 +12574,7 @@
         <v>2.28</v>
       </c>
       <c r="V47">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W47">
         <v>1.51</v>
@@ -12586,7 +12586,7 @@
         <v>12</v>
       </c>
       <c r="Z47">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA47">
         <v>40</v>
@@ -12628,7 +12628,7 @@
         <v>85</v>
       </c>
       <c r="AN47">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO47">
         <v>24</v>
@@ -12637,13 +12637,13 @@
         <v>13</v>
       </c>
       <c r="AQ47">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR47">
         <v>17.5</v>
       </c>
       <c r="AS47">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT47">
         <v>11</v>
@@ -12655,7 +12655,7 @@
         <v>10</v>
       </c>
       <c r="AW47">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX47">
         <v>19</v>
@@ -12667,19 +12667,19 @@
         <v>13.5</v>
       </c>
       <c r="BA47">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB47">
+        <v>7.4</v>
+      </c>
+      <c r="BC47">
         <v>7</v>
       </c>
-      <c r="BC47">
-        <v>6.6</v>
-      </c>
       <c r="BD47">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE47">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF47">
         <v>18</v>
@@ -12774,7 +12774,7 @@
         <v>1.9</v>
       </c>
       <c r="H48">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I48">
         <v>4.8</v>
@@ -12783,7 +12783,7 @@
         <v>4.1</v>
       </c>
       <c r="K48">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L48">
         <v>1.01</v>
@@ -12798,22 +12798,22 @@
         <v>1.22</v>
       </c>
       <c r="P48">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q48">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="R48">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="S48">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T48">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U48">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="V48">
         <v>1.26</v>
@@ -12825,7 +12825,7 @@
         <v>26</v>
       </c>
       <c r="Y48">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z48">
         <v>42</v>
@@ -12852,13 +12852,13 @@
         <v>11</v>
       </c>
       <c r="AH48">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI48">
         <v>60</v>
       </c>
       <c r="AJ48">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK48">
         <v>17.5</v>
@@ -12882,13 +12882,13 @@
         <v>18</v>
       </c>
       <c r="AR48">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS48">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT48">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU48">
         <v>8.6</v>
@@ -12897,7 +12897,7 @@
         <v>15.5</v>
       </c>
       <c r="AW48">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX48">
         <v>11</v>
@@ -12909,7 +12909,7 @@
         <v>14.5</v>
       </c>
       <c r="BA48">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB48">
         <v>16</v>
@@ -12918,10 +12918,10 @@
         <v>14.5</v>
       </c>
       <c r="BD48">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE48">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF48">
         <v>7.2</v>
@@ -13013,19 +13013,19 @@
         <v>2.46</v>
       </c>
       <c r="G49">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H49">
         <v>2.62</v>
       </c>
       <c r="I49">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="J49">
         <v>3.9</v>
       </c>
       <c r="K49">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L49">
         <v>1.01</v>
@@ -13049,7 +13049,7 @@
         <v>1.64</v>
       </c>
       <c r="S49">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="T49">
         <v>1.54</v>
@@ -13058,7 +13058,7 @@
         <v>2.64</v>
       </c>
       <c r="V49">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W49">
         <v>1.6</v>
@@ -13136,7 +13136,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV49">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW49">
         <v>21</v>
@@ -13252,10 +13252,10 @@
         <v>289</v>
       </c>
       <c r="F50">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G50">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H50">
         <v>3.3</v>
@@ -13267,10 +13267,10 @@
         <v>3.75</v>
       </c>
       <c r="K50">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L50">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M50">
         <v>1.05</v>
@@ -13279,19 +13279,19 @@
         <v>4.4</v>
       </c>
       <c r="O50">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P50">
         <v>2.2</v>
       </c>
       <c r="Q50">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R50">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S50">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="T50">
         <v>1.63</v>
@@ -13303,13 +13303,13 @@
         <v>1.37</v>
       </c>
       <c r="W50">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X50">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y50">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z50">
         <v>40</v>
@@ -13330,7 +13330,7 @@
         <v>38</v>
       </c>
       <c r="AF50">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG50">
         <v>11.5</v>
@@ -13345,7 +13345,7 @@
         <v>40</v>
       </c>
       <c r="AK50">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL50">
         <v>34</v>
@@ -13369,7 +13369,7 @@
         <v>16</v>
       </c>
       <c r="AS50">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT50">
         <v>10</v>
@@ -13414,64 +13414,64 @@
         <v>19.5</v>
       </c>
       <c r="BH50">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI50">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BJ50">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK50">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL50">
         <v>1000</v>
       </c>
       <c r="BM50">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN50">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO50">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP50">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ50">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR50">
         <v>1000</v>
       </c>
       <c r="BS50">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT50">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU50">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV50">
         <v>1000</v>
       </c>
       <c r="BW50">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX50">
         <v>1000</v>
       </c>
       <c r="BY50">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ50">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA50">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="CB50" t="s">
         <v>342</v>
@@ -13494,7 +13494,7 @@
         <v>290</v>
       </c>
       <c r="F51">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G51">
         <v>1.85</v>
@@ -13542,7 +13542,7 @@
         <v>2.18</v>
       </c>
       <c r="V51">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W51">
         <v>2.16</v>
@@ -13614,7 +13614,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AT51">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU51">
         <v>8.4</v>
@@ -13629,7 +13629,7 @@
         <v>10.5</v>
       </c>
       <c r="AY51">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ51">
         <v>15.5</v>
@@ -13677,7 +13677,7 @@
         <v>1000</v>
       </c>
       <c r="BO51">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BP51">
         <v>1000</v>
@@ -13856,7 +13856,7 @@
         <v>10</v>
       </c>
       <c r="AT52">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU52">
         <v>8.800000000000001</v>
@@ -13978,7 +13978,7 @@
         <v>292</v>
       </c>
       <c r="F53">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G53">
         <v>2.36</v>
@@ -13990,7 +13990,7 @@
         <v>3.35</v>
       </c>
       <c r="J53">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K53">
         <v>4</v>
@@ -14017,7 +14017,7 @@
         <v>1.54</v>
       </c>
       <c r="S53">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T53">
         <v>1.6</v>
@@ -14032,7 +14032,7 @@
         <v>1.73</v>
       </c>
       <c r="X53">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y53">
         <v>17.5</v>
@@ -14053,7 +14053,7 @@
         <v>16.5</v>
       </c>
       <c r="AE53">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF53">
         <v>18</v>
@@ -14071,10 +14071,10 @@
         <v>34</v>
       </c>
       <c r="AK53">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL53">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM53">
         <v>75</v>
@@ -14083,7 +14083,7 @@
         <v>13</v>
       </c>
       <c r="AO53">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AP53">
         <v>18</v>
@@ -14095,7 +14095,7 @@
         <v>19</v>
       </c>
       <c r="AS53">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT53">
         <v>11.5</v>
@@ -14107,7 +14107,7 @@
         <v>12</v>
       </c>
       <c r="AW53">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX53">
         <v>14.5</v>
@@ -14119,7 +14119,7 @@
         <v>13.5</v>
       </c>
       <c r="BA53">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB53">
         <v>21</v>
@@ -14128,10 +14128,10 @@
         <v>16.5</v>
       </c>
       <c r="BD53">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE53">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF53">
         <v>11</v>
@@ -14223,13 +14223,13 @@
         <v>2.24</v>
       </c>
       <c r="G54">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H54">
         <v>3.55</v>
       </c>
       <c r="I54">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J54">
         <v>3.45</v>
@@ -14256,10 +14256,10 @@
         <v>2.08</v>
       </c>
       <c r="R54">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S54">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T54">
         <v>1.86</v>
@@ -14271,7 +14271,7 @@
         <v>1.37</v>
       </c>
       <c r="W54">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X54">
         <v>13</v>
@@ -14289,7 +14289,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC54">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD54">
         <v>15.5</v>
@@ -14379,13 +14379,13 @@
         <v>17</v>
       </c>
       <c r="BG54">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH54">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI54">
-        <v>1.51</v>
+        <v>2.76</v>
       </c>
       <c r="BJ54">
         <v>1000</v>
@@ -14462,7 +14462,7 @@
         <v>294</v>
       </c>
       <c r="F55">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G55">
         <v>1.67</v>
@@ -14477,7 +14477,7 @@
         <v>4.8</v>
       </c>
       <c r="K55">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="L55">
         <v>1.01</v>
@@ -14489,7 +14489,7 @@
         <v>7</v>
       </c>
       <c r="O55">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P55">
         <v>3.05</v>
@@ -14552,7 +14552,7 @@
         <v>55</v>
       </c>
       <c r="AJ55">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK55">
         <v>15.5</v>
@@ -14946,7 +14946,7 @@
         <v>296</v>
       </c>
       <c r="F57">
-        <v>6</v>
+        <v>2.82</v>
       </c>
       <c r="G57">
         <v>11</v>
@@ -14955,13 +14955,13 @@
         <v>1.43</v>
       </c>
       <c r="I57">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="J57">
         <v>4.3</v>
       </c>
       <c r="K57">
-        <v>7.6</v>
+        <v>950</v>
       </c>
       <c r="L57">
         <v>1.01</v>
@@ -14973,7 +14973,7 @@
         <v>3.2</v>
       </c>
       <c r="O57">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="P57">
         <v>1.98</v>
@@ -14982,7 +14982,7 @@
         <v>1.73</v>
       </c>
       <c r="R57">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S57">
         <v>2.8</v>
@@ -14994,7 +14994,7 @@
         <v>1.01</v>
       </c>
       <c r="V57">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="W57">
         <v>1.1</v>
@@ -15681,13 +15681,13 @@
         <v>1.11</v>
       </c>
       <c r="I60">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="J60">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="K60">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="L60">
         <v>1.26</v>
@@ -15699,28 +15699,28 @@
         <v>5.8</v>
       </c>
       <c r="O60">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P60">
         <v>2.66</v>
       </c>
       <c r="Q60">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R60">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S60">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T60">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="U60">
         <v>1.34</v>
       </c>
       <c r="V60">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W60">
         <v>1.02</v>
@@ -15732,10 +15732,10 @@
         <v>9.6</v>
       </c>
       <c r="Z60">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AA60">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AB60">
         <v>110</v>
@@ -15780,7 +15780,7 @@
         <v>3.1</v>
       </c>
       <c r="AP60">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ60">
         <v>8.199999999999999</v>
@@ -15789,58 +15789,58 @@
         <v>5.7</v>
       </c>
       <c r="AS60">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT60">
         <v>10.5</v>
       </c>
       <c r="AU60">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV60">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="AW60">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX60">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AY60">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AZ60">
+        <v>10.5</v>
+      </c>
+      <c r="BA60">
         <v>11</v>
       </c>
-      <c r="BA60">
-        <v>9</v>
-      </c>
       <c r="BB60">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BC60">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BD60">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BE60">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BF60">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BG60">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="BH60">
         <v>5.8</v>
       </c>
       <c r="BI60">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BJ60">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BK60">
         <v>18</v>
@@ -15852,7 +15852,7 @@
         <v>21</v>
       </c>
       <c r="BN60">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BO60">
         <v>27</v>
@@ -15873,13 +15873,13 @@
         <v>3.35</v>
       </c>
       <c r="BU60">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="BV60">
         <v>5.2</v>
       </c>
       <c r="BW60">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BX60">
         <v>36</v>
@@ -15929,7 +15929,7 @@
         <v>6</v>
       </c>
       <c r="K61">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L61">
         <v>1.33</v>
@@ -15941,7 +15941,7 @@
         <v>4.8</v>
       </c>
       <c r="O61">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P61">
         <v>2.24</v>
@@ -15953,13 +15953,13 @@
         <v>1.49</v>
       </c>
       <c r="S61">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T61">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="U61">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V61">
         <v>1.08</v>
@@ -15980,7 +15980,7 @@
         <v>740</v>
       </c>
       <c r="AB61">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC61">
         <v>13.5</v>
@@ -15989,7 +15989,7 @@
         <v>48</v>
       </c>
       <c r="AE61">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AF61">
         <v>7.4</v>
@@ -16028,10 +16028,10 @@
         <v>32</v>
       </c>
       <c r="AR61">
+        <v>13</v>
+      </c>
+      <c r="AS61">
         <v>13.5</v>
-      </c>
-      <c r="AS61">
-        <v>15</v>
       </c>
       <c r="AT61">
         <v>8</v>
@@ -16043,10 +16043,10 @@
         <v>38</v>
       </c>
       <c r="AW61">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX61">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY61">
         <v>10</v>
@@ -16055,7 +16055,7 @@
         <v>30</v>
       </c>
       <c r="BA61">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BB61">
         <v>8.6</v>
@@ -16064,16 +16064,16 @@
         <v>13.5</v>
       </c>
       <c r="BD61">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BE61">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BF61">
         <v>4.8</v>
       </c>
       <c r="BG61">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH61">
         <v>1000</v>
@@ -16159,7 +16159,7 @@
         <v>2.4</v>
       </c>
       <c r="G62">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H62">
         <v>3.5</v>
@@ -16180,16 +16180,16 @@
         <v>1.11</v>
       </c>
       <c r="N62">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O62">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P62">
         <v>1.63</v>
       </c>
       <c r="Q62">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R62">
         <v>1.23</v>
@@ -16198,19 +16198,19 @@
         <v>5</v>
       </c>
       <c r="T62">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U62">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V62">
         <v>1.38</v>
       </c>
       <c r="W62">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X62">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y62">
         <v>10.5</v>
@@ -16243,7 +16243,7 @@
         <v>23</v>
       </c>
       <c r="AI62">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ62">
         <v>34</v>
@@ -16252,19 +16252,19 @@
         <v>32</v>
       </c>
       <c r="AL62">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM62">
         <v>160</v>
       </c>
       <c r="AN62">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO62">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP62">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ62">
         <v>9.6</v>
@@ -16309,10 +16309,10 @@
         <v>50</v>
       </c>
       <c r="BE62">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BF62">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BG62">
         <v>55</v>
@@ -16422,16 +16422,16 @@
         <v>1.12</v>
       </c>
       <c r="N63">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O63">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P63">
         <v>1.59</v>
       </c>
       <c r="Q63">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R63">
         <v>1.21</v>
@@ -16440,7 +16440,7 @@
         <v>5.3</v>
       </c>
       <c r="T63">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U63">
         <v>1.84</v>
@@ -16473,7 +16473,7 @@
         <v>15</v>
       </c>
       <c r="AE63">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF63">
         <v>14.5</v>
@@ -16491,7 +16491,7 @@
         <v>38</v>
       </c>
       <c r="AK63">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL63">
         <v>65</v>
@@ -16506,7 +16506,7 @@
         <v>90</v>
       </c>
       <c r="AP63">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ63">
         <v>9.4</v>
@@ -16527,7 +16527,7 @@
         <v>14</v>
       </c>
       <c r="AW63">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX63">
         <v>13</v>
@@ -16539,7 +16539,7 @@
         <v>21</v>
       </c>
       <c r="BA63">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BB63">
         <v>30</v>
@@ -16560,7 +16560,7 @@
         <v>50</v>
       </c>
       <c r="BH63">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI63">
         <v>2.44</v>
@@ -16575,7 +16575,7 @@
         <v>1000</v>
       </c>
       <c r="BM63">
-        <v>1.21</v>
+        <v>2.08</v>
       </c>
       <c r="BN63">
         <v>1000</v>
@@ -16587,13 +16587,13 @@
         <v>1000</v>
       </c>
       <c r="BQ63">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BR63">
         <v>1000</v>
       </c>
       <c r="BS63">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BT63">
         <v>1000</v>
@@ -16605,19 +16605,19 @@
         <v>1000</v>
       </c>
       <c r="BW63">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BX63">
         <v>1000</v>
       </c>
       <c r="BY63">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BZ63">
         <v>1000</v>
       </c>
       <c r="CA63">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="CB63" t="s">
         <v>342</v>
@@ -16891,7 +16891,7 @@
         <v>2.42</v>
       </c>
       <c r="I65">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J65">
         <v>3.35</v>
@@ -16906,22 +16906,22 @@
         <v>1.08</v>
       </c>
       <c r="N65">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O65">
         <v>1.37</v>
       </c>
       <c r="P65">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q65">
         <v>2.1</v>
       </c>
       <c r="R65">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S65">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T65">
         <v>1.84</v>
@@ -16930,10 +16930,10 @@
         <v>2.08</v>
       </c>
       <c r="V65">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W65">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X65">
         <v>13</v>
@@ -17002,7 +17002,7 @@
         <v>10.5</v>
       </c>
       <c r="AT65">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU65">
         <v>6.8</v>
@@ -17047,7 +17047,7 @@
         <v>1000</v>
       </c>
       <c r="BI65">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="BJ65">
         <v>11.5</v>
@@ -17059,7 +17059,7 @@
         <v>1000</v>
       </c>
       <c r="BM65">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BN65">
         <v>7.2</v>
@@ -17071,13 +17071,13 @@
         <v>38</v>
       </c>
       <c r="BQ65">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="BR65">
         <v>1000</v>
       </c>
       <c r="BS65">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BT65">
         <v>5.9</v>
@@ -17086,22 +17086,22 @@
         <v>4.3</v>
       </c>
       <c r="BV65">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BW65">
-        <v>1.94</v>
+        <v>4.5</v>
       </c>
       <c r="BX65">
         <v>48</v>
       </c>
       <c r="BY65">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BZ65">
         <v>44</v>
       </c>
       <c r="CA65">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CB65" t="s">
         <v>342</v>
@@ -17130,7 +17130,7 @@
         <v>2.06</v>
       </c>
       <c r="H66">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I66">
         <v>4.8</v>
@@ -17142,13 +17142,13 @@
         <v>3.45</v>
       </c>
       <c r="L66">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="M66">
         <v>1.11</v>
       </c>
       <c r="N66">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="O66">
         <v>1.5</v>
@@ -17163,10 +17163,10 @@
         <v>1.22</v>
       </c>
       <c r="S66">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T66">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U66">
         <v>1.78</v>
@@ -17289,19 +17289,19 @@
         <v>1000</v>
       </c>
       <c r="BI66">
-        <v>1.4</v>
+        <v>2.38</v>
       </c>
       <c r="BJ66">
         <v>1000</v>
       </c>
       <c r="BK66">
-        <v>1.35</v>
+        <v>2.48</v>
       </c>
       <c r="BL66">
         <v>1000</v>
       </c>
       <c r="BM66">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="BN66">
         <v>5.9</v>
@@ -17319,7 +17319,7 @@
         <v>1000</v>
       </c>
       <c r="BS66">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="BT66">
         <v>1000</v>
@@ -17331,19 +17331,19 @@
         <v>1000</v>
       </c>
       <c r="BW66">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="BX66">
         <v>1000</v>
       </c>
       <c r="BY66">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="BZ66">
         <v>1000</v>
       </c>
       <c r="CA66">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="CB66" t="s">
         <v>342</v>
@@ -17614,7 +17614,7 @@
         <v>5.9</v>
       </c>
       <c r="H68">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="I68">
         <v>1.93</v>
@@ -17623,7 +17623,7 @@
         <v>3.6</v>
       </c>
       <c r="K68">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L68">
         <v>1.01</v>
@@ -17641,7 +17641,7 @@
         <v>1.76</v>
       </c>
       <c r="Q68">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R68">
         <v>1.27</v>
@@ -17671,7 +17671,7 @@
         <v>11.5</v>
       </c>
       <c r="AA68">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AB68">
         <v>970</v>
@@ -17680,13 +17680,13 @@
         <v>9</v>
       </c>
       <c r="AD68">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE68">
         <v>1000</v>
       </c>
       <c r="AF68">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG68">
         <v>22</v>
@@ -17716,58 +17716,58 @@
         <v>1000</v>
       </c>
       <c r="AP68">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="AQ68">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="AR68">
-        <v>1.82</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS68">
         <v>16.5</v>
       </c>
       <c r="AT68">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="AU68">
         <v>6</v>
       </c>
       <c r="AV68">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="AW68">
         <v>17</v>
       </c>
       <c r="AX68">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="AY68">
-        <v>16.5</v>
+        <v>2.3</v>
       </c>
       <c r="AZ68">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="BA68">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="BB68">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="BC68">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="BD68">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="BE68">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="BF68">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="BG68">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="BH68">
         <v>1000</v>
@@ -17853,10 +17853,10 @@
         <v>1.34</v>
       </c>
       <c r="G69">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H69">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I69">
         <v>13.5</v>
@@ -17865,7 +17865,7 @@
         <v>5.1</v>
       </c>
       <c r="K69">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L69">
         <v>1.01</v>
@@ -17877,7 +17877,7 @@
         <v>6</v>
       </c>
       <c r="O69">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P69">
         <v>2.8</v>
@@ -17886,19 +17886,19 @@
         <v>1.39</v>
       </c>
       <c r="R69">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S69">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="T69">
         <v>1.57</v>
       </c>
       <c r="U69">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V69">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W69">
         <v>3.1</v>
@@ -17940,7 +17940,7 @@
         <v>1000</v>
       </c>
       <c r="AJ69">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK69">
         <v>1000</v>
@@ -17952,22 +17952,22 @@
         <v>1000</v>
       </c>
       <c r="AN69">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO69">
         <v>1000</v>
       </c>
       <c r="AP69">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AQ69">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AR69">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AS69">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AT69">
         <v>8</v>
@@ -17976,10 +17976,10 @@
         <v>8</v>
       </c>
       <c r="AV69">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AW69">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AX69">
         <v>6.6</v>
@@ -17988,10 +17988,10 @@
         <v>6.4</v>
       </c>
       <c r="AZ69">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="BA69">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="BB69">
         <v>7.2</v>
@@ -18000,16 +18000,16 @@
         <v>7.2</v>
       </c>
       <c r="BD69">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="BE69">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="BF69">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="BG69">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="BH69">
         <v>1000</v>
@@ -18092,7 +18092,7 @@
         <v>309</v>
       </c>
       <c r="F70">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="G70">
         <v>2.12</v>
@@ -18101,13 +18101,13 @@
         <v>3.55</v>
       </c>
       <c r="I70">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J70">
         <v>3.85</v>
       </c>
       <c r="K70">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L70">
         <v>1.01</v>
@@ -18140,7 +18140,7 @@
         <v>2.36</v>
       </c>
       <c r="V70">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W70">
         <v>1.89</v>
@@ -18164,7 +18164,7 @@
         <v>10</v>
       </c>
       <c r="AD70">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE70">
         <v>48</v>
@@ -18200,7 +18200,7 @@
         <v>32</v>
       </c>
       <c r="AP70">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AQ70">
         <v>15.5</v>
@@ -18209,7 +18209,7 @@
         <v>7.2</v>
       </c>
       <c r="AS70">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT70">
         <v>10.5</v>
@@ -18334,16 +18334,16 @@
         <v>310</v>
       </c>
       <c r="F71">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G71">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H71">
         <v>3.85</v>
       </c>
       <c r="I71">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J71">
         <v>4.8</v>
@@ -18358,13 +18358,13 @@
         <v>1.01</v>
       </c>
       <c r="N71">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O71">
         <v>1.09</v>
       </c>
       <c r="P71">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q71">
         <v>1.3</v>
@@ -18373,10 +18373,10 @@
         <v>2.2</v>
       </c>
       <c r="S71">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="T71">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="U71">
         <v>3.25</v>
@@ -18385,13 +18385,13 @@
         <v>1.31</v>
       </c>
       <c r="W71">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X71">
         <v>65</v>
       </c>
       <c r="Y71">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Z71">
         <v>55</v>
@@ -18415,7 +18415,7 @@
         <v>24</v>
       </c>
       <c r="AG71">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH71">
         <v>17.5</v>
@@ -18436,22 +18436,22 @@
         <v>44</v>
       </c>
       <c r="AN71">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="AO71">
         <v>19.5</v>
       </c>
       <c r="AP71">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AQ71">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AR71">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AS71">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT71">
         <v>20</v>
@@ -18463,7 +18463,7 @@
         <v>17</v>
       </c>
       <c r="AW71">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AX71">
         <v>18</v>
@@ -18475,7 +18475,7 @@
         <v>13</v>
       </c>
       <c r="BA71">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB71">
         <v>20</v>
@@ -18487,10 +18487,10 @@
         <v>17.5</v>
       </c>
       <c r="BE71">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF71">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG71">
         <v>14.5</v>
@@ -18576,16 +18576,16 @@
         <v>311</v>
       </c>
       <c r="F72">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="G72">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H72">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I72">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J72">
         <v>4.8</v>
@@ -18594,7 +18594,7 @@
         <v>5.7</v>
       </c>
       <c r="L72">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="M72">
         <v>1.02</v>
@@ -18606,7 +18606,7 @@
         <v>1.12</v>
       </c>
       <c r="P72">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q72">
         <v>1.36</v>
@@ -18615,19 +18615,19 @@
         <v>1.88</v>
       </c>
       <c r="S72">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="T72">
         <v>1.52</v>
       </c>
       <c r="U72">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V72">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W72">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X72">
         <v>46</v>
@@ -18660,7 +18660,7 @@
         <v>12</v>
       </c>
       <c r="AH72">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI72">
         <v>55</v>
@@ -18684,16 +18684,16 @@
         <v>38</v>
       </c>
       <c r="AP72">
+        <v>7.4</v>
+      </c>
+      <c r="AQ72">
         <v>7</v>
       </c>
-      <c r="AQ72">
-        <v>6.6</v>
-      </c>
       <c r="AR72">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS72">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT72">
         <v>14</v>
@@ -18705,7 +18705,7 @@
         <v>19</v>
       </c>
       <c r="AW72">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX72">
         <v>12</v>
@@ -18717,7 +18717,7 @@
         <v>14.5</v>
       </c>
       <c r="BA72">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB72">
         <v>14.5</v>
@@ -18729,13 +18729,13 @@
         <v>19</v>
       </c>
       <c r="BE72">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF72">
         <v>4.3</v>
       </c>
       <c r="BG72">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH72">
         <v>1000</v>
@@ -19305,16 +19305,16 @@
         <v>2.46</v>
       </c>
       <c r="G75">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="H75">
         <v>2.64</v>
       </c>
       <c r="I75">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J75">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K75">
         <v>4.6</v>
@@ -19326,31 +19326,31 @@
         <v>1.05</v>
       </c>
       <c r="N75">
-        <v>2.64</v>
+        <v>4.5</v>
       </c>
       <c r="O75">
         <v>1.21</v>
       </c>
       <c r="P75">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q75">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="R75">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S75">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T75">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="U75">
         <v>2.3</v>
       </c>
       <c r="V75">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W75">
         <v>1.53</v>
@@ -19410,58 +19410,58 @@
         <v>1000</v>
       </c>
       <c r="AP75">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AQ75">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AR75">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AS75">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AT75">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AU75">
         <v>1.01</v>
       </c>
       <c r="AV75">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AW75">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AX75">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AY75">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AZ75">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BA75">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BB75">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BC75">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BD75">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BE75">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BF75">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BG75">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BH75">
         <v>1000</v>
@@ -19792,16 +19792,16 @@
         <v>4.7</v>
       </c>
       <c r="H77">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="I77">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J77">
         <v>4.1</v>
       </c>
       <c r="K77">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L77">
         <v>1.01</v>
@@ -19816,19 +19816,19 @@
         <v>1.2</v>
       </c>
       <c r="P77">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q77">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R77">
         <v>1.6</v>
       </c>
       <c r="S77">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T77">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U77">
         <v>2.42</v>
@@ -19843,13 +19843,13 @@
         <v>28</v>
       </c>
       <c r="Y77">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z77">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA77">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AB77">
         <v>25</v>
@@ -19918,31 +19918,31 @@
         <v>15</v>
       </c>
       <c r="AX77">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY77">
         <v>15.5</v>
       </c>
       <c r="AZ77">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA77">
         <v>10</v>
       </c>
       <c r="BB77">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC77">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BD77">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE77">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BF77">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG77">
         <v>7.2</v>
@@ -20052,7 +20052,7 @@
         <v>1.04</v>
       </c>
       <c r="N78">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O78">
         <v>1.22</v>
@@ -20124,7 +20124,7 @@
         <v>16.5</v>
       </c>
       <c r="AL78">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM78">
         <v>370</v>
@@ -20133,7 +20133,7 @@
         <v>4.5</v>
       </c>
       <c r="AO78">
-        <v>710</v>
+        <v>680</v>
       </c>
       <c r="AP78">
         <v>19.5</v>
@@ -20142,10 +20142,10 @@
         <v>40</v>
       </c>
       <c r="AR78">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS78">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AT78">
         <v>7.8</v>
@@ -20154,10 +20154,10 @@
         <v>14</v>
       </c>
       <c r="AV78">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="AW78">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX78">
         <v>6.2</v>
@@ -20169,7 +20169,7 @@
         <v>38</v>
       </c>
       <c r="BA78">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BB78">
         <v>7.6</v>
@@ -20181,7 +20181,7 @@
         <v>12.5</v>
       </c>
       <c r="BE78">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BF78">
         <v>4.2</v>
@@ -20193,13 +20193,13 @@
         <v>4.1</v>
       </c>
       <c r="BI78">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="BJ78">
         <v>15</v>
       </c>
       <c r="BK78">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BL78">
         <v>1000</v>
@@ -20282,7 +20282,7 @@
         <v>8.6</v>
       </c>
       <c r="J79">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K79">
         <v>4.3</v>
@@ -20297,7 +20297,7 @@
         <v>3.1</v>
       </c>
       <c r="O79">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P79">
         <v>1.7</v>
@@ -20321,7 +20321,7 @@
         <v>1.13</v>
       </c>
       <c r="W79">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X79">
         <v>11.5</v>
@@ -20518,7 +20518,7 @@
         <v>3.35</v>
       </c>
       <c r="H80">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I80">
         <v>2.42</v>
@@ -20557,7 +20557,7 @@
         <v>1.7</v>
       </c>
       <c r="U80">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V80">
         <v>1.7</v>
@@ -20566,7 +20566,7 @@
         <v>1.42</v>
       </c>
       <c r="X80">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y80">
         <v>12</v>
@@ -20575,16 +20575,16 @@
         <v>16.5</v>
       </c>
       <c r="AA80">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB80">
         <v>14.5</v>
       </c>
       <c r="AC80">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD80">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE80">
         <v>24</v>
@@ -20608,7 +20608,7 @@
         <v>34</v>
       </c>
       <c r="AL80">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM80">
         <v>80</v>
@@ -20617,7 +20617,7 @@
         <v>29</v>
       </c>
       <c r="AO80">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AP80">
         <v>14.5</v>
@@ -20629,7 +20629,7 @@
         <v>15</v>
       </c>
       <c r="AS80">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT80">
         <v>13</v>
@@ -20638,7 +20638,7 @@
         <v>7.6</v>
       </c>
       <c r="AV80">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW80">
         <v>21</v>
@@ -20662,13 +20662,13 @@
         <v>30</v>
       </c>
       <c r="BD80">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE80">
         <v>70</v>
       </c>
       <c r="BF80">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BG80">
         <v>15.5</v>
@@ -20683,7 +20683,7 @@
         <v>9</v>
       </c>
       <c r="BK80">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL80">
         <v>110</v>
@@ -20787,7 +20787,7 @@
         <v>2.12</v>
       </c>
       <c r="Q81">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R81">
         <v>1.44</v>
@@ -20805,7 +20805,7 @@
         <v>1.79</v>
       </c>
       <c r="W81">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X81">
         <v>16</v>
@@ -20865,7 +20865,7 @@
         <v>15</v>
       </c>
       <c r="AQ81">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR81">
         <v>13.5</v>
@@ -20996,19 +20996,19 @@
         <v>321</v>
       </c>
       <c r="F82">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="G82">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="H82">
+        <v>1.42</v>
+      </c>
+      <c r="I82">
         <v>1.43</v>
       </c>
-      <c r="I82">
-        <v>1.44</v>
-      </c>
       <c r="J82">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K82">
         <v>5.2</v>
@@ -21020,19 +21020,19 @@
         <v>1.06</v>
       </c>
       <c r="N82">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O82">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P82">
         <v>2.16</v>
       </c>
       <c r="Q82">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R82">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S82">
         <v>3.1</v>
@@ -21041,10 +21041,10 @@
         <v>2.14</v>
       </c>
       <c r="U82">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V82">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="W82">
         <v>1.11</v>
@@ -21080,7 +21080,7 @@
         <v>34</v>
       </c>
       <c r="AH82">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI82">
         <v>44</v>
@@ -21089,7 +21089,7 @@
         <v>380</v>
       </c>
       <c r="AK82">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AL82">
         <v>130</v>
@@ -21107,7 +21107,7 @@
         <v>16</v>
       </c>
       <c r="AQ82">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR82">
         <v>7.4</v>
@@ -21140,22 +21140,22 @@
         <v>34</v>
       </c>
       <c r="BB82">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC82">
+        <v>15.5</v>
+      </c>
+      <c r="BD82">
+        <v>15.5</v>
+      </c>
+      <c r="BE82">
         <v>16</v>
       </c>
-      <c r="BD82">
-        <v>16</v>
-      </c>
-      <c r="BE82">
-        <v>16.5</v>
-      </c>
       <c r="BF82">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG82">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH82">
         <v>4.1</v>
@@ -21244,7 +21244,7 @@
         <v>2.64</v>
       </c>
       <c r="H83">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="I83">
         <v>3.1</v>
@@ -21253,7 +21253,7 @@
         <v>3.55</v>
       </c>
       <c r="K83">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L83">
         <v>1.35</v>
@@ -21280,7 +21280,7 @@
         <v>3.1</v>
       </c>
       <c r="T83">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U83">
         <v>2.24</v>
@@ -21289,7 +21289,7 @@
         <v>1.47</v>
       </c>
       <c r="W83">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X83">
         <v>20</v>
@@ -21486,10 +21486,10 @@
         <v>2.4</v>
       </c>
       <c r="H84">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="I84">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J84">
         <v>3</v>
@@ -21501,7 +21501,7 @@
         <v>1.47</v>
       </c>
       <c r="M84">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N84">
         <v>2.84</v>
@@ -21522,13 +21522,13 @@
         <v>4.1</v>
       </c>
       <c r="T84">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U84">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V84">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W84">
         <v>1.72</v>
@@ -21546,7 +21546,7 @@
         <v>1000</v>
       </c>
       <c r="AB84">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC84">
         <v>970</v>
@@ -21964,13 +21964,13 @@
         <v>325</v>
       </c>
       <c r="F86">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="G86">
         <v>2.36</v>
       </c>
       <c r="H86">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I86">
         <v>4.8</v>
@@ -21979,7 +21979,7 @@
         <v>1.1</v>
       </c>
       <c r="K86">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="L86">
         <v>1.01</v>
@@ -21988,13 +21988,13 @@
         <v>1.01</v>
       </c>
       <c r="N86">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O86">
         <v>1.11</v>
       </c>
       <c r="P86">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q86">
         <v>1.34</v>
@@ -22003,7 +22003,7 @@
         <v>1.61</v>
       </c>
       <c r="S86">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="T86">
         <v>1.01</v>
@@ -22481,13 +22481,13 @@
         <v>1.28</v>
       </c>
       <c r="Q88">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R88">
         <v>1.08</v>
       </c>
       <c r="S88">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="T88">
         <v>1.01</v>
@@ -22699,7 +22699,7 @@
         <v>2.24</v>
       </c>
       <c r="I89">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J89">
         <v>3.35</v>
@@ -22717,31 +22717,31 @@
         <v>3.25</v>
       </c>
       <c r="O89">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P89">
         <v>1.77</v>
       </c>
       <c r="Q89">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="R89">
         <v>1.29</v>
       </c>
       <c r="S89">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T89">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="U89">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="V89">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W89">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X89">
         <v>12.5</v>
@@ -22768,7 +22768,7 @@
         <v>32</v>
       </c>
       <c r="AF89">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AG89">
         <v>16</v>
@@ -22795,7 +22795,7 @@
         <v>65</v>
       </c>
       <c r="AO89">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AP89">
         <v>10.5</v>
@@ -22807,7 +22807,7 @@
         <v>12</v>
       </c>
       <c r="AS89">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT89">
         <v>10.5</v>
@@ -22819,7 +22819,7 @@
         <v>10</v>
       </c>
       <c r="AW89">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX89">
         <v>20</v>
@@ -22831,22 +22831,22 @@
         <v>17.5</v>
       </c>
       <c r="BA89">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB89">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC89">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BD89">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BE89">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF89">
         <v>7.6</v>
-      </c>
-      <c r="BF89">
-        <v>7</v>
       </c>
       <c r="BG89">
         <v>19</v>
@@ -22953,16 +22953,16 @@
         <v>1.55</v>
       </c>
       <c r="M90">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N90">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="O90">
         <v>1.55</v>
       </c>
       <c r="P90">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q90">
         <v>2.64</v>
@@ -22986,7 +22986,7 @@
         <v>1.53</v>
       </c>
       <c r="X90">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="Y90">
         <v>9</v>
@@ -22998,7 +22998,7 @@
         <v>75</v>
       </c>
       <c r="AB90">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC90">
         <v>7.4</v>
@@ -23049,7 +23049,7 @@
         <v>16.5</v>
       </c>
       <c r="AS90">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT90">
         <v>7.2</v>
@@ -23061,7 +23061,7 @@
         <v>13</v>
       </c>
       <c r="AW90">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX90">
         <v>14</v>
@@ -23070,88 +23070,88 @@
         <v>12</v>
       </c>
       <c r="AZ90">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA90">
+        <v>8.4</v>
+      </c>
+      <c r="BB90">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC90">
         <v>7.6</v>
       </c>
-      <c r="BB90">
-        <v>7.4</v>
-      </c>
-      <c r="BC90">
-        <v>7</v>
-      </c>
       <c r="BD90">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE90">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF90">
         <v>8</v>
       </c>
-      <c r="BF90">
-        <v>7.2</v>
-      </c>
       <c r="BG90">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH90">
         <v>1000</v>
       </c>
       <c r="BI90">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BJ90">
         <v>1000</v>
       </c>
       <c r="BK90">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BL90">
         <v>1000</v>
       </c>
       <c r="BM90">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BN90">
         <v>1000</v>
       </c>
       <c r="BO90">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BP90">
         <v>1000</v>
       </c>
       <c r="BQ90">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BR90">
         <v>1000</v>
       </c>
       <c r="BS90">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BT90">
         <v>1000</v>
       </c>
       <c r="BU90">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BV90">
         <v>1000</v>
       </c>
       <c r="BW90">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BX90">
         <v>1000</v>
       </c>
       <c r="BY90">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BZ90">
         <v>1000</v>
       </c>
       <c r="CA90">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="CB90" t="s">
         <v>342</v>
@@ -23174,58 +23174,58 @@
         <v>330</v>
       </c>
       <c r="F91">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="G91">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H91">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I91">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J91">
         <v>4.6</v>
       </c>
       <c r="K91">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="L91">
         <v>1.29</v>
       </c>
       <c r="M91">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N91">
         <v>4</v>
       </c>
       <c r="O91">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P91">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="Q91">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R91">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S91">
         <v>2.96</v>
       </c>
       <c r="T91">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U91">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="V91">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W91">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X91">
         <v>1000</v>
@@ -23285,13 +23285,13 @@
         <v>8.4</v>
       </c>
       <c r="AQ91">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AR91">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AS91">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AT91">
         <v>5.3</v>
@@ -23300,10 +23300,10 @@
         <v>6.4</v>
       </c>
       <c r="AV91">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AW91">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AX91">
         <v>5.2</v>
@@ -23312,10 +23312,10 @@
         <v>6.4</v>
       </c>
       <c r="AZ91">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BA91">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BB91">
         <v>6.8</v>
@@ -23324,16 +23324,16 @@
         <v>8.4</v>
       </c>
       <c r="BD91">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BE91">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BF91">
         <v>4.6</v>
       </c>
       <c r="BG91">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BH91">
         <v>1000</v>
@@ -23670,7 +23670,7 @@
         <v>4.1</v>
       </c>
       <c r="J93">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="K93">
         <v>4.9</v>
@@ -23903,10 +23903,10 @@
         <v>2.72</v>
       </c>
       <c r="G94">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H94">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I94">
         <v>2.78</v>
@@ -24166,22 +24166,22 @@
         <v>1.05</v>
       </c>
       <c r="N95">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O95">
         <v>1.24</v>
       </c>
       <c r="P95">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="Q95">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="R95">
         <v>1.42</v>
       </c>
       <c r="S95">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="T95">
         <v>1.69</v>
@@ -24399,7 +24399,7 @@
         <v>5.5</v>
       </c>
       <c r="K96">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="L96">
         <v>1.25</v>
@@ -24411,10 +24411,10 @@
         <v>5.5</v>
       </c>
       <c r="O96">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P96">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q96">
         <v>1.58</v>
@@ -24423,16 +24423,16 @@
         <v>1.62</v>
       </c>
       <c r="S96">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="T96">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U96">
         <v>2.06</v>
       </c>
       <c r="V96">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W96">
         <v>3.15</v>
@@ -24474,7 +24474,7 @@
         <v>95</v>
       </c>
       <c r="AJ96">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AK96">
         <v>15</v>
@@ -24492,16 +24492,16 @@
         <v>120</v>
       </c>
       <c r="AP96">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ96">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR96">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AS96">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT96">
         <v>9.4</v>
@@ -24510,10 +24510,10 @@
         <v>11.5</v>
       </c>
       <c r="AV96">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AW96">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX96">
         <v>9</v>
@@ -24525,7 +24525,7 @@
         <v>17.5</v>
       </c>
       <c r="BA96">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB96">
         <v>11.5</v>
@@ -24534,16 +24534,16 @@
         <v>13</v>
       </c>
       <c r="BD96">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE96">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF96">
         <v>4.8</v>
       </c>
       <c r="BG96">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH96">
         <v>1000</v>
@@ -24626,22 +24626,22 @@
         <v>336</v>
       </c>
       <c r="F97">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="G97">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="H97">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I97">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J97">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K97">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L97">
         <v>1.01</v>
@@ -24656,13 +24656,13 @@
         <v>1.43</v>
       </c>
       <c r="P97">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q97">
         <v>2.22</v>
       </c>
       <c r="R97">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S97">
         <v>4.2</v>
@@ -24671,13 +24671,13 @@
         <v>1.93</v>
       </c>
       <c r="U97">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V97">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W97">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="X97">
         <v>11.5</v>
@@ -24698,7 +24698,7 @@
         <v>8.6</v>
       </c>
       <c r="AD97">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE97">
         <v>55</v>
@@ -24746,7 +24746,7 @@
         <v>7.8</v>
       </c>
       <c r="AT97">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU97">
         <v>7</v>
@@ -24770,7 +24770,7 @@
         <v>7.6</v>
       </c>
       <c r="BB97">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC97">
         <v>6.8</v>
@@ -24779,13 +24779,13 @@
         <v>7.4</v>
       </c>
       <c r="BE97">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF97">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG97">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH97">
         <v>1000</v>
@@ -24877,7 +24877,7 @@
         <v>3.1</v>
       </c>
       <c r="I98">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J98">
         <v>4</v>
@@ -25164,7 +25164,7 @@
         <v>1.71</v>
       </c>
       <c r="X99">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y99">
         <v>16</v>
@@ -25221,7 +25221,7 @@
         <v>16</v>
       </c>
       <c r="AQ99">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR99">
         <v>20</v>
@@ -25406,7 +25406,7 @@
         <v>1.38</v>
       </c>
       <c r="X100">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y100">
         <v>18</v>
@@ -25612,7 +25612,7 @@
         <v>6</v>
       </c>
       <c r="L101">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M101">
         <v>1.01</v>
@@ -25639,7 +25639,7 @@
         <v>1.47</v>
       </c>
       <c r="U101">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="V101">
         <v>1.16</v>
@@ -25696,16 +25696,16 @@
         <v>180</v>
       </c>
       <c r="AN101">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AO101">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP101">
         <v>29</v>
       </c>
       <c r="AQ101">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AR101">
         <v>34</v>
@@ -25738,7 +25738,7 @@
         <v>40</v>
       </c>
       <c r="BB101">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC101">
         <v>12</v>
@@ -25789,13 +25789,13 @@
         <v>1000</v>
       </c>
       <c r="BS101">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT101">
         <v>1000</v>
       </c>
       <c r="BU101">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BV101">
         <v>1000</v>
@@ -25863,7 +25863,7 @@
         <v>7.2</v>
       </c>
       <c r="O102">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P102">
         <v>3.05</v>
@@ -25887,7 +25887,7 @@
         <v>1.64</v>
       </c>
       <c r="W102">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X102">
         <v>40</v>
